--- a/excel/Japan_Neutral_Rate_Models.xlsx
+++ b/excel/Japan_Neutral_Rate_Models.xlsx
@@ -21779,19 +21779,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.721048762834366</v>
+        <v>2.189891650120106</v>
       </c>
       <c r="C4" t="n">
-        <v>4.629779820880789</v>
+        <v>3.704199271826353</v>
       </c>
       <c r="D4" t="n">
-        <v>4.927041302841351</v>
+        <v>1.600929458958214</v>
       </c>
       <c r="E4" t="n">
-        <v>4.714582215169532</v>
+        <v>2.718143682487966</v>
       </c>
       <c r="F4" t="n">
-        <v>4.433181481437944</v>
+        <v>2.669982087306957</v>
       </c>
     </row>
     <row r="5">
@@ -21801,22 +21801,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.768275420197056</v>
+        <v>2.190447218164243</v>
       </c>
       <c r="C5" t="n">
-        <v>4.792968368412067</v>
+        <v>3.704047735573145</v>
       </c>
       <c r="D5" t="n">
-        <v>4.898878053210615</v>
+        <v>1.601303527555404</v>
       </c>
       <c r="E5" t="n">
-        <v>4.94560065019061</v>
+        <v>2.717990697044214</v>
       </c>
       <c r="F5" t="n">
-        <v>4.378707722566554</v>
+        <v>2.669749703933348</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4990375072895265</v>
+        <v>0.1260408596170537</v>
       </c>
     </row>
     <row r="6">
@@ -21826,22 +21826,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.727383491179229</v>
+        <v>2.188500886490559</v>
       </c>
       <c r="C6" t="n">
-        <v>4.723941672392746</v>
+        <v>3.703592982563218</v>
       </c>
       <c r="D6" t="n">
-        <v>4.552358914111661</v>
+        <v>1.598855270361571</v>
       </c>
       <c r="E6" t="n">
-        <v>4.801631276889612</v>
+        <v>2.715392604877904</v>
       </c>
       <c r="F6" t="n">
-        <v>4.190439755207384</v>
+        <v>2.669098371687085</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4821354681305463</v>
+        <v>0.0975428846689432</v>
       </c>
     </row>
     <row r="7">
@@ -21851,22 +21851,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.372014992321049</v>
+        <v>2.183704018445536</v>
       </c>
       <c r="C7" t="n">
-        <v>4.60901301929429</v>
+        <v>3.702728773953192</v>
       </c>
       <c r="D7" t="n">
-        <v>4.3959320290006</v>
+        <v>1.592861023364508</v>
       </c>
       <c r="E7" t="n">
-        <v>4.443860435648523</v>
+        <v>2.709451361381313</v>
       </c>
       <c r="F7" t="n">
-        <v>4.024474319799194</v>
+        <v>2.667854680422479</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4775352268628376</v>
+        <v>0.0965917185550209</v>
       </c>
     </row>
     <row r="8">
@@ -21876,22 +21876,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.350494058334913</v>
+        <v>2.179532408884269</v>
       </c>
       <c r="C8" t="n">
-        <v>4.663343360858214</v>
+        <v>3.701362331830191</v>
       </c>
       <c r="D8" t="n">
-        <v>4.109666513600244</v>
+        <v>1.590126692019528</v>
       </c>
       <c r="E8" t="n">
-        <v>4.371869678303732</v>
+        <v>2.706370467296889</v>
       </c>
       <c r="F8" t="n">
-        <v>3.883101187046235</v>
+        <v>2.665881006259332</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3845638421233026</v>
+        <v>0.0358516745092611</v>
       </c>
     </row>
     <row r="9">
@@ -21901,22 +21901,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.660715867100982</v>
+        <v>2.175344893983689</v>
       </c>
       <c r="C9" t="n">
-        <v>4.833450709565691</v>
+        <v>3.699387075888097</v>
       </c>
       <c r="D9" t="n">
-        <v>4.116722488072258</v>
+        <v>1.589370518170815</v>
       </c>
       <c r="E9" t="n">
-        <v>4.608675492981162</v>
+        <v>2.705137618200976</v>
       </c>
       <c r="F9" t="n">
-        <v>3.827776549642256</v>
+        <v>2.663031039818183</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3836406707788879</v>
+        <v>0.0345884487796335</v>
       </c>
     </row>
     <row r="10">
@@ -21926,22 +21926,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.85984673083639</v>
+        <v>2.168719609259084</v>
       </c>
       <c r="C10" t="n">
-        <v>5.0453043412318</v>
+        <v>3.696701321823354</v>
       </c>
       <c r="D10" t="n">
-        <v>3.951034443128493</v>
+        <v>1.586382707390485</v>
       </c>
       <c r="E10" t="n">
-        <v>4.595875317115231</v>
+        <v>2.701819704182037</v>
       </c>
       <c r="F10" t="n">
-        <v>3.744466562977053</v>
+        <v>2.659162286155225</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3744557952316529</v>
+        <v>0.0179865256749753</v>
       </c>
     </row>
     <row r="11">
@@ -21951,22 +21951,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.972233968182793</v>
+        <v>2.159430616546703</v>
       </c>
       <c r="C11" t="n">
-        <v>5.189855067584999</v>
+        <v>3.693211176000598</v>
       </c>
       <c r="D11" t="n">
-        <v>3.909983992820288</v>
+        <v>1.582102566891606</v>
       </c>
       <c r="E11" t="n">
-        <v>4.634483292088405</v>
+        <v>2.697181702725392</v>
       </c>
       <c r="F11" t="n">
-        <v>3.68515361744374</v>
+        <v>2.654160620138721</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3793052173559146</v>
+        <v>0.0337865290468613</v>
       </c>
     </row>
     <row r="12">
@@ -21976,22 +21976,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.066098461761757</v>
+        <v>2.147634803552198</v>
       </c>
       <c r="C12" t="n">
-        <v>5.407091422152035</v>
+        <v>3.688854835180576</v>
       </c>
       <c r="D12" t="n">
-        <v>4.042701474114795</v>
+        <v>1.575545001627447</v>
       </c>
       <c r="E12" t="n">
-        <v>4.693889793590074</v>
+        <v>2.690353288005874</v>
       </c>
       <c r="F12" t="n">
-        <v>3.649859914377172</v>
+        <v>2.647933695623552</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4194985883576578</v>
+        <v>0.07855713527755979</v>
       </c>
     </row>
     <row r="13">
@@ -22001,22 +22001,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.297755949682279</v>
+        <v>2.13373373873255</v>
       </c>
       <c r="C13" t="n">
-        <v>5.708092267134655</v>
+        <v>3.683574737452496</v>
       </c>
       <c r="D13" t="n">
-        <v>3.764552056247531</v>
+        <v>1.568240753527408</v>
       </c>
       <c r="E13" t="n">
-        <v>4.738052075683869</v>
+        <v>2.682730092795138</v>
       </c>
       <c r="F13" t="n">
-        <v>3.504209335951731</v>
+        <v>2.640415684573156</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4017088125962316</v>
+        <v>0.0757869359993304</v>
       </c>
     </row>
     <row r="14">
@@ -22026,22 +22026,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.357823269149134</v>
+        <v>2.115809293586513</v>
       </c>
       <c r="C14" t="n">
-        <v>5.845637621461002</v>
+        <v>3.677310803238674</v>
       </c>
       <c r="D14" t="n">
-        <v>3.71750626768398</v>
+        <v>1.556488457230278</v>
       </c>
       <c r="E14" t="n">
-        <v>4.704323013933296</v>
+        <v>2.67098691945715</v>
       </c>
       <c r="F14" t="n">
-        <v>3.434966871163116</v>
+        <v>2.631552807021396</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3864331611520786</v>
+        <v>0.0512496486744027</v>
       </c>
     </row>
     <row r="15">
@@ -22051,22 +22051,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.215593235583411</v>
+        <v>2.093854762447159</v>
       </c>
       <c r="C15" t="n">
-        <v>5.6589083362319</v>
+        <v>3.67003370590148</v>
       </c>
       <c r="D15" t="n">
-        <v>3.584377760172797</v>
+        <v>1.54040105804124</v>
       </c>
       <c r="E15" t="n">
-        <v>4.501939257100252</v>
+        <v>2.655108396317335</v>
       </c>
       <c r="F15" t="n">
-        <v>3.33824236737876</v>
+        <v>2.62132983944717</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3445713271840722</v>
+        <v>0.0175076879362832</v>
       </c>
     </row>
     <row r="16">
@@ -22076,22 +22076,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.073671657818703</v>
+        <v>2.068870563326998</v>
       </c>
       <c r="C16" t="n">
-        <v>5.232290002205212</v>
+        <v>3.661761584127795</v>
       </c>
       <c r="D16" t="n">
-        <v>3.266584941715989</v>
+        <v>1.522107123116938</v>
       </c>
       <c r="E16" t="n">
-        <v>4.277237159355135</v>
+        <v>2.637077435383762</v>
       </c>
       <c r="F16" t="n">
-        <v>3.18234608429499</v>
+        <v>2.609766130551364</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2948350281935075</v>
+        <v>-0.0180516486011284</v>
       </c>
     </row>
     <row r="17">
@@ -22101,22 +22101,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.729515846204789</v>
+        <v>2.040302164908797</v>
       </c>
       <c r="C17" t="n">
-        <v>4.789394105757175</v>
+        <v>3.652548717586725</v>
       </c>
       <c r="D17" t="n">
-        <v>3.298981759147996</v>
+        <v>1.499869989740031</v>
       </c>
       <c r="E17" t="n">
-        <v>4.022349420439787</v>
+        <v>2.615349863603518</v>
       </c>
       <c r="F17" t="n">
-        <v>3.120723014520363</v>
+        <v>2.596901076951574</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3124160125248277</v>
+        <v>-0.0021354430092943</v>
       </c>
     </row>
     <row r="18">
@@ -22126,22 +22126,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.265200797145923</v>
+        <v>2.009702727467696</v>
       </c>
       <c r="C18" t="n">
-        <v>4.364987917261148</v>
+        <v>3.642452930951761</v>
       </c>
       <c r="D18" t="n">
-        <v>3.330977707279726</v>
+        <v>1.475317005685064</v>
       </c>
       <c r="E18" t="n">
-        <v>3.694468075053728</v>
+        <v>2.591354835406483</v>
       </c>
       <c r="F18" t="n">
-        <v>3.063979255577357</v>
+        <v>2.582807865942649</v>
       </c>
       <c r="G18" t="n">
-        <v>0.326416679008211</v>
+        <v>0.0266936957938512</v>
       </c>
     </row>
     <row r="19">
@@ -22151,22 +22151,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.977018697652542</v>
+        <v>1.979243716935558</v>
       </c>
       <c r="C19" t="n">
-        <v>3.973322005430403</v>
+        <v>3.631541510154553</v>
       </c>
       <c r="D19" t="n">
-        <v>3.160245270171484</v>
+        <v>1.452064404509695</v>
       </c>
       <c r="E19" t="n">
-        <v>3.488526759294173</v>
+        <v>2.568487001195752</v>
       </c>
       <c r="F19" t="n">
-        <v>2.967410085589829</v>
+        <v>2.567578849634717</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2857827795809949</v>
+        <v>0.0066223612034019</v>
       </c>
     </row>
     <row r="20">
@@ -22176,22 +22176,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.708537185182183</v>
+        <v>1.948855202445783</v>
       </c>
       <c r="C20" t="n">
-        <v>3.53152248879491</v>
+        <v>3.619881522975725</v>
       </c>
       <c r="D20" t="n">
-        <v>3.011522574573385</v>
+        <v>1.427935867313657</v>
       </c>
       <c r="E20" t="n">
-        <v>3.182172689319129</v>
+        <v>2.544854551189405</v>
       </c>
       <c r="F20" t="n">
-        <v>2.890708978197204</v>
+        <v>2.551299803168966</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2597311278885996</v>
+        <v>-0.0231104152809987</v>
       </c>
     </row>
     <row r="21">
@@ -22201,22 +22201,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.609315417724024</v>
+        <v>1.919636450125448</v>
       </c>
       <c r="C21" t="n">
-        <v>3.255242360848343</v>
+        <v>3.607564872832095</v>
       </c>
       <c r="D21" t="n">
-        <v>3.033981838535724</v>
+        <v>1.40693347590827</v>
       </c>
       <c r="E21" t="n">
-        <v>3.202958598004406</v>
+        <v>2.524038553873228</v>
       </c>
       <c r="F21" t="n">
-        <v>2.853757903837495</v>
+        <v>2.5340655476405</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2385867963274466</v>
+        <v>-0.0236941106764547</v>
       </c>
     </row>
     <row r="22">
@@ -22226,22 +22226,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.375973328689816</v>
+        <v>1.890461305144194</v>
       </c>
       <c r="C22" t="n">
-        <v>3.019052283716936</v>
+        <v>3.594654977261091</v>
       </c>
       <c r="D22" t="n">
-        <v>2.853998638239072</v>
+        <v>1.384889483213314</v>
       </c>
       <c r="E22" t="n">
-        <v>2.91254391019912</v>
+        <v>2.502334289124915</v>
       </c>
       <c r="F22" t="n">
-        <v>2.765656440617554</v>
+        <v>2.515954076164033</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2151036741519377</v>
+        <v>-0.0568746111186525</v>
       </c>
     </row>
     <row r="23">
@@ -22251,22 +22251,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.105964834036203</v>
+        <v>1.86237390102627</v>
       </c>
       <c r="C23" t="n">
-        <v>2.700391875043821</v>
+        <v>3.581210762686716</v>
       </c>
       <c r="D23" t="n">
-        <v>2.705525941518409</v>
+        <v>1.364773022570745</v>
       </c>
       <c r="E23" t="n">
-        <v>2.672013483053509</v>
+        <v>2.482345179822625</v>
       </c>
       <c r="F23" t="n">
-        <v>2.668199037307208</v>
+        <v>2.497052257678096</v>
       </c>
       <c r="G23" t="n">
-        <v>0.197401061297292</v>
+        <v>-0.0580827465975397</v>
       </c>
     </row>
     <row r="24">
@@ -22276,22 +22276,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9827060157664635</v>
+        <v>1.836687736552514</v>
       </c>
       <c r="C24" t="n">
-        <v>2.43924660486648</v>
+        <v>3.567305346170463</v>
       </c>
       <c r="D24" t="n">
-        <v>2.821515977734322</v>
+        <v>1.347680158226735</v>
       </c>
       <c r="E24" t="n">
-        <v>2.62034945072944</v>
+        <v>2.465147897612784</v>
       </c>
       <c r="F24" t="n">
-        <v>2.641340208172331</v>
+        <v>2.477436928968711</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2251615320102626</v>
+        <v>-0.0211301506248714</v>
       </c>
     </row>
     <row r="25">
@@ -22301,22 +22301,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.049161939443687</v>
+        <v>1.813660547016896</v>
       </c>
       <c r="C25" t="n">
-        <v>2.216072890701886</v>
+        <v>3.552990702315751</v>
       </c>
       <c r="D25" t="n">
-        <v>2.71881848769591</v>
+        <v>1.334895680366637</v>
       </c>
       <c r="E25" t="n">
-        <v>2.660722846215717</v>
+        <v>2.451932427547764</v>
       </c>
       <c r="F25" t="n">
-        <v>2.57683443737451</v>
+        <v>2.457169321990193</v>
       </c>
       <c r="G25" t="n">
-        <v>0.234713627225705</v>
+        <v>0.0005779417961825</v>
       </c>
     </row>
     <row r="26">
@@ -22326,22 +22326,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9157206978410316</v>
+        <v>1.791614166107401</v>
       </c>
       <c r="C26" t="n">
-        <v>2.153339309597555</v>
+        <v>3.538315925370654</v>
       </c>
       <c r="D26" t="n">
-        <v>2.854508441501176</v>
+        <v>1.322176792759244</v>
       </c>
       <c r="E26" t="n">
-        <v>2.555761815084665</v>
+        <v>2.438860241158926</v>
       </c>
       <c r="F26" t="n">
-        <v>2.582205103271299</v>
+        <v>2.436284189603058</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2917985901182188</v>
+        <v>0.0470348945163674</v>
       </c>
     </row>
     <row r="27">
@@ -22351,22 +22351,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.780309698807645</v>
+        <v>1.77198929532921</v>
       </c>
       <c r="C27" t="n">
-        <v>2.329227729186209</v>
+        <v>3.523309136752895</v>
       </c>
       <c r="D27" t="n">
-        <v>2.823001714751958</v>
+        <v>1.312579411768322</v>
       </c>
       <c r="E27" t="n">
-        <v>2.447886891888274</v>
+        <v>2.428611636987137</v>
       </c>
       <c r="F27" t="n">
-        <v>2.569459952550603</v>
+        <v>2.414818569073918</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3159837234929037</v>
+        <v>0.09116281021064809</v>
       </c>
     </row>
     <row r="28">
@@ -22376,22 +22376,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8535480032120311</v>
+        <v>1.755859335529364</v>
       </c>
       <c r="C28" t="n">
-        <v>2.590339177035117</v>
+        <v>3.507962215206461</v>
       </c>
       <c r="D28" t="n">
-        <v>3.2082919641827</v>
+        <v>1.307079240684258</v>
       </c>
       <c r="E28" t="n">
-        <v>2.679383295482657</v>
+        <v>2.422192121814713</v>
       </c>
       <c r="F28" t="n">
-        <v>2.662325231364947</v>
+        <v>2.392787990538898</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4156346694509942</v>
+        <v>0.2003873630464581</v>
       </c>
     </row>
     <row r="29">
@@ -22401,22 +22401,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.071653442071753</v>
+        <v>1.742779689820447</v>
       </c>
       <c r="C29" t="n">
-        <v>2.627131153417071</v>
+        <v>3.492242189273123</v>
       </c>
       <c r="D29" t="n">
-        <v>3.136897712895402</v>
+        <v>1.304572045508858</v>
       </c>
       <c r="E29" t="n">
-        <v>2.811540768700104</v>
+        <v>2.41862024578726</v>
       </c>
       <c r="F29" t="n">
-        <v>2.684295658729093</v>
+        <v>2.37018138297919</v>
       </c>
       <c r="G29" t="n">
-        <v>0.406047985841667</v>
+        <v>0.1953269074853862</v>
       </c>
     </row>
     <row r="30">
@@ -22426,22 +22426,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.258096162596162</v>
+        <v>1.731381557658903</v>
       </c>
       <c r="C30" t="n">
-        <v>2.622841718718331</v>
+        <v>3.476146361211454</v>
       </c>
       <c r="D30" t="n">
-        <v>3.264662821103596</v>
+        <v>1.302935876269844</v>
       </c>
       <c r="E30" t="n">
-        <v>2.984379581810051</v>
+        <v>2.415963208807361</v>
       </c>
       <c r="F30" t="n">
-        <v>2.714715193298326</v>
+        <v>2.346962456568255</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4221486758555066</v>
+        <v>0.2077266363272396</v>
       </c>
     </row>
     <row r="31">
@@ -22451,22 +22451,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.425247624422975</v>
+        <v>1.721276278468505</v>
       </c>
       <c r="C31" t="n">
-        <v>2.831797787368921</v>
+        <v>3.459669325531499</v>
       </c>
       <c r="D31" t="n">
-        <v>3.083537719251225</v>
+        <v>1.30191205684301</v>
       </c>
       <c r="E31" t="n">
-        <v>3.019612858133093</v>
+        <v>2.413924454846425</v>
       </c>
       <c r="F31" t="n">
-        <v>2.615439780357564</v>
+        <v>2.323084990136792</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4043832424245843</v>
+        <v>0.1953108898499289</v>
       </c>
     </row>
     <row r="32">
@@ -22476,22 +22476,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.648391108995001</v>
+        <v>1.71220401190274</v>
       </c>
       <c r="C32" t="n">
-        <v>3.053959627779303</v>
+        <v>3.442760583498273</v>
       </c>
       <c r="D32" t="n">
-        <v>2.781595628944289</v>
+        <v>1.301432525062104</v>
       </c>
       <c r="E32" t="n">
-        <v>3.021327343618753</v>
+        <v>2.412451605272233</v>
       </c>
       <c r="F32" t="n">
-        <v>2.476217979869334</v>
+        <v>2.29849177391398</v>
       </c>
       <c r="G32" t="n">
-        <v>0.3525215299450426</v>
+        <v>0.1458741166938664</v>
       </c>
     </row>
     <row r="33">
@@ -22501,22 +22501,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.856101858194765</v>
+        <v>1.702934086631234</v>
       </c>
       <c r="C33" t="n">
-        <v>3.115718098560144</v>
+        <v>3.425364743487543</v>
       </c>
       <c r="D33" t="n">
-        <v>2.755792295747576</v>
+        <v>1.301645236826378</v>
       </c>
       <c r="E33" t="n">
-        <v>3.209582850911826</v>
+        <v>2.4116399174269</v>
       </c>
       <c r="F33" t="n">
-        <v>2.418363556403285</v>
+        <v>2.273117691393022</v>
       </c>
       <c r="G33" t="n">
-        <v>0.329926617999432</v>
+        <v>0.1259518535493879</v>
       </c>
     </row>
     <row r="34">
@@ -22526,22 +22526,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.670062400036098</v>
+        <v>1.691624912639619</v>
       </c>
       <c r="C34" t="n">
-        <v>3.256500408518742</v>
+        <v>3.407454792917298</v>
       </c>
       <c r="D34" t="n">
-        <v>2.722894523298808</v>
+        <v>1.29760576642053</v>
       </c>
       <c r="E34" t="n">
-        <v>2.988704703016591</v>
+        <v>2.406939335312289</v>
       </c>
       <c r="F34" t="n">
-        <v>2.353991757667252</v>
+        <v>2.246892890873312</v>
       </c>
       <c r="G34" t="n">
-        <v>0.3603600090617886</v>
+        <v>0.1431911932610314</v>
       </c>
     </row>
     <row r="35">
@@ -22551,22 +22551,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.529835903470534</v>
+        <v>1.680735566418901</v>
       </c>
       <c r="C35" t="n">
-        <v>3.446887201331041</v>
+        <v>3.388980354340865</v>
       </c>
       <c r="D35" t="n">
-        <v>2.578548372169793</v>
+        <v>1.294899512155719</v>
       </c>
       <c r="E35" t="n">
-        <v>2.886831854700689</v>
+        <v>2.403345555146186</v>
       </c>
       <c r="F35" t="n">
-        <v>2.289015701934223</v>
+        <v>2.219773899372953</v>
       </c>
       <c r="G35" t="n">
-        <v>0.3025094642556143</v>
+        <v>0.1115597947533011</v>
       </c>
     </row>
     <row r="36">
@@ -22576,22 +22576,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.673975937500857</v>
+        <v>1.671169995762055</v>
       </c>
       <c r="C36" t="n">
-        <v>3.620553154259175</v>
+        <v>3.369885637216781</v>
       </c>
       <c r="D36" t="n">
-        <v>2.6493920913439</v>
+        <v>1.293665163631378</v>
       </c>
       <c r="E36" t="n">
-        <v>3.020544163727583</v>
+        <v>2.40114573791169</v>
       </c>
       <c r="F36" t="n">
-        <v>2.268819650192612</v>
+        <v>2.191705869267007</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3102721228574925</v>
+        <v>0.1226919285602181</v>
       </c>
     </row>
     <row r="37">
@@ -22601,22 +22601,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.067685874657794</v>
+        <v>1.662232049702452</v>
       </c>
       <c r="C37" t="n">
-        <v>3.917769114615664</v>
+        <v>3.35012973234538</v>
       </c>
       <c r="D37" t="n">
-        <v>2.457753746655063</v>
+        <v>1.293825581864107</v>
       </c>
       <c r="E37" t="n">
-        <v>3.222881102893485</v>
+        <v>2.400245556238961</v>
       </c>
       <c r="F37" t="n">
-        <v>2.19059992394598</v>
+        <v>2.162624661503957</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2744377379291498</v>
+        <v>0.0916410020377376</v>
       </c>
     </row>
     <row r="38">
@@ -22626,22 +22626,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.337055499409851</v>
+        <v>1.651261759952014</v>
       </c>
       <c r="C38" t="n">
-        <v>4.13752303421025</v>
+        <v>3.329647835656707</v>
       </c>
       <c r="D38" t="n">
-        <v>2.443216800305457</v>
+        <v>1.291620984220644</v>
       </c>
       <c r="E38" t="n">
-        <v>3.382379614750564</v>
+        <v>2.397206212303082</v>
       </c>
       <c r="F38" t="n">
-        <v>2.140592001921538</v>
+        <v>2.132455764278764</v>
       </c>
       <c r="G38" t="n">
-        <v>0.2824763312222142</v>
+        <v>0.08833780805676</v>
       </c>
     </row>
     <row r="39">
@@ -22651,22 +22651,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.250874318216</v>
+        <v>1.636961451213276</v>
       </c>
       <c r="C39" t="n">
-        <v>4.23238381756379</v>
+        <v>3.308393332950041</v>
       </c>
       <c r="D39" t="n">
-        <v>2.267612395337974</v>
+        <v>1.284905785048381</v>
       </c>
       <c r="E39" t="n">
-        <v>3.206452573886638</v>
+        <v>2.389951686405977</v>
       </c>
       <c r="F39" t="n">
-        <v>2.060023002810882</v>
+        <v>2.101141196534736</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2465072590363075</v>
+        <v>0.0493848157362193</v>
       </c>
     </row>
     <row r="40">
@@ -22676,22 +22676,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.113961310631939</v>
+        <v>1.620826701353364</v>
       </c>
       <c r="C40" t="n">
-        <v>4.214861250228987</v>
+        <v>3.286335311125574</v>
       </c>
       <c r="D40" t="n">
-        <v>2.18673029943008</v>
+        <v>1.276461361897965</v>
       </c>
       <c r="E40" t="n">
-        <v>3.093450176312589</v>
+        <v>2.380994194105223</v>
       </c>
       <c r="F40" t="n">
-        <v>1.995654988615841</v>
+        <v>2.068651237092074</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2057847781716636</v>
+        <v>0.0224505980308911</v>
       </c>
     </row>
     <row r="41">
@@ -22701,22 +22701,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.211747415862476</v>
+        <v>1.604125936759885</v>
       </c>
       <c r="C41" t="n">
-        <v>4.155790723258152</v>
+        <v>3.263459249393464</v>
       </c>
       <c r="D41" t="n">
-        <v>2.13152720250282</v>
+        <v>1.267804021889693</v>
       </c>
       <c r="E41" t="n">
-        <v>3.146653847534038</v>
+        <v>2.371792402728037</v>
       </c>
       <c r="F41" t="n">
-        <v>1.921130418351338</v>
+        <v>2.034967214223038</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1790238236397466</v>
+        <v>0.0049375456997129</v>
       </c>
     </row>
     <row r="42">
@@ -22726,22 +22726,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.529091909023697</v>
+        <v>1.586249061063955</v>
       </c>
       <c r="C42" t="n">
-        <v>4.237889914748818</v>
+        <v>3.239768597625786</v>
       </c>
       <c r="D42" t="n">
-        <v>1.852284831305908</v>
+        <v>1.258624774255395</v>
       </c>
       <c r="E42" t="n">
-        <v>3.249395310069726</v>
+        <v>2.36209860048033</v>
       </c>
       <c r="F42" t="n">
-        <v>1.786999372036825</v>
+        <v>2.000072153080987</v>
       </c>
       <c r="G42" t="n">
-        <v>0.138441074673407</v>
+        <v>-0.0332924668342601</v>
       </c>
     </row>
     <row r="43">
@@ -22751,22 +22751,22 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.705191073434622</v>
+        <v>1.564875240540723</v>
       </c>
       <c r="C43" t="n">
-        <v>4.287680112802105</v>
+        <v>3.215247820217695</v>
       </c>
       <c r="D43" t="n">
-        <v>1.847701082061192</v>
+        <v>1.245504232967694</v>
       </c>
       <c r="E43" t="n">
-        <v>3.326623022128491</v>
+        <v>2.34876129217836</v>
       </c>
       <c r="F43" t="n">
-        <v>1.72930356975127</v>
+        <v>1.963952841690163</v>
       </c>
       <c r="G43" t="n">
-        <v>0.122944107056635</v>
+        <v>-0.0597248096983747</v>
       </c>
     </row>
     <row r="44">
@@ -22776,22 +22776,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.616211974964135</v>
+        <v>1.53925969199973</v>
       </c>
       <c r="C44" t="n">
-        <v>4.404665654297498</v>
+        <v>3.189910556413487</v>
       </c>
       <c r="D44" t="n">
-        <v>1.688829417297264</v>
+        <v>1.227696404284007</v>
       </c>
       <c r="E44" t="n">
-        <v>3.175481647650941</v>
+        <v>2.33099497219901</v>
       </c>
       <c r="F44" t="n">
-        <v>1.622984544286104</v>
+        <v>1.926624898469088</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1028416565289771</v>
+        <v>-0.0772337452879384</v>
       </c>
     </row>
     <row r="45">
@@ -22801,22 +22801,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.382020357292382</v>
+        <v>1.510271192323896</v>
       </c>
       <c r="C45" t="n">
-        <v>4.338620899869046</v>
+        <v>3.163755833549857</v>
       </c>
       <c r="D45" t="n">
-        <v>1.613569545891423</v>
+        <v>1.205795438748156</v>
       </c>
       <c r="E45" t="n">
-        <v>2.952217682710272</v>
+        <v>2.309356287013024</v>
       </c>
       <c r="F45" t="n">
-        <v>1.531171842169765</v>
+        <v>1.888134635943045</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0907333496161444</v>
+        <v>-0.0835904125550488</v>
       </c>
     </row>
     <row r="46">
@@ -22826,22 +22826,22 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.285662354113428</v>
+        <v>1.479497154582661</v>
       </c>
       <c r="C46" t="n">
-        <v>4.304575725715189</v>
+        <v>3.136831240924697</v>
       </c>
       <c r="D46" t="n">
-        <v>1.464900291532441</v>
+        <v>1.182884146690522</v>
       </c>
       <c r="E46" t="n">
-        <v>2.866802008021421</v>
+        <v>2.286686020948292</v>
       </c>
       <c r="F46" t="n">
-        <v>1.447996533905097</v>
+        <v>1.84855540522009</v>
       </c>
       <c r="G46" t="n">
-        <v>0.024092171454853</v>
+        <v>-0.1350723706187371</v>
       </c>
     </row>
     <row r="47">
@@ -22851,22 +22851,22 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.214523387085665</v>
+        <v>1.44645799302977</v>
       </c>
       <c r="C47" t="n">
-        <v>4.30690845679166</v>
+        <v>3.109181100951862</v>
       </c>
       <c r="D47" t="n">
-        <v>1.420742498650009</v>
+        <v>1.157178333086071</v>
       </c>
       <c r="E47" t="n">
-        <v>2.782627043637529</v>
+        <v>2.261436978642108</v>
       </c>
       <c r="F47" t="n">
-        <v>1.367227422392219</v>
+        <v>1.807966808552678</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0183014944253302</v>
+        <v>-0.1448840512872919</v>
       </c>
     </row>
     <row r="48">
@@ -22876,22 +22876,22 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.122399284539686</v>
+        <v>1.411224281417482</v>
       </c>
       <c r="C48" t="n">
-        <v>4.242308896020484</v>
+        <v>3.080853158161186</v>
       </c>
       <c r="D48" t="n">
-        <v>1.182285623216786</v>
+        <v>1.129073927458675</v>
       </c>
       <c r="E48" t="n">
-        <v>2.605584526312091</v>
+        <v>2.233917923197705</v>
       </c>
       <c r="F48" t="n">
-        <v>1.240554320052081</v>
+        <v>1.766467420533228</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.037963785048344</v>
+        <v>-0.1956822730450083</v>
       </c>
     </row>
     <row r="49">
@@ -22901,22 +22901,22 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.012768458416034</v>
+        <v>1.373842544566</v>
       </c>
       <c r="C49" t="n">
-        <v>4.051898942214991</v>
+        <v>3.051912042595113</v>
       </c>
       <c r="D49" t="n">
-        <v>1.161505202387272</v>
+        <v>1.099081155020391</v>
       </c>
       <c r="E49" t="n">
-        <v>2.54569780824815</v>
+        <v>2.204618631202043</v>
       </c>
       <c r="F49" t="n">
-        <v>1.140753111001354</v>
+        <v>1.724170417820752</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.0632121623662511</v>
+        <v>-0.2171351479762046</v>
       </c>
     </row>
     <row r="50">
@@ -22926,22 +22926,22 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1.761387485817318</v>
+        <v>1.334083835637386</v>
       </c>
       <c r="C50" t="n">
-        <v>3.696324637826146</v>
+        <v>3.022438944393438</v>
       </c>
       <c r="D50" t="n">
-        <v>0.7419312632465013</v>
+        <v>1.065777258290641</v>
       </c>
       <c r="E50" t="n">
-        <v>2.150631065515639</v>
+        <v>2.172242284467123</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9467571300265908</v>
+        <v>1.681202203083539</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.1405177077572812</v>
+        <v>-0.2961728818308055</v>
       </c>
     </row>
     <row r="51">
@@ -22951,22 +22951,22 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1.490653021571208</v>
+        <v>1.292901499926925</v>
       </c>
       <c r="C51" t="n">
-        <v>3.441970712369684</v>
+        <v>2.992550281553824</v>
       </c>
       <c r="D51" t="n">
-        <v>0.7011172747052339</v>
+        <v>1.032014330553935</v>
       </c>
       <c r="E51" t="n">
-        <v>1.982084607564349</v>
+        <v>2.139362663140425</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8370609247311295</v>
+        <v>1.637709553521216</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.1695606971293773</v>
+        <v>-0.3140193235155477</v>
       </c>
     </row>
     <row r="52">
@@ -22976,22 +22976,22 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.15767190078465</v>
+        <v>1.250718483136281</v>
       </c>
       <c r="C52" t="n">
-        <v>3.070883344814184</v>
+        <v>2.962333886838155</v>
       </c>
       <c r="D52" t="n">
-        <v>0.5245414137641146</v>
+        <v>0.9970455166459252</v>
       </c>
       <c r="E52" t="n">
-        <v>1.656185970991491</v>
+        <v>2.105344835660812</v>
       </c>
       <c r="F52" t="n">
-        <v>0.7218575234048269</v>
+        <v>1.593845355750153</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.2077216187341765</v>
+        <v>-0.3513926912347382</v>
       </c>
     </row>
     <row r="53">
@@ -23001,22 +23001,22 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8488299675867359</v>
+        <v>1.208642603154051</v>
       </c>
       <c r="C53" t="n">
-        <v>2.709722233334005</v>
+        <v>2.931908514334981</v>
       </c>
       <c r="D53" t="n">
-        <v>0.4889191130735401</v>
+        <v>0.9631268691182342</v>
       </c>
       <c r="E53" t="n">
-        <v>1.450886605347854</v>
+        <v>2.072238420437797</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6404926209241446</v>
+        <v>1.5497721168659</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.2256723051266764</v>
+        <v>-0.3582366783965688</v>
       </c>
     </row>
     <row r="54">
@@ -23026,22 +23026,22 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4803738147719123</v>
+        <v>1.166930422607087</v>
       </c>
       <c r="C54" t="n">
-        <v>2.276067793954716</v>
+        <v>2.90137973182753</v>
       </c>
       <c r="D54" t="n">
-        <v>0.4447428948607848</v>
+        <v>0.930172550238712</v>
       </c>
       <c r="E54" t="n">
-        <v>1.21076986125199</v>
+        <v>2.040019553216952</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5547055999059055</v>
+        <v>1.505648157081085</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.2343944477146844</v>
+        <v>-0.3637589467848117</v>
       </c>
     </row>
     <row r="55">
@@ -23051,22 +23051,22 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.0282298780849457</v>
+        <v>1.126350547510351</v>
       </c>
       <c r="C55" t="n">
-        <v>1.720832371682023</v>
+        <v>2.870855211897288</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2965278516121949</v>
+        <v>0.8977186786024909</v>
       </c>
       <c r="E55" t="n">
-        <v>0.7522451207174434</v>
+        <v>2.00826716129285</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4355996756024151</v>
+        <v>1.461627489506362</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.2425913618610583</v>
+        <v>-0.3701233999256625</v>
       </c>
     </row>
     <row r="56">
@@ -23076,22 +23076,22 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.2620902452000679</v>
+        <v>1.089673593450827</v>
       </c>
       <c r="C56" t="n">
-        <v>1.317788666911444</v>
+        <v>2.840461486361153</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3070400147278574</v>
+        <v>0.8716707988549066</v>
       </c>
       <c r="E56" t="n">
-        <v>0.6879415512378999</v>
+        <v>1.982373814755576</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3597538487182386</v>
+        <v>1.417861962434242</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.2698859912589961</v>
+        <v>-0.3729773212536985</v>
       </c>
     </row>
     <row r="57">
@@ -23101,22 +23101,22 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.3574168481750335</v>
+        <v>1.056547884508805</v>
       </c>
       <c r="C57" t="n">
-        <v>1.007062490969231</v>
+        <v>2.810286867412405</v>
       </c>
       <c r="D57" t="n">
-        <v>0.1796818816346977</v>
+        <v>0.8496394825059896</v>
       </c>
       <c r="E57" t="n">
-        <v>0.5569737353742348</v>
+        <v>1.960294912737622</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2482528864396585</v>
+        <v>1.37446435629943</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.2780634847826022</v>
+        <v>-0.3875198690049379</v>
       </c>
     </row>
     <row r="58">
@@ -23126,22 +23126,22 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.3730641106148453</v>
+        <v>1.026982053336656</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9925969653306213</v>
+        <v>2.780419415696717</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0683802689773398</v>
+        <v>0.8324717454532609</v>
       </c>
       <c r="E58" t="n">
-        <v>0.4870017836741314</v>
+        <v>1.942721927786433</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1318260140373013</v>
+        <v>1.331524434145823</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.2703518653981662</v>
+        <v>-0.3741620859885333</v>
       </c>
     </row>
     <row r="59">
@@ -23151,22 +23151,22 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.2005319350015653</v>
+        <v>1.001358619657096</v>
       </c>
       <c r="C59" t="n">
-        <v>1.1758281525568</v>
+        <v>2.750900355221919</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.0143534635520186</v>
+        <v>0.8210233796537985</v>
       </c>
       <c r="E59" t="n">
-        <v>0.5528173072696357</v>
+        <v>1.930443061799677</v>
       </c>
       <c r="F59" t="n">
-        <v>0.08067131443761009</v>
+        <v>1.289104716350588</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.2798270002383533</v>
+        <v>-0.3782958115464885</v>
       </c>
     </row>
     <row r="60">
@@ -23176,22 +23176,22 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.0422085504645495</v>
+        <v>0.9784678208427482</v>
       </c>
       <c r="C60" t="n">
-        <v>1.347992533207764</v>
+        <v>2.721739941614024</v>
       </c>
       <c r="D60" t="n">
-        <v>0.229343498417237</v>
+        <v>0.814684070761194</v>
       </c>
       <c r="E60" t="n">
-        <v>0.862455429645601</v>
+        <v>1.922895298295551</v>
       </c>
       <c r="F60" t="n">
-        <v>0.1467966324927032</v>
+        <v>1.247236686251959</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.2279168321961037</v>
+        <v>-0.3258524459372071</v>
       </c>
     </row>
     <row r="61">
@@ -23201,22 +23201,22 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.017483682102918</v>
+        <v>0.9566099535859428</v>
       </c>
       <c r="C61" t="n">
-        <v>1.42476320133418</v>
+        <v>2.692941323099362</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3562390390019008</v>
+        <v>0.8083031048902694</v>
       </c>
       <c r="E61" t="n">
-        <v>0.7702486789221523</v>
+        <v>1.915345392617331</v>
       </c>
       <c r="F61" t="n">
-        <v>0.197420948637094</v>
+        <v>1.205926405075722</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.1602982267816997</v>
+        <v>-0.2713705695385653</v>
       </c>
     </row>
     <row r="62">
@@ -23226,22 +23226,22 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.0310523112886502</v>
+        <v>0.9374300707292478</v>
       </c>
       <c r="C62" t="n">
-        <v>1.576578367406628</v>
+        <v>2.664513710534574</v>
       </c>
       <c r="D62" t="n">
-        <v>0.4126164783294909</v>
+        <v>0.8072052630720981</v>
       </c>
       <c r="E62" t="n">
-        <v>0.8942474410951069</v>
+        <v>1.912570683675112</v>
       </c>
       <c r="F62" t="n">
-        <v>0.2408859046538465</v>
+        <v>1.165183749374532</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.1693510664209793</v>
+        <v>-0.2556424308061253</v>
       </c>
     </row>
     <row r="63">
@@ -23251,22 +23251,22 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.1598500271363492</v>
+        <v>0.9202325266898734</v>
       </c>
       <c r="C63" t="n">
-        <v>1.826234276944778</v>
+        <v>2.636441586700357</v>
       </c>
       <c r="D63" t="n">
-        <v>0.4416650149708778</v>
+        <v>0.8065913799941864</v>
       </c>
       <c r="E63" t="n">
-        <v>0.7422424934689168</v>
+        <v>1.910345897014345</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2810986160943631</v>
+        <v>1.124985312195941</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.1476711497459741</v>
+        <v>-0.2494178940019917</v>
       </c>
     </row>
     <row r="64">
@@ -23276,22 +23276,22 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.0330023576720206</v>
+        <v>0.907080884943714</v>
       </c>
       <c r="C64" t="n">
-        <v>2.107707948640853</v>
+        <v>2.608689783711277</v>
       </c>
       <c r="D64" t="n">
-        <v>0.426526006313105</v>
+        <v>0.8125805921439584</v>
       </c>
       <c r="E64" t="n">
-        <v>0.9551239085256528</v>
+        <v>1.914130325166544</v>
       </c>
       <c r="F64" t="n">
-        <v>0.3187818837150023</v>
+        <v>1.085306162734366</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.1933248013240698</v>
+        <v>-0.2689864925010032</v>
       </c>
     </row>
     <row r="65">
@@ -23301,22 +23301,22 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4540957112489079</v>
+        <v>0.8966002315488959</v>
       </c>
       <c r="C65" t="n">
-        <v>2.341137753719673</v>
+        <v>2.581213185517281</v>
       </c>
       <c r="D65" t="n">
-        <v>0.5050217051443617</v>
+        <v>0.8217088588778019</v>
       </c>
       <c r="E65" t="n">
-        <v>1.267788187884023</v>
+        <v>1.920921686143497</v>
       </c>
       <c r="F65" t="n">
-        <v>0.3581286951156356</v>
+        <v>1.046079396525905</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.1800915165900857</v>
+        <v>-0.2675313666292633</v>
       </c>
     </row>
     <row r="66">
@@ -23326,22 +23326,22 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.8588727048628964</v>
+        <v>0.8868008881002045</v>
       </c>
       <c r="C66" t="n">
-        <v>2.353684977478471</v>
+        <v>2.553956837203716</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3289957589962325</v>
+        <v>0.8319581607620474</v>
       </c>
       <c r="E66" t="n">
-        <v>1.43673273417659</v>
+        <v>1.928752545041133</v>
       </c>
       <c r="F66" t="n">
-        <v>0.3190184544640394</v>
+        <v>1.007221195730782</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.1987643480502962</v>
+        <v>-0.2904353174160475</v>
       </c>
     </row>
     <row r="67">
@@ -23351,22 +23351,22 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1.165639056912539</v>
+        <v>0.8763491755236954</v>
       </c>
       <c r="C67" t="n">
-        <v>2.394574126944853</v>
+        <v>2.526898003565909</v>
       </c>
       <c r="D67" t="n">
-        <v>0.3535979315851003</v>
+        <v>0.8420851181386251</v>
       </c>
       <c r="E67" t="n">
-        <v>1.628275014367995</v>
+        <v>1.936436502874558</v>
       </c>
       <c r="F67" t="n">
-        <v>0.3271358052334216</v>
+        <v>0.9686425092683384</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.1873771235032782</v>
+        <v>-0.2824532805714517</v>
       </c>
     </row>
     <row r="68">
@@ -23376,22 +23376,22 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1.311397882815066</v>
+        <v>0.8643055212543014</v>
       </c>
       <c r="C68" t="n">
-        <v>2.628302951774266</v>
+        <v>2.500005459659412</v>
       </c>
       <c r="D68" t="n">
-        <v>0.4071152691511578</v>
+        <v>0.8510057630068424</v>
       </c>
       <c r="E68" t="n">
-        <v>1.741547851355838</v>
+        <v>1.942930542880182</v>
       </c>
       <c r="F68" t="n">
-        <v>0.3655782465668654</v>
+        <v>0.9302598265626104</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.1705994448622739</v>
+        <v>-0.2662606757140052</v>
       </c>
     </row>
     <row r="69">
@@ -23401,22 +23401,22 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1.285319888033291</v>
+        <v>0.850451699906472</v>
       </c>
       <c r="C69" t="n">
-        <v>2.853001924070774</v>
+        <v>2.473216573426881</v>
       </c>
       <c r="D69" t="n">
-        <v>0.5031173415017646</v>
+        <v>0.8576876664704223</v>
       </c>
       <c r="E69" t="n">
-        <v>1.735859665333074</v>
+        <v>1.947275983606285</v>
       </c>
       <c r="F69" t="n">
-        <v>0.4329626603129211</v>
+        <v>0.8920012560136737</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.1629844430153309</v>
+        <v>-0.2590423461379746</v>
       </c>
     </row>
     <row r="70">
@@ -23426,22 +23426,22 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1.348236847014186</v>
+        <v>0.8359565992952596</v>
       </c>
       <c r="C70" t="n">
-        <v>3.12057877752729</v>
+        <v>2.446487231356413</v>
       </c>
       <c r="D70" t="n">
-        <v>0.5253129181982156</v>
+        <v>0.8641088383378319</v>
       </c>
       <c r="E70" t="n">
-        <v>1.795707775269378</v>
+        <v>1.951275455913402</v>
       </c>
       <c r="F70" t="n">
-        <v>0.4779216201853073</v>
+        <v>0.8538119083071054</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.1920719108312222</v>
+        <v>-0.2772976681194595</v>
       </c>
     </row>
     <row r="71">
@@ -23451,22 +23451,22 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1.5190639997436</v>
+        <v>0.8204113626356415</v>
       </c>
       <c r="C71" t="n">
-        <v>3.250470808768119</v>
+        <v>2.419760328161972</v>
       </c>
       <c r="D71" t="n">
-        <v>0.4445288177170068</v>
+        <v>0.8700326103419664</v>
       </c>
       <c r="E71" t="n">
-        <v>1.905507355696702</v>
+        <v>1.954782533335675</v>
       </c>
       <c r="F71" t="n">
-        <v>0.4645834298300348</v>
+        <v>0.8156392443923485</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.2065311570160352</v>
+        <v>-0.2904872767671687</v>
       </c>
     </row>
     <row r="72">
@@ -23476,22 +23476,22 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1.423175718877227</v>
+        <v>0.8019444471629189</v>
       </c>
       <c r="C72" t="n">
-        <v>3.121628351682665</v>
+        <v>2.392993463266256</v>
       </c>
       <c r="D72" t="n">
-        <v>0.3462707340467334</v>
+        <v>0.8717908877991851</v>
       </c>
       <c r="E72" t="n">
-        <v>1.74761693013071</v>
+        <v>1.954425301960221</v>
       </c>
       <c r="F72" t="n">
-        <v>0.4437896148745494</v>
+        <v>0.7774348330462768</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.2092200127832411</v>
+        <v>-0.3052203889401756</v>
       </c>
     </row>
     <row r="73">
@@ -23501,22 +23501,22 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1.196754747240096</v>
+        <v>0.7816150955146752</v>
       </c>
       <c r="C73" t="n">
-        <v>2.90185320953148</v>
+        <v>2.366179348595636</v>
       </c>
       <c r="D73" t="n">
-        <v>0.3767693218400065</v>
+        <v>0.8716116207919473</v>
       </c>
       <c r="E73" t="n">
-        <v>1.606990534448301</v>
+        <v>1.9521397526215</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4786889680975343</v>
+        <v>0.7391789704995623</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.2333368200673695</v>
+        <v>-0.3187898088611359</v>
       </c>
     </row>
     <row r="74">
@@ -23526,22 +23526,22 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1.168414242367988</v>
+        <v>0.7611325705320695</v>
       </c>
       <c r="C74" t="n">
-        <v>2.901484131366465</v>
+        <v>2.339330146890782</v>
       </c>
       <c r="D74" t="n">
-        <v>0.4111531679483428</v>
+        <v>0.8718453578560919</v>
       </c>
       <c r="E74" t="n">
-        <v>1.631964044993948</v>
+        <v>1.950145906969451</v>
       </c>
       <c r="F74" t="n">
-        <v>0.5277469196059267</v>
+        <v>0.7008662610876976</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.2526374972072517</v>
+        <v>-0.3268274649798284</v>
       </c>
     </row>
     <row r="75">
@@ -23551,22 +23551,22 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1.372078376304534</v>
+        <v>0.7405066622429768</v>
       </c>
       <c r="C75" t="n">
-        <v>3.103601656273432</v>
+        <v>2.312435141077637</v>
       </c>
       <c r="D75" t="n">
-        <v>0.4011861834823821</v>
+        <v>0.8719415570445133</v>
       </c>
       <c r="E75" t="n">
-        <v>1.745148127605979</v>
+        <v>1.948003641583313</v>
       </c>
       <c r="F75" t="n">
-        <v>0.5685186402573966</v>
+        <v>0.6624899826471714</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.261419086898071</v>
+        <v>-0.3354349178206539</v>
       </c>
     </row>
     <row r="76">
@@ -23576,22 +23576,22 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1.705639500269433</v>
+        <v>0.7186864491172442</v>
       </c>
       <c r="C76" t="n">
-        <v>3.438855543644289</v>
+        <v>2.285479870861552</v>
       </c>
       <c r="D76" t="n">
-        <v>0.5161795191278896</v>
+        <v>0.871312767709072</v>
       </c>
       <c r="E76" t="n">
-        <v>2.02420469313093</v>
+        <v>1.945155791077877</v>
       </c>
       <c r="F76" t="n">
-        <v>0.6240188372835989</v>
+        <v>0.6240456619897914</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.2331186500513092</v>
+        <v>-0.3068135125488442</v>
       </c>
     </row>
     <row r="77">
@@ -23601,22 +23601,22 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1.859579271147712</v>
+        <v>0.6937758384032779</v>
       </c>
       <c r="C77" t="n">
-        <v>3.536130328186476</v>
+        <v>2.258433751952458</v>
       </c>
       <c r="D77" t="n">
-        <v>0.5612162956878335</v>
+        <v>0.8660955574506124</v>
       </c>
       <c r="E77" t="n">
-        <v>2.079517906545173</v>
+        <v>1.938058578325617</v>
       </c>
       <c r="F77" t="n">
-        <v>0.6579635118591681</v>
+        <v>0.5855350492085163</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.2138477746769743</v>
+        <v>-0.2983466549540088</v>
       </c>
     </row>
     <row r="78">
@@ -23626,22 +23626,22 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1.840000448462682</v>
+        <v>0.6655836815535841</v>
       </c>
       <c r="C78" t="n">
-        <v>3.535153842946401</v>
+        <v>2.231318787090734</v>
       </c>
       <c r="D78" t="n">
-        <v>0.5206687824131302</v>
+        <v>0.8570114819359853</v>
       </c>
       <c r="E78" t="n">
-        <v>2.04749564561937</v>
+        <v>1.927297693149794</v>
       </c>
       <c r="F78" t="n">
-        <v>0.6573866388761477</v>
+        <v>0.5469888528133874</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.2242727078858418</v>
+        <v>-0.3027193704212164</v>
       </c>
     </row>
     <row r="79">
@@ -23651,22 +23651,22 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1.645558205908295</v>
+        <v>0.634238346580986</v>
       </c>
       <c r="C79" t="n">
-        <v>3.382521702800955</v>
+        <v>2.204159680354117</v>
       </c>
       <c r="D79" t="n">
-        <v>0.5588058988497686</v>
+        <v>0.8429401863558841</v>
       </c>
       <c r="E79" t="n">
-        <v>1.883774723684609</v>
+        <v>1.91189216042763</v>
       </c>
       <c r="F79" t="n">
-        <v>0.6646453472435129</v>
+        <v>0.5084599403578192</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.2259215170093393</v>
+        <v>-0.3064717766559194</v>
       </c>
     </row>
     <row r="80">
@@ -23676,22 +23676,22 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1.513421722095495</v>
+        <v>0.6011938479921186</v>
       </c>
       <c r="C80" t="n">
-        <v>3.20441941147292</v>
+        <v>2.177010573679491</v>
       </c>
       <c r="D80" t="n">
-        <v>0.5152489862983386</v>
+        <v>0.8267806939424194</v>
       </c>
       <c r="E80" t="n">
-        <v>1.793908028308753</v>
+        <v>1.894473229638544</v>
       </c>
       <c r="F80" t="n">
-        <v>0.6296458852745392</v>
+        <v>0.4700304861089646</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.2337361636118802</v>
+        <v>-0.3002953909297009</v>
       </c>
     </row>
     <row r="81">
@@ -23701,22 +23701,22 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1.367318670229686</v>
+        <v>0.5662790351154308</v>
       </c>
       <c r="C81" t="n">
-        <v>2.97460589334654</v>
+        <v>2.149927934141529</v>
       </c>
       <c r="D81" t="n">
-        <v>0.4698637403457404</v>
+        <v>0.8076176151591206</v>
       </c>
       <c r="E81" t="n">
-        <v>1.674472770298321</v>
+        <v>1.874297254552424</v>
       </c>
       <c r="F81" t="n">
-        <v>0.5989319175142696</v>
+        <v>0.4317914143236225</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.2395579644610205</v>
+        <v>-0.3080781381970434</v>
       </c>
     </row>
     <row r="82">
@@ -23726,22 +23726,22 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1.068478410895656</v>
+        <v>0.5294255131530083</v>
       </c>
       <c r="C82" t="n">
-        <v>2.790768159302371</v>
+        <v>2.122988288030277</v>
       </c>
       <c r="D82" t="n">
-        <v>0.4517893805163601</v>
+        <v>0.7847303026582537</v>
       </c>
       <c r="E82" t="n">
-        <v>1.424976230899259</v>
+        <v>1.850673229167168</v>
       </c>
       <c r="F82" t="n">
-        <v>0.5869575565292856</v>
+        <v>0.3938489640622893</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.2561065669129717</v>
+        <v>-0.3253575800122201</v>
       </c>
     </row>
     <row r="83">
@@ -23751,22 +23751,22 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7764948158858709</v>
+        <v>0.4919392486905438</v>
       </c>
       <c r="C83" t="n">
-        <v>2.531834509173484</v>
+        <v>2.096260446297067</v>
       </c>
       <c r="D83" t="n">
-        <v>0.4166209969133813</v>
+        <v>0.7609215030860428</v>
       </c>
       <c r="E83" t="n">
-        <v>1.250794808364261</v>
+        <v>1.826156542946931</v>
       </c>
       <c r="F83" t="n">
-        <v>0.5689192267910607</v>
+        <v>0.3563288927277394</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.2578784631671409</v>
+        <v>-0.3141954534216449</v>
       </c>
     </row>
     <row r="84">
@@ -23776,22 +23776,22 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.3896190920145677</v>
+        <v>0.4541244467628531</v>
       </c>
       <c r="C84" t="n">
-        <v>1.964973011619431</v>
+        <v>2.069814594904052</v>
       </c>
       <c r="D84" t="n">
-        <v>0.5477738637149732</v>
+        <v>0.7349399443823348</v>
       </c>
       <c r="E84" t="n">
-        <v>1.020781892023057</v>
+        <v>1.799684339363429</v>
       </c>
       <c r="F84" t="n">
-        <v>0.6099679265782565</v>
+        <v>0.3193576077007216</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.2399379001051332</v>
+        <v>-0.2992270930642089</v>
       </c>
     </row>
     <row r="85">
@@ -23801,22 +23801,22 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.070845951345789</v>
+        <v>0.4176288686809861</v>
       </c>
       <c r="C85" t="n">
-        <v>1.683617076343229</v>
+        <v>2.043789449957827</v>
       </c>
       <c r="D85" t="n">
-        <v>0.5189760163118817</v>
+        <v>0.7097523348154091</v>
       </c>
       <c r="E85" t="n">
-        <v>0.8286636105232096</v>
+        <v>1.773941201732855</v>
       </c>
       <c r="F85" t="n">
-        <v>0.6180514771625852</v>
+        <v>0.2830707755575239</v>
       </c>
       <c r="G85" t="n">
-        <v>-0.2564091885360789</v>
+        <v>-0.3010930812770216</v>
       </c>
     </row>
     <row r="86">
@@ -23826,22 +23826,22 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-0.1822525615785752</v>
+        <v>0.3829992750310373</v>
       </c>
       <c r="C86" t="n">
-        <v>1.441110941078366</v>
+        <v>2.018258228766336</v>
       </c>
       <c r="D86" t="n">
-        <v>0.5944026390699901</v>
+        <v>0.6853719589446214</v>
       </c>
       <c r="E86" t="n">
-        <v>0.7062377541041878</v>
+        <v>1.749040714524311</v>
       </c>
       <c r="F86" t="n">
-        <v>0.6436940847293195</v>
+        <v>0.247591312455409</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.2308087128670102</v>
+        <v>-0.274064819502308</v>
       </c>
     </row>
     <row r="87">
@@ -23851,22 +23851,22 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-0.3701703245524017</v>
+        <v>0.3509532185293962</v>
       </c>
       <c r="C87" t="n">
-        <v>1.014035510384044</v>
+        <v>1.993290977239602</v>
       </c>
       <c r="D87" t="n">
-        <v>0.6808476111670355</v>
+        <v>0.6622016817500258</v>
       </c>
       <c r="E87" t="n">
-        <v>0.6018886164354966</v>
+        <v>1.725341341681466</v>
       </c>
       <c r="F87" t="n">
-        <v>0.6818068367232358</v>
+        <v>0.2130305490662887</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.2205605238770978</v>
+        <v>-0.2596112291123124</v>
       </c>
     </row>
     <row r="88">
@@ -23876,22 +23876,22 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-0.3375856701446684</v>
+        <v>0.3223437388327481</v>
       </c>
       <c r="C88" t="n">
-        <v>0.6638358773238333</v>
+        <v>1.968989740303734</v>
       </c>
       <c r="D88" t="n">
-        <v>0.7550130206186815</v>
+        <v>0.6426513469683091</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7280780039781521</v>
+        <v>1.705070943949424</v>
       </c>
       <c r="F88" t="n">
-        <v>0.6983078258822331</v>
+        <v>0.1794845305633412</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.185108613769622</v>
+        <v>-0.2124503375428581</v>
       </c>
     </row>
     <row r="89">
@@ -23901,22 +23901,22 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.3876462389606234</v>
+        <v>0.2958496088273648</v>
       </c>
       <c r="C89" t="n">
-        <v>0.7037338075042538</v>
+        <v>1.945448009515209</v>
       </c>
       <c r="D89" t="n">
-        <v>0.886379031573888</v>
+        <v>0.6228858430468041</v>
       </c>
       <c r="E89" t="n">
-        <v>0.723598487517048</v>
+        <v>1.68478833730026</v>
       </c>
       <c r="F89" t="n">
-        <v>0.7348146647238714</v>
+        <v>0.1470178232631284</v>
       </c>
       <c r="G89" t="n">
-        <v>-0.1680402864427011</v>
+        <v>-0.2080537494155159</v>
       </c>
     </row>
     <row r="90">
@@ -23926,22 +23926,22 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-0.3862051876201091</v>
+        <v>0.2721655383630528</v>
       </c>
       <c r="C90" t="n">
-        <v>0.8157514841612036</v>
+        <v>1.922692720667797</v>
       </c>
       <c r="D90" t="n">
-        <v>0.7033463235629419</v>
+        <v>0.6052171229966739</v>
       </c>
       <c r="E90" t="n">
-        <v>0.6839471469715783</v>
+        <v>1.666513196369384</v>
       </c>
       <c r="F90" t="n">
-        <v>0.6666621771861923</v>
+        <v>0.1156884242310992</v>
       </c>
       <c r="G90" t="n">
-        <v>-0.2054662549744759</v>
+        <v>-0.2341678542856203</v>
       </c>
     </row>
     <row r="91">
@@ -23951,22 +23951,22 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-0.3140679782819755</v>
+        <v>0.2509984620624716</v>
       </c>
       <c r="C91" t="n">
-        <v>0.8302924067433082</v>
+        <v>1.900746230776112</v>
       </c>
       <c r="D91" t="n">
-        <v>0.6122007260529101</v>
+        <v>0.5892372860921888</v>
       </c>
       <c r="E91" t="n">
-        <v>0.7222587744335113</v>
+        <v>1.649945374614345</v>
       </c>
       <c r="F91" t="n">
-        <v>0.6132846791057665</v>
+        <v>0.08553044185154959</v>
       </c>
       <c r="G91" t="n">
-        <v>-0.2275936141098958</v>
+        <v>-0.259115140048714</v>
       </c>
     </row>
     <row r="92">
@@ -23976,22 +23976,22 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-0.2955964916370637</v>
+        <v>0.2315180956132945</v>
       </c>
       <c r="C92" t="n">
-        <v>0.7129799824434583</v>
+        <v>1.879631691819442</v>
       </c>
       <c r="D92" t="n">
-        <v>0.4749655385240677</v>
+        <v>0.5740429646536356</v>
       </c>
       <c r="E92" t="n">
-        <v>0.6852643326267447</v>
+        <v>1.634204408314548</v>
       </c>
       <c r="F92" t="n">
-        <v>0.581744454925477</v>
+        <v>0.0565608511364819</v>
       </c>
       <c r="G92" t="n">
-        <v>-0.2892581881512103</v>
+        <v>-0.3243133775369717</v>
       </c>
     </row>
     <row r="93">
@@ -24001,22 +24001,22 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-0.3414526335875063</v>
+        <v>0.2134223622445272</v>
       </c>
       <c r="C93" t="n">
-        <v>0.7232480684296008</v>
+        <v>1.859385017716077</v>
       </c>
       <c r="D93" t="n">
-        <v>0.4216852492487818</v>
+        <v>0.5599692141646031</v>
       </c>
       <c r="E93" t="n">
-        <v>0.6602620915134558</v>
+        <v>1.61955654364807</v>
       </c>
       <c r="F93" t="n">
-        <v>0.5650788219234245</v>
+        <v>0.0287867835903835</v>
       </c>
       <c r="G93" t="n">
-        <v>-0.3046198282522886</v>
+        <v>-0.3384069915783122</v>
       </c>
     </row>
     <row r="94">
@@ -24026,22 +24026,22 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-0.5065764532808632</v>
+        <v>0.1965746565665989</v>
       </c>
       <c r="C94" t="n">
-        <v>0.6377104287724827</v>
+        <v>1.839994470754758</v>
       </c>
       <c r="D94" t="n">
-        <v>0.4288550685036682</v>
+        <v>0.5464091595196567</v>
       </c>
       <c r="E94" t="n">
-        <v>0.5561106278414132</v>
+        <v>1.605437647162368</v>
       </c>
       <c r="F94" t="n">
-        <v>0.5842155245173982</v>
+        <v>0.0022054262001563</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.3170248975455434</v>
+        <v>-0.3523101001541839</v>
       </c>
     </row>
     <row r="95">
@@ -24051,22 +24051,22 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-0.6618815311474084</v>
+        <v>0.1818629089557981</v>
       </c>
       <c r="C95" t="n">
-        <v>0.4564522784397875</v>
+        <v>1.821454670751212</v>
       </c>
       <c r="D95" t="n">
-        <v>0.4110387750337181</v>
+        <v>0.5349625835933169</v>
       </c>
       <c r="E95" t="n">
-        <v>0.4700724606375828</v>
+        <v>1.593290044320621</v>
       </c>
       <c r="F95" t="n">
-        <v>0.6157952909032505</v>
+        <v>-0.023191212954922</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.3520033204804203</v>
+        <v>-0.3800513086431158</v>
       </c>
     </row>
     <row r="96">
@@ -24076,22 +24076,22 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-0.7718600165379619</v>
+        <v>0.1695484361087764</v>
       </c>
       <c r="C96" t="n">
-        <v>0.3481071014533794</v>
+        <v>1.803762257471688</v>
       </c>
       <c r="D96" t="n">
-        <v>0.4890779502963423</v>
+        <v>0.5262218253999107</v>
       </c>
       <c r="E96" t="n">
-        <v>0.4782980322768925</v>
+        <v>1.583697693938003</v>
       </c>
       <c r="F96" t="n">
-        <v>0.6512112644450553</v>
+        <v>-0.0474267905214573</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.3415920394063018</v>
+        <v>-0.3664326152904439</v>
       </c>
     </row>
     <row r="97">
@@ -24101,22 +24101,22 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-0.9583801651684104</v>
+        <v>0.1595201872605036</v>
       </c>
       <c r="C97" t="n">
-        <v>0.3922205563642018</v>
+        <v>1.786892152522548</v>
       </c>
       <c r="D97" t="n">
-        <v>0.5094822767566312</v>
+        <v>0.5187452064313431</v>
       </c>
       <c r="E97" t="n">
-        <v>0.3383077672559774</v>
+        <v>1.575348459328334</v>
       </c>
       <c r="F97" t="n">
-        <v>0.6590547096751148</v>
+        <v>-0.07054334242264999</v>
       </c>
       <c r="G97" t="n">
-        <v>-0.3179009437023764</v>
+        <v>-0.3461018888878877</v>
       </c>
     </row>
     <row r="98">
@@ -24126,22 +24126,22 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-0.940612423745792</v>
+        <v>0.1533525037156193</v>
       </c>
       <c r="C98" t="n">
-        <v>0.5970435571655084</v>
+        <v>1.770795541730098</v>
       </c>
       <c r="D98" t="n">
-        <v>0.4618875734726878</v>
+        <v>0.5160534429764354</v>
       </c>
       <c r="E98" t="n">
-        <v>0.379902782399671</v>
+        <v>1.571430455640488</v>
       </c>
       <c r="F98" t="n">
-        <v>0.6729229311153414</v>
+        <v>-0.09259259876109729</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.3614704845652974</v>
+        <v>-0.3753896526303667</v>
       </c>
     </row>
     <row r="99">
@@ -24151,22 +24151,22 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-0.6714275159031384</v>
+        <v>0.1508279978323625</v>
       </c>
       <c r="C99" t="n">
-        <v>1.068880901339811</v>
+        <v>1.755411573461783</v>
       </c>
       <c r="D99" t="n">
-        <v>0.5516009632715839</v>
+        <v>0.5173658162644648</v>
       </c>
       <c r="E99" t="n">
-        <v>0.6033553563858637</v>
+        <v>1.57131398342894</v>
       </c>
       <c r="F99" t="n">
-        <v>0.7053118382195402</v>
+        <v>-0.1136585682760964</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.3291893072482366</v>
+        <v>-0.3457688865216968</v>
       </c>
     </row>
     <row r="100">
@@ -24176,22 +24176,22 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-0.2304883227397827</v>
+        <v>0.1509987415674969</v>
       </c>
       <c r="C100" t="n">
-        <v>1.564191444425076</v>
+        <v>1.740636533913782</v>
       </c>
       <c r="D100" t="n">
-        <v>0.6857550884746896</v>
+        <v>0.5216868677838118</v>
       </c>
       <c r="E100" t="n">
-        <v>0.9454520110704884</v>
+        <v>1.57404003391587</v>
       </c>
       <c r="F100" t="n">
-        <v>0.744016373319195</v>
+        <v>-0.1338498170700892</v>
       </c>
       <c r="G100" t="n">
-        <v>-0.2898709823178006</v>
+        <v>-0.3078913637560609</v>
       </c>
     </row>
     <row r="101">
@@ -24201,22 +24201,22 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.2566198376725919</v>
+        <v>0.1522095749569363</v>
       </c>
       <c r="C101" t="n">
-        <v>2.059779724615975</v>
+        <v>1.726373903121119</v>
       </c>
       <c r="D101" t="n">
-        <v>0.7505873984194931</v>
+        <v>0.5274154041660255</v>
       </c>
       <c r="E101" t="n">
-        <v>1.320784449799745</v>
+        <v>1.578125946352758</v>
       </c>
       <c r="F101" t="n">
-        <v>0.7484311544652439</v>
+        <v>-0.1532934837136462</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.2563522825981973</v>
+        <v>-0.2779236805304492</v>
       </c>
     </row>
     <row r="102">
@@ -24226,22 +24226,22 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5212544084846864</v>
+        <v>0.1523825674004397</v>
       </c>
       <c r="C102" t="n">
-        <v>2.461805524120424</v>
+        <v>1.712520663437433</v>
       </c>
       <c r="D102" t="n">
-        <v>0.675032016728377</v>
+        <v>0.5303444052935475</v>
       </c>
       <c r="E102" t="n">
-        <v>1.389831320614408</v>
+        <v>1.579692220085271</v>
       </c>
       <c r="F102" t="n">
-        <v>0.7148270108680108</v>
+        <v>-0.172126035152736</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.2668703392716078</v>
+        <v>-0.3026816781965653</v>
       </c>
     </row>
     <row r="103">
@@ -24251,22 +24251,22 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.8655631248173177</v>
+        <v>0.1521627219501355</v>
       </c>
       <c r="C103" t="n">
-        <v>2.872972378926065</v>
+        <v>1.698992984167706</v>
       </c>
       <c r="D103" t="n">
-        <v>0.5556640132409214</v>
+        <v>0.5332814940181736</v>
       </c>
       <c r="E103" t="n">
-        <v>1.57221961326766</v>
+        <v>1.581203398428159</v>
       </c>
       <c r="F103" t="n">
-        <v>0.6529901368864081</v>
+        <v>-0.1904667739543817</v>
       </c>
       <c r="G103" t="n">
-        <v>-0.2836836913576286</v>
+        <v>-0.3080328163863087</v>
       </c>
     </row>
     <row r="104">
@@ -24276,22 +24276,22 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1.256004033072247</v>
+        <v>0.1502243332951041</v>
       </c>
       <c r="C104" t="n">
-        <v>3.105341815730416</v>
+        <v>1.685694822920873</v>
       </c>
       <c r="D104" t="n">
-        <v>0.6476027016226132</v>
+        <v>0.5348236821959702</v>
       </c>
       <c r="E104" t="n">
-        <v>1.908139637360346</v>
+        <v>1.581445220706621</v>
       </c>
       <c r="F104" t="n">
-        <v>0.6580925984425954</v>
+        <v>-0.2084355424202973</v>
       </c>
       <c r="G104" t="n">
-        <v>-0.2823832056477015</v>
+        <v>-0.3123872508182084</v>
       </c>
     </row>
     <row r="105">
@@ -24301,22 +24301,22 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1.311337739061828</v>
+        <v>0.144304612941166</v>
       </c>
       <c r="C105" t="n">
-        <v>3.083166369650499</v>
+        <v>1.672554553719479</v>
       </c>
       <c r="D105" t="n">
-        <v>0.4126789647593198</v>
+        <v>0.5299806493929085</v>
       </c>
       <c r="E105" t="n">
-        <v>1.740349530165146</v>
+        <v>1.575798562999583</v>
       </c>
       <c r="F105" t="n">
-        <v>0.6051933642789517</v>
+        <v>-0.226141095467032</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.3268786973618676</v>
+        <v>-0.3736806490680794</v>
       </c>
     </row>
     <row r="106">
@@ -24326,22 +24326,22 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1.292095836285148</v>
+        <v>0.1353303871076614</v>
       </c>
       <c r="C106" t="n">
-        <v>3.005945828236816</v>
+        <v>1.659540521309415</v>
       </c>
       <c r="D106" t="n">
-        <v>0.4493785414301728</v>
+        <v>0.522905150344986</v>
       </c>
       <c r="E106" t="n">
-        <v>1.794136004442662</v>
+        <v>1.567950279835559</v>
       </c>
       <c r="F106" t="n">
-        <v>0.6068054520960557</v>
+        <v>-0.2436513454707227</v>
       </c>
       <c r="G106" t="n">
-        <v>-0.3507027584249277</v>
+        <v>-0.3820014168852363</v>
       </c>
     </row>
     <row r="107">
@@ -24351,22 +24351,22 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1.111318553270865</v>
+        <v>0.1230407900591443</v>
       </c>
       <c r="C107" t="n">
-        <v>2.841785223715632</v>
+        <v>1.646621291735614</v>
       </c>
       <c r="D107" t="n">
-        <v>0.4741405180872304</v>
+        <v>0.5105155274312994</v>
       </c>
       <c r="E107" t="n">
-        <v>1.610219151344405</v>
+        <v>1.555188299614155</v>
       </c>
       <c r="F107" t="n">
-        <v>0.6067300051239118</v>
+        <v>-0.26101839406668</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.321564233396406</v>
+        <v>-0.3624750248847863</v>
       </c>
     </row>
     <row r="108">
@@ -24376,22 +24376,22 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.9935222405152032</v>
+        <v>0.108943337845383</v>
       </c>
       <c r="C108" t="n">
-        <v>2.754163931855459</v>
+        <v>1.633794478184509</v>
       </c>
       <c r="D108" t="n">
-        <v>0.4950674423016784</v>
+        <v>0.4966451248557284</v>
       </c>
       <c r="E108" t="n">
-        <v>1.579104706938863</v>
+        <v>1.540950431892552</v>
       </c>
       <c r="F108" t="n">
-        <v>0.6286448535870337</v>
+        <v>-0.2782596267447834</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.3403610801867079</v>
+        <v>-0.364583215048661</v>
       </c>
     </row>
     <row r="109">
@@ -24401,22 +24401,22 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.902307052600008</v>
+        <v>0.0931059809507683</v>
       </c>
       <c r="C109" t="n">
-        <v>2.698189782939857</v>
+        <v>1.621053493938226</v>
       </c>
       <c r="D109" t="n">
-        <v>0.6844276917235519</v>
+        <v>0.4795012731717012</v>
       </c>
       <c r="E109" t="n">
-        <v>1.565814029031452</v>
+        <v>1.523723002796951</v>
       </c>
       <c r="F109" t="n">
-        <v>0.6788227207769174</v>
+        <v>-0.2953844839204713</v>
       </c>
       <c r="G109" t="n">
-        <v>-0.3058118127396695</v>
+        <v>-0.3352873485333456</v>
       </c>
     </row>
     <row r="110">
@@ -24426,22 +24426,22 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.9080773008204854</v>
+        <v>0.0761749109325509</v>
       </c>
       <c r="C110" t="n">
-        <v>2.70806103709835</v>
+        <v>1.608407330539844</v>
       </c>
       <c r="D110" t="n">
-        <v>0.5637541739890847</v>
+        <v>0.4605030903948943</v>
       </c>
       <c r="E110" t="n">
-        <v>1.51893393510663</v>
+        <v>1.504768291997662</v>
       </c>
       <c r="F110" t="n">
-        <v>0.6377342247288067</v>
+        <v>-0.3123830381089751</v>
       </c>
       <c r="G110" t="n">
-        <v>-0.3248988503850159</v>
+        <v>-0.3458125841009503</v>
       </c>
     </row>
     <row r="111">
@@ -24451,22 +24451,22 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.8675281117009312</v>
+        <v>0.0572988346669132</v>
       </c>
       <c r="C111" t="n">
-        <v>2.590289637646465</v>
+        <v>1.595858616822451</v>
       </c>
       <c r="D111" t="n">
-        <v>0.4982806974621059</v>
+        <v>0.4386810632273672</v>
       </c>
       <c r="E111" t="n">
-        <v>1.487075042330851</v>
+        <v>1.483269763373663</v>
       </c>
       <c r="F111" t="n">
-        <v>0.6122242103055485</v>
+        <v>-0.3292392583197378</v>
       </c>
       <c r="G111" t="n">
-        <v>-0.3470347753852084</v>
+        <v>-0.3719606210236063</v>
       </c>
     </row>
     <row r="112">
@@ -24476,22 +24476,22 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5547172512683112</v>
+        <v>0.0359847875665992</v>
       </c>
       <c r="C112" t="n">
-        <v>2.313583563241426</v>
+        <v>1.58343551956489</v>
       </c>
       <c r="D112" t="n">
-        <v>0.560642317866563</v>
+        <v>0.4113887717105182</v>
       </c>
       <c r="E112" t="n">
-        <v>1.213076991519383</v>
+        <v>1.456764462825989</v>
       </c>
       <c r="F112" t="n">
-        <v>0.6098211754220506</v>
+        <v>-0.3459229752222283</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.321193572377264</v>
+        <v>-0.3548089926891826</v>
       </c>
     </row>
     <row r="113">
@@ -24501,22 +24501,22 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.4524672503062903</v>
+        <v>0.0149236387861892</v>
       </c>
       <c r="C113" t="n">
-        <v>1.840870310635009</v>
+        <v>1.571180361120048</v>
       </c>
       <c r="D113" t="n">
-        <v>0.4579686552117789</v>
+        <v>0.3851507507563267</v>
       </c>
       <c r="E113" t="n">
-        <v>1.20622214219466</v>
+        <v>1.431172228785673</v>
       </c>
       <c r="F113" t="n">
-        <v>0.5986491891877251</v>
+        <v>-0.3623732624056648</v>
       </c>
       <c r="G113" t="n">
-        <v>-0.3985982878787969</v>
+        <v>-0.4059971002398472</v>
       </c>
     </row>
     <row r="114">
@@ -24526,22 +24526,22 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.2511455544019099</v>
+        <v>-0.0073362507312411</v>
       </c>
       <c r="C114" t="n">
-        <v>1.330659365221337</v>
+        <v>1.55916151755453</v>
       </c>
       <c r="D114" t="n">
-        <v>0.4675864999375463</v>
+        <v>0.3554559387221738</v>
       </c>
       <c r="E114" t="n">
-        <v>1.06521323628179</v>
+        <v>1.402558181075743</v>
       </c>
       <c r="F114" t="n">
-        <v>0.5978633578521436</v>
+        <v>-0.3785432330427212</v>
       </c>
       <c r="G114" t="n">
-        <v>-0.3910083892775337</v>
+        <v>-0.416313547193515</v>
       </c>
     </row>
     <row r="115">
@@ -24551,22 +24551,22 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-0.2025650366876594</v>
+        <v>-0.0306533174780774</v>
       </c>
       <c r="C115" t="n">
-        <v>0.9829558910492396</v>
+        <v>1.547453922129047</v>
       </c>
       <c r="D115" t="n">
-        <v>0.2818374009112626</v>
+        <v>0.3230133012497411</v>
       </c>
       <c r="E115" t="n">
-        <v>0.6939556050497501</v>
+        <v>1.371431060676987</v>
       </c>
       <c r="F115" t="n">
-        <v>0.5700864810404364</v>
+        <v>-0.3943684487019854</v>
       </c>
       <c r="G115" t="n">
-        <v>-0.4722229675566611</v>
+        <v>-0.4937575076396659</v>
       </c>
     </row>
     <row r="116">
@@ -24576,22 +24576,22 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-0.5906686319094518</v>
+        <v>-0.0527728621050995</v>
       </c>
       <c r="C116" t="n">
-        <v>0.866542523987989</v>
+        <v>1.536116744767253</v>
       </c>
       <c r="D116" t="n">
-        <v>0.211175739901804</v>
+        <v>0.2908492925889625</v>
       </c>
       <c r="E116" t="n">
-        <v>0.4283165806164617</v>
+        <v>1.340604572520175</v>
       </c>
       <c r="F116" t="n">
-        <v>0.5562615645845994</v>
+        <v>-0.4097739368045959</v>
       </c>
       <c r="G116" t="n">
-        <v>-0.5297343222566291</v>
+        <v>-0.5411943126202933</v>
       </c>
     </row>
     <row r="117">
@@ -24601,22 +24601,22 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-0.6841613650548886</v>
+        <v>-0.07226076540107</v>
       </c>
       <c r="C117" t="n">
-        <v>0.8693147101724489</v>
+        <v>1.525184720345438</v>
       </c>
       <c r="D117" t="n">
-        <v>0.199408037111071</v>
+        <v>0.2618866574740863</v>
       </c>
       <c r="E117" t="n">
-        <v>0.4498683623000877</v>
+        <v>1.31281280520297</v>
       </c>
       <c r="F117" t="n">
-        <v>0.5348116566376583</v>
+        <v>-0.4246916796184321</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.5642235040889628</v>
+        <v>-0.5650866666719585</v>
       </c>
     </row>
     <row r="118">
@@ -24626,22 +24626,22 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-0.7582311597499523</v>
+        <v>-0.0901670874895141</v>
       </c>
       <c r="C118" t="n">
-        <v>0.7110049656858907</v>
+        <v>1.51467119214928</v>
       </c>
       <c r="D118" t="n">
-        <v>0.0618407730310411</v>
+        <v>0.2329692332552912</v>
       </c>
       <c r="E118" t="n">
-        <v>0.3100193590933317</v>
+        <v>1.285232787152362</v>
       </c>
       <c r="F118" t="n">
-        <v>0.4586654949486271</v>
+        <v>-0.4390784307247073</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.5823900210510081</v>
+        <v>-0.5950851329794613</v>
       </c>
     </row>
     <row r="119">
@@ -24651,22 +24651,22 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-0.7676270089354182</v>
+        <v>-0.1061450592019197</v>
       </c>
       <c r="C119" t="n">
-        <v>0.6290801277538643</v>
+        <v>1.504622234354639</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.0127341522900024</v>
+        <v>0.2063217339608396</v>
       </c>
       <c r="E119" t="n">
-        <v>0.3090986688604217</v>
+        <v>1.259805619506975</v>
       </c>
       <c r="F119" t="n">
-        <v>0.3772414975270952</v>
+        <v>-0.4528948835074083</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.6158251086852842</v>
+        <v>-0.6205667343291499</v>
       </c>
     </row>
     <row r="120">
@@ -24676,22 +24676,22 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>-0.7432792371433954</v>
+        <v>-0.1204470849887862</v>
       </c>
       <c r="C120" t="n">
-        <v>0.5909322728302236</v>
+        <v>1.49505561026837</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.2517912629665729</v>
+        <v>0.1806690429580699</v>
       </c>
       <c r="E120" t="n">
-        <v>0.1877003516141512</v>
+        <v>1.235417037875319</v>
       </c>
       <c r="F120" t="n">
-        <v>0.2665039219300933</v>
+        <v>-0.4661189776070095</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.6526052384143846</v>
+        <v>-0.6625576724146596</v>
       </c>
     </row>
     <row r="121">
@@ -24701,22 +24701,22 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-0.7212777585133709</v>
+        <v>-0.1334759770002389</v>
       </c>
       <c r="C121" t="n">
-        <v>0.6805409907368843</v>
+        <v>1.485986859490123</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.1323477899767746</v>
+        <v>0.1574054700933942</v>
       </c>
       <c r="E121" t="n">
-        <v>0.3156341862843708</v>
+        <v>1.213285656752463</v>
       </c>
       <c r="F121" t="n">
-        <v>0.2510664428754574</v>
+        <v>-0.4787366229105553</v>
       </c>
       <c r="G121" t="n">
-        <v>-0.6372145679581129</v>
+        <v>-0.6429004458290986</v>
       </c>
     </row>
     <row r="122">
@@ -24726,22 +24726,22 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-1.016871879140825</v>
+        <v>-0.1463770588422701</v>
       </c>
       <c r="C122" t="n">
-        <v>0.5031707510237697</v>
+        <v>1.477386764752884</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.1747637556590054</v>
+        <v>0.1324669323743705</v>
       </c>
       <c r="E122" t="n">
-        <v>0.0436173695948117</v>
+        <v>1.189715879520908</v>
       </c>
       <c r="F122" t="n">
-        <v>0.2252254450756062</v>
+        <v>-0.4907476806800502</v>
       </c>
       <c r="G122" t="n">
-        <v>-0.6433448219065898</v>
+        <v>-0.6622831314349884</v>
       </c>
     </row>
     <row r="123">
@@ -24751,22 +24751,22 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-1.252034647994602</v>
+        <v>-0.1566734489849262</v>
       </c>
       <c r="C123" t="n">
-        <v>0.4157669682562659</v>
+        <v>1.469276055402131</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.1147861977491128</v>
+        <v>0.1105623574126664</v>
       </c>
       <c r="E123" t="n">
-        <v>-0.0597168934879967</v>
+        <v>1.168933054114914</v>
       </c>
       <c r="F123" t="n">
-        <v>0.1943390257179832</v>
+        <v>-0.5021422120121798</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.6430331372571677</v>
+        <v>-0.6431430050076827</v>
       </c>
     </row>
     <row r="124">
@@ -24776,22 +24776,22 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>-1.110739935811974</v>
+        <v>-0.1628839217917039</v>
       </c>
       <c r="C124" t="n">
-        <v>0.6129330759213969</v>
+        <v>1.461652257400579</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.2284592890442975</v>
+        <v>0.0937416219998468</v>
       </c>
       <c r="E124" t="n">
-        <v>0.040486822271302</v>
+        <v>1.152949862848874</v>
       </c>
       <c r="F124" t="n">
-        <v>0.1222122130558437</v>
+        <v>-0.5129315797242443</v>
       </c>
       <c r="G124" t="n">
-        <v>-0.6704369970776483</v>
+        <v>-0.6624533795396419</v>
       </c>
     </row>
     <row r="125">
@@ -24801,22 +24801,22 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-0.8176908522981241</v>
+        <v>-0.166484164751941</v>
       </c>
       <c r="C125" t="n">
-        <v>0.8710277518173201</v>
+        <v>1.454466154119277</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.1588642148555047</v>
+        <v>0.0793417244652365</v>
       </c>
       <c r="E125" t="n">
-        <v>0.2454135795701074</v>
+        <v>1.139365642697076</v>
       </c>
       <c r="F125" t="n">
-        <v>0.06720340897598261</v>
+        <v>-0.5231616200207898</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.6522184792496588</v>
+        <v>-0.6551198262273258</v>
       </c>
     </row>
     <row r="126">
@@ -24826,22 +24826,22 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>-0.5004074508766094</v>
+        <v>-0.1686945447884287</v>
       </c>
       <c r="C126" t="n">
-        <v>1.045909074938708</v>
+        <v>1.447663596566767</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.2637870471908453</v>
+        <v>0.0668232599259504</v>
       </c>
       <c r="E126" t="n">
-        <v>0.4287617944085228</v>
+        <v>1.127597922158111</v>
       </c>
       <c r="F126" t="n">
-        <v>-0.0753114426362279</v>
+        <v>-0.5328927636416779</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.6728457104473489</v>
+        <v>-0.6764286240618185</v>
       </c>
     </row>
     <row r="127">
@@ -24851,22 +24851,22 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>-0.3725614085723281</v>
+        <v>-0.1711709006759127</v>
       </c>
       <c r="C127" t="n">
-        <v>1.150689678524999</v>
+        <v>1.441197526937789</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.3304706143399357</v>
+        <v>0.0532514232809218</v>
       </c>
       <c r="E127" t="n">
-        <v>0.4495720256733907</v>
+        <v>1.114960687363052</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.3171747450708989</v>
+        <v>-0.5421982713591466</v>
       </c>
       <c r="G127" t="n">
-        <v>-0.6825059121279449</v>
+        <v>-0.6976540536562563</v>
       </c>
     </row>
     <row r="128">
@@ -24876,22 +24876,22 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>-0.3530046707945578</v>
+        <v>-0.1737467318620402</v>
       </c>
       <c r="C128" t="n">
-        <v>1.239020888506757</v>
+        <v>1.435021609362427</v>
       </c>
       <c r="D128" t="n">
-        <v>-1.082042303318896</v>
+        <v>0.0394483908373279</v>
       </c>
       <c r="E128" t="n">
-        <v>0.0821526815766882</v>
+        <v>1.102121261625358</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.8145100845645519</v>
+        <v>-0.5511439088070802</v>
       </c>
       <c r="G128" t="n">
-        <v>-0.7239134166251104</v>
+        <v>-0.7355301490576749</v>
       </c>
     </row>
     <row r="129">
@@ -24901,22 +24901,22 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-0.3651608414546063</v>
+        <v>-0.1764332482203012</v>
       </c>
       <c r="C129" t="n">
-        <v>1.258162628148462</v>
+        <v>1.429079962589927</v>
       </c>
       <c r="D129" t="n">
-        <v>-1.21046875581929</v>
+        <v>0.0278513971216698</v>
       </c>
       <c r="E129" t="n">
-        <v>0.0710566353496782</v>
+        <v>1.091301003121791</v>
       </c>
       <c r="F129" t="n">
-        <v>-1.09647833637695</v>
+        <v>-0.5597939923697799</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.7466540820652268</v>
+        <v>-0.7553460098289526</v>
       </c>
     </row>
     <row r="130">
@@ -24926,22 +24926,22 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>-0.6435382304030721</v>
+        <v>-0.1799698791647463</v>
       </c>
       <c r="C130" t="n">
-        <v>1.17833082886037</v>
+        <v>1.42331828243418</v>
       </c>
       <c r="D130" t="n">
-        <v>-1.285464734115414</v>
+        <v>0.0152059591127313</v>
       </c>
       <c r="E130" t="n">
-        <v>-0.224055493167583</v>
+        <v>1.079491491364381</v>
       </c>
       <c r="F130" t="n">
-        <v>-1.264865252262139</v>
+        <v>-0.5682161406744687</v>
       </c>
       <c r="G130" t="n">
-        <v>-0.7622782215078709</v>
+        <v>-0.7832346723393453</v>
       </c>
     </row>
     <row r="131">
@@ -24951,22 +24951,22 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>-0.7351366285623202</v>
+        <v>-0.1817919127987803</v>
       </c>
       <c r="C131" t="n">
-        <v>1.092379891272614</v>
+        <v>1.417691621680092</v>
       </c>
       <c r="D131" t="n">
-        <v>-1.397242209424447</v>
+        <v>0.0074980482679727</v>
       </c>
       <c r="E131" t="n">
-        <v>-0.2686775286504474</v>
+        <v>1.072082477908853</v>
       </c>
       <c r="F131" t="n">
-        <v>-1.405653084176967</v>
+        <v>-0.576459853192744</v>
       </c>
       <c r="G131" t="n">
-        <v>-0.7813943017694081</v>
+        <v>-0.7791116102632488</v>
       </c>
     </row>
     <row r="132">
@@ -24976,22 +24976,22 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>-0.633220350363717</v>
+        <v>-0.181938763317337</v>
       </c>
       <c r="C132" t="n">
-        <v>1.050629913658965</v>
+        <v>1.412149915278012</v>
       </c>
       <c r="D132" t="n">
-        <v>-1.370965342252978</v>
+        <v>0.0031471742649085</v>
       </c>
       <c r="E132" t="n">
-        <v>-0.1974606999262104</v>
+        <v>1.067784712562389</v>
       </c>
       <c r="F132" t="n">
-        <v>-1.45630139569051</v>
+        <v>-0.5845958420859245</v>
       </c>
       <c r="G132" t="n">
-        <v>-0.8033017978493462</v>
+        <v>-0.808266709584776</v>
       </c>
     </row>
     <row r="133">
@@ -25001,22 +25001,22 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-0.4246918401608368</v>
+        <v>-0.1810818812714323</v>
       </c>
       <c r="C133" t="n">
-        <v>1.423596908170184</v>
+        <v>1.406659983210084</v>
       </c>
       <c r="D133" t="n">
-        <v>-1.513854458736655</v>
+        <v>0.002078219282728</v>
       </c>
       <c r="E133" t="n">
-        <v>-0.1209033681288311</v>
+        <v>1.066457089692669</v>
       </c>
       <c r="F133" t="n">
-        <v>-1.548097893646815</v>
+        <v>-0.5927032151880248</v>
       </c>
       <c r="G133" t="n">
-        <v>-0.7882772087040086</v>
+        <v>-0.7921369109086718</v>
       </c>
     </row>
     <row r="134">
@@ -25026,22 +25026,22 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-0.1920205169914624</v>
+        <v>-0.1798929138632656</v>
       </c>
       <c r="C134" t="n">
-        <v>1.713756811498287</v>
+        <v>1.401114972316795</v>
       </c>
       <c r="D134" t="n">
-        <v>-1.392632909045199</v>
+        <v>0.0026622030305363</v>
       </c>
       <c r="E134" t="n">
-        <v>0.0279155866941912</v>
+        <v>1.066607951086467</v>
       </c>
       <c r="F134" t="n">
-        <v>-1.523023986961335</v>
+        <v>-0.6008702353517623</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.7673969801005951</v>
+        <v>-0.7777895274433365</v>
       </c>
     </row>
     <row r="135">
@@ -25051,22 +25051,22 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.1855804949900363</v>
+        <v>-0.1785260309515572</v>
       </c>
       <c r="C135" t="n">
-        <v>1.965014833051106</v>
+        <v>1.395446808832448</v>
       </c>
       <c r="D135" t="n">
-        <v>-1.297461222705779</v>
+        <v>0.006428886067642</v>
       </c>
       <c r="E135" t="n">
-        <v>0.3727605110697077</v>
+        <v>1.069582663116758</v>
       </c>
       <c r="F135" t="n">
-        <v>-1.468559648737554</v>
+        <v>-0.6091818526825652</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.7755119098572718</v>
+        <v>-0.7780574818781019</v>
       </c>
     </row>
     <row r="136">
@@ -25076,22 +25076,22 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.3089141074930981</v>
+        <v>-0.1795095575252847</v>
       </c>
       <c r="C136" t="n">
-        <v>2.153109121969192</v>
+        <v>1.389587111347781</v>
       </c>
       <c r="D136" t="n">
-        <v>-1.216059264344235</v>
+        <v>0.0076349636323787</v>
       </c>
       <c r="E136" t="n">
-        <v>0.4271901080674181</v>
+        <v>1.070192805210844</v>
       </c>
       <c r="F136" t="n">
-        <v>-1.443278926467231</v>
+        <v>-0.6177322825015913</v>
       </c>
       <c r="G136" t="n">
-        <v>-0.7303874763470177</v>
+        <v>-0.7529092066513182</v>
       </c>
     </row>
     <row r="137">
@@ -25101,22 +25101,22 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.2691269307515926</v>
+        <v>-0.1822904136677743</v>
       </c>
       <c r="C137" t="n">
-        <v>2.422168857468122</v>
+        <v>1.383486284559478</v>
       </c>
       <c r="D137" t="n">
-        <v>-1.329745632059897</v>
+        <v>0.0075269702760323</v>
       </c>
       <c r="E137" t="n">
-        <v>0.313328663239689</v>
+        <v>1.06944449016637</v>
       </c>
       <c r="F137" t="n">
-        <v>-1.46499530774609</v>
+        <v>-0.62658930412424</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.7518815436549969</v>
+        <v>-0.7674639332314797</v>
       </c>
     </row>
     <row r="138">
@@ -25126,22 +25126,22 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5186888217912515</v>
+        <v>-0.1850798136873026</v>
       </c>
       <c r="C138" t="n">
-        <v>2.894209936089234</v>
+        <v>1.377098547005987</v>
       </c>
       <c r="D138" t="n">
-        <v>-1.268735644703536</v>
+        <v>0.0091927974012193</v>
       </c>
       <c r="E138" t="n">
-        <v>0.5197300212841484</v>
+        <v>1.070226458247349</v>
       </c>
       <c r="F138" t="n">
-        <v>-1.427448618580587</v>
+        <v>-0.6358057135213003</v>
       </c>
       <c r="G138" t="n">
-        <v>-0.7561608221209863</v>
+        <v>-0.7605393854836451</v>
       </c>
     </row>
     <row r="139">
@@ -25151,22 +25151,22 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1.059926660410807</v>
+        <v>-0.188726603636796</v>
       </c>
       <c r="C139" t="n">
-        <v>3.226534266102486</v>
+        <v>1.370351548694358</v>
       </c>
       <c r="D139" t="n">
-        <v>-1.037589135263113</v>
+        <v>0.0112119680641669</v>
       </c>
       <c r="E139" t="n">
-        <v>0.978821794175615</v>
+        <v>1.07130489188285</v>
       </c>
       <c r="F139" t="n">
-        <v>-1.344623564458377</v>
+        <v>-0.6454377747835347</v>
       </c>
       <c r="G139" t="n">
-        <v>-0.7165133405014374</v>
+        <v>-0.7250296367629383</v>
       </c>
     </row>
     <row r="140">
@@ -25176,22 +25176,22 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1.60360551560899</v>
+        <v>-0.1955917904937563</v>
       </c>
       <c r="C140" t="n">
-        <v>3.389281319253238</v>
+        <v>1.363213077379434</v>
       </c>
       <c r="D140" t="n">
-        <v>-1.166648785057998</v>
+        <v>0.0094999963360349</v>
       </c>
       <c r="E140" t="n">
-        <v>1.201257385544717</v>
+        <v>1.068919566280451</v>
       </c>
       <c r="F140" t="n">
-        <v>-1.34968693127356</v>
+        <v>-0.6555367114716207</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.7120413631261284</v>
+        <v>-0.7329627557428011</v>
       </c>
     </row>
     <row r="141">
@@ -25201,22 +25201,22 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2.025758896920176</v>
+        <v>-0.2073736785433209</v>
       </c>
       <c r="C141" t="n">
-        <v>3.580782327662062</v>
+        <v>1.355689651435779</v>
       </c>
       <c r="D141" t="n">
-        <v>-1.050335123672208</v>
+        <v>0.0028549186709438</v>
       </c>
       <c r="E141" t="n">
-        <v>1.485679966325264</v>
+        <v>1.061896077423853</v>
       </c>
       <c r="F141" t="n">
-        <v>-1.293952587739659</v>
+        <v>-0.6661267629394099</v>
       </c>
       <c r="G141" t="n">
-        <v>-0.7066295828047416</v>
+        <v>-0.7318484465083908</v>
       </c>
     </row>
     <row r="142">
@@ -25226,22 +25226,22 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>2.023303954840036</v>
+        <v>-0.2262065032734632</v>
       </c>
       <c r="C142" t="n">
-        <v>3.329987035083374</v>
+        <v>1.347762445330285</v>
       </c>
       <c r="D142" t="n">
-        <v>-0.9387269771806606</v>
+        <v>-0.0120686143454857</v>
       </c>
       <c r="E142" t="n">
-        <v>1.503199818573557</v>
+        <v>1.047155979104883</v>
       </c>
       <c r="F142" t="n">
-        <v>-1.26708997078206</v>
+        <v>-0.67719708237554</v>
       </c>
       <c r="G142" t="n">
-        <v>-0.6481608603576</v>
+        <v>-0.6827864751556115</v>
       </c>
     </row>
     <row r="143">
@@ -25251,22 +25251,22 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1.302821873167898</v>
+        <v>-0.2526146350487821</v>
       </c>
       <c r="C143" t="n">
-        <v>2.822404754870956</v>
+        <v>1.339491595016226</v>
       </c>
       <c r="D143" t="n">
-        <v>-0.9163542556534594</v>
+        <v>-0.0380334853813995</v>
       </c>
       <c r="E143" t="n">
-        <v>0.9626745163889934</v>
+        <v>1.022135831731539</v>
       </c>
       <c r="F143" t="n">
-        <v>-1.25800103946381</v>
+        <v>-0.6886840954977781</v>
       </c>
       <c r="G143" t="n">
-        <v>-0.6528419945869028</v>
+        <v>-0.6950651971931048</v>
       </c>
     </row>
     <row r="144">
@@ -25276,22 +25276,22 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.3754939652736309</v>
+        <v>-0.2824979252690935</v>
       </c>
       <c r="C144" t="n">
-        <v>2.25612454380624</v>
+        <v>1.330965328825113</v>
       </c>
       <c r="D144" t="n">
-        <v>-1.076976415283969</v>
+        <v>-0.06890420846477061</v>
       </c>
       <c r="E144" t="n">
-        <v>0.3231038587053847</v>
+        <v>0.9924390055595708</v>
       </c>
       <c r="F144" t="n">
-        <v>-1.299130713131362</v>
+        <v>-0.7004584962460175</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.7534263299858872</v>
+        <v>-0.7716703899888221</v>
       </c>
     </row>
     <row r="145">
@@ -25301,22 +25301,22 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>-0.2327135209576138</v>
+        <v>-0.3118388662426248</v>
       </c>
       <c r="C145" t="n">
-        <v>1.891371173118114</v>
+        <v>1.322292558371933</v>
       </c>
       <c r="D145" t="n">
-        <v>-1.285856212824678</v>
+        <v>-0.100364374662055</v>
       </c>
       <c r="E145" t="n">
-        <v>-0.1540094296771247</v>
+        <v>0.9622083646259654</v>
       </c>
       <c r="F145" t="n">
-        <v>-1.379257230850466</v>
+        <v>-0.7123683830160349</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.8231312123621434</v>
+        <v>-0.8272412846939561</v>
       </c>
     </row>
     <row r="146">
@@ -25326,22 +25326,22 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-0.3484394838758426</v>
+        <v>-0.3390549900211277</v>
       </c>
       <c r="C146" t="n">
-        <v>1.664302456568742</v>
+        <v>1.313563940999623</v>
       </c>
       <c r="D146" t="n">
-        <v>-1.326218458233929</v>
+        <v>-0.1285116467903364</v>
       </c>
       <c r="E146" t="n">
-        <v>-0.1440474095344958</v>
+        <v>0.9350923016204692</v>
       </c>
       <c r="F146" t="n">
-        <v>-1.414845660876162</v>
+        <v>-0.7242651474746564</v>
       </c>
       <c r="G146" t="n">
-        <v>-0.8521546716857339</v>
+        <v>-0.8437835359236823</v>
       </c>
     </row>
     <row r="147">
@@ -25351,22 +25351,22 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-0.5176606599805771</v>
+        <v>-0.3661625897573659</v>
       </c>
       <c r="C147" t="n">
-        <v>1.301684757438176</v>
+        <v>1.304857836175983</v>
       </c>
       <c r="D147" t="n">
-        <v>-1.280280509398957</v>
+        <v>-0.1587027681793706</v>
       </c>
       <c r="E147" t="n">
-        <v>-0.2997445238926688</v>
+        <v>0.9062590596379434</v>
       </c>
       <c r="F147" t="n">
-        <v>-1.40799486926348</v>
+        <v>-0.7360255474194657</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.8348121344480378</v>
+        <v>-0.8468687926517301</v>
       </c>
     </row>
     <row r="148">
@@ -25376,22 +25376,22 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-0.6904697358244141</v>
+        <v>-0.3923003319255329</v>
       </c>
       <c r="C148" t="n">
-        <v>0.9829977752266974</v>
+        <v>1.296290312645529</v>
       </c>
       <c r="D148" t="n">
-        <v>-1.234692686553303</v>
+        <v>-0.1880440054934107</v>
       </c>
       <c r="E148" t="n">
-        <v>-0.3643035558673189</v>
+        <v>0.8782142598533418</v>
       </c>
       <c r="F148" t="n">
-        <v>-1.405677562458396</v>
+        <v>-0.7475165381094604</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.8386345394249048</v>
+        <v>-0.8381276970728344</v>
       </c>
     </row>
     <row r="149">
@@ -25401,22 +25401,22 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-0.8005157137898382</v>
+        <v>-0.4169055921764748</v>
       </c>
       <c r="C149" t="n">
-        <v>0.6089779055100257</v>
+        <v>1.287957492288714</v>
       </c>
       <c r="D149" t="n">
-        <v>-1.309398703125888</v>
+        <v>-0.2170336572807425</v>
       </c>
       <c r="E149" t="n">
-        <v>-0.4824308740852219</v>
+        <v>0.850612852923148</v>
       </c>
       <c r="F149" t="n">
-        <v>-1.423582256663019</v>
+        <v>-0.7586167899267078</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.8449857351933857</v>
+        <v>-0.8459667896407741</v>
       </c>
     </row>
     <row r="150">
@@ -25426,22 +25426,22 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>-0.7949982038797061</v>
+        <v>-0.4395570316381032</v>
       </c>
       <c r="C150" t="n">
-        <v>0.3405241772141593</v>
+        <v>1.279971366246844</v>
       </c>
       <c r="D150" t="n">
-        <v>-1.152640890922322</v>
+        <v>-0.2444888808200991</v>
       </c>
       <c r="E150" t="n">
-        <v>-0.390065230403293</v>
+        <v>0.8245215981009508</v>
       </c>
       <c r="F150" t="n">
-        <v>-1.382318461816786</v>
+        <v>-0.7692141956069931</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.826809721931878</v>
+        <v>-0.8235043376107761</v>
       </c>
     </row>
     <row r="151">
@@ -25451,22 +25451,22 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>-0.7942270724465157</v>
+        <v>-0.4608974966580665</v>
       </c>
       <c r="C151" t="n">
-        <v>0.1280927587727235</v>
+        <v>1.272420006044874</v>
       </c>
       <c r="D151" t="n">
-        <v>-1.170365119434965</v>
+        <v>-0.2714643479113618</v>
       </c>
       <c r="E151" t="n">
-        <v>-0.3553950660441849</v>
+        <v>0.7990121985991476</v>
       </c>
       <c r="F151" t="n">
-        <v>-1.377554386691071</v>
+        <v>-0.779212881709815</v>
       </c>
       <c r="G151" t="n">
-        <v>-0.8311643826776373</v>
+        <v>-0.8304818065221273</v>
       </c>
     </row>
     <row r="152">
@@ -25476,22 +25476,22 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-1.093451070997771</v>
+        <v>-0.4820741053774213</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.2484342777002823</v>
+        <v>1.265369058892201</v>
       </c>
       <c r="D152" t="n">
-        <v>-1.282346628725896</v>
+        <v>-0.3005802240494684</v>
       </c>
       <c r="E152" t="n">
-        <v>-0.6104409906171403</v>
+        <v>0.7716795937248735</v>
       </c>
       <c r="F152" t="n">
-        <v>-1.386282747001041</v>
+        <v>-0.7885290737730505</v>
       </c>
       <c r="G152" t="n">
-        <v>-0.8889805352139764</v>
+        <v>-0.8988838669452313</v>
       </c>
     </row>
     <row r="153">
@@ -25501,22 +25501,22 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>-1.554212019326901</v>
+        <v>-0.5018385984696243</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.5353610692581668</v>
+        <v>1.258909167797001</v>
       </c>
       <c r="D153" t="n">
-        <v>-1.373328272910681</v>
+        <v>-0.3291128966938994</v>
       </c>
       <c r="E153" t="n">
-        <v>-0.8829252569596527</v>
+        <v>0.744952226754334</v>
       </c>
       <c r="F153" t="n">
-        <v>-1.425396608726001</v>
+        <v>-0.7970745860906199</v>
       </c>
       <c r="G153" t="n">
-        <v>-0.9395585062442536</v>
+        <v>-0.94034486319138</v>
       </c>
     </row>
     <row r="154">
@@ -25526,22 +25526,22 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>-2.040350731767886</v>
+        <v>-0.5187341907858917</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.7450560724178674</v>
+        <v>1.253095449458147</v>
       </c>
       <c r="D154" t="n">
-        <v>-1.544292574598912</v>
+        <v>-0.3557833500930334</v>
       </c>
       <c r="E154" t="n">
-        <v>-1.205984206144672</v>
+        <v>0.7200726831738886</v>
       </c>
       <c r="F154" t="n">
-        <v>-1.496279694080835</v>
+        <v>-0.8047741317308184</v>
       </c>
       <c r="G154" t="n">
-        <v>-1.017203448246172</v>
+        <v>-1.015385850597196</v>
       </c>
     </row>
     <row r="155">
@@ -25551,22 +25551,22 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>-2.316828485244076</v>
+        <v>-0.5309534521048839</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.6620618573790898</v>
+        <v>1.247978082126054</v>
       </c>
       <c r="D155" t="n">
-        <v>-1.943137997311138</v>
+        <v>-0.3778177580761168</v>
       </c>
       <c r="E155" t="n">
-        <v>-1.491328133924539</v>
+        <v>0.6995917033331578</v>
       </c>
       <c r="F155" t="n">
-        <v>-1.611088925807022</v>
+        <v>-0.8115723537501177</v>
       </c>
       <c r="G155" t="n">
-        <v>-1.176603954947651</v>
+        <v>-1.168235581516655</v>
       </c>
     </row>
     <row r="156">
@@ -25576,22 +25576,22 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>-2.156336116866159</v>
+        <v>-0.5376622045287548</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.3596571191564045</v>
+        <v>1.243559482555015</v>
       </c>
       <c r="D156" t="n">
-        <v>-2.197441894484145</v>
+        <v>-0.3924866192573493</v>
       </c>
       <c r="E156" t="n">
-        <v>-1.399915815274593</v>
+        <v>0.686036257901657</v>
       </c>
       <c r="F156" t="n">
-        <v>-1.714723289736813</v>
+        <v>-0.8174492607693298</v>
       </c>
       <c r="G156" t="n">
-        <v>-1.280410197973141</v>
+        <v>-1.267616121746084</v>
       </c>
     </row>
     <row r="157">
@@ -25601,22 +25601,22 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-1.754891690500787</v>
+        <v>-0.5404972009164799</v>
       </c>
       <c r="C157" t="n">
-        <v>0.08799706839852731</v>
+        <v>1.239816560644606</v>
       </c>
       <c r="D157" t="n">
-        <v>-2.391881421232005</v>
+        <v>-0.4021519022456319</v>
       </c>
       <c r="E157" t="n">
-        <v>-1.21827568637428</v>
+        <v>0.6772374965162866</v>
       </c>
       <c r="F157" t="n">
-        <v>-1.805732748598408</v>
+        <v>-0.8224310392210358</v>
       </c>
       <c r="G157" t="n">
-        <v>-1.344420221417384</v>
+        <v>-1.344359668525745</v>
       </c>
     </row>
     <row r="158">
@@ -25626,22 +25626,22 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-1.32058538930367</v>
+        <v>-0.541548592264119</v>
       </c>
       <c r="C158" t="n">
-        <v>0.4320994219093601</v>
+        <v>1.23669431102082</v>
       </c>
       <c r="D158" t="n">
-        <v>-2.601835100376563</v>
+        <v>-0.4077231537390764</v>
       </c>
       <c r="E158" t="n">
-        <v>-0.9934624459856568</v>
+        <v>0.6722498479859524</v>
       </c>
       <c r="F158" t="n">
-        <v>-1.896673717861064</v>
+        <v>-0.826570409801534</v>
       </c>
       <c r="G158" t="n">
-        <v>-1.384349839506946</v>
+        <v>-1.389847473650611</v>
       </c>
     </row>
     <row r="159">
@@ -25651,22 +25651,22 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>-1.196381413568725</v>
+        <v>-0.5431082873345553</v>
       </c>
       <c r="C159" t="n">
-        <v>0.753800199130227</v>
+        <v>1.234151275210423</v>
       </c>
       <c r="D159" t="n">
-        <v>-2.757641128099705</v>
+        <v>-0.4137153861625244</v>
       </c>
       <c r="E159" t="n">
-        <v>-1.09143419658843</v>
+        <v>0.6668906607366649</v>
       </c>
       <c r="F159" t="n">
-        <v>-1.907139120582997</v>
+        <v>-0.8299385040114782</v>
       </c>
       <c r="G159" t="n">
-        <v>-1.394403622636719</v>
+        <v>-1.41840639106983</v>
       </c>
     </row>
     <row r="160">
@@ -25676,22 +25676,22 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>-1.146017738568934</v>
+        <v>-0.5443217145359471</v>
       </c>
       <c r="C160" t="n">
-        <v>0.8642466291542131</v>
+        <v>1.23212053723311</v>
       </c>
       <c r="D160" t="n">
-        <v>-2.121731667439454</v>
+        <v>-0.4162995495179142</v>
       </c>
       <c r="E160" t="n">
-        <v>-0.7210858352405218</v>
+        <v>0.6645192092713335</v>
       </c>
       <c r="F160" t="n">
-        <v>-1.702170653056983</v>
+        <v>-0.8325934617247044</v>
       </c>
       <c r="G160" t="n">
-        <v>-1.317145212074182</v>
+        <v>-1.326094348775481</v>
       </c>
     </row>
     <row r="161">
@@ -25701,22 +25701,22 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-1.27534550549828</v>
+        <v>-0.5454825181224905</v>
       </c>
       <c r="C161" t="n">
-        <v>0.8369726922758675</v>
+        <v>1.23055403928415</v>
       </c>
       <c r="D161" t="n">
-        <v>-2.185326556704228</v>
+        <v>-0.4196171172934071</v>
       </c>
       <c r="E161" t="n">
-        <v>-0.9031944470377402</v>
+        <v>0.6614855334199121</v>
       </c>
       <c r="F161" t="n">
-        <v>-1.680016542539579</v>
+        <v>-0.8346045787981893</v>
       </c>
       <c r="G161" t="n">
-        <v>-1.292448349932604</v>
+        <v>-1.310742627972998</v>
       </c>
     </row>
     <row r="162">
@@ -25726,22 +25726,22 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>-1.34810646813381</v>
+        <v>-0.5450515350937317</v>
       </c>
       <c r="C162" t="n">
-        <v>0.7142508821886512</v>
+        <v>1.229401938021343</v>
       </c>
       <c r="D162" t="n">
-        <v>-2.104858144120606</v>
+        <v>-0.4203901393116673</v>
       </c>
       <c r="E162" t="n">
-        <v>-0.919458636525907</v>
+        <v>0.6607514490595072</v>
       </c>
       <c r="F162" t="n">
-        <v>-1.681664969419522</v>
+        <v>-0.8360354605569174</v>
       </c>
       <c r="G162" t="n">
-        <v>-1.257147225630147</v>
+        <v>-1.26296210467933</v>
       </c>
     </row>
     <row r="163">
@@ -25751,22 +25751,22 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>-1.134279766981503</v>
+        <v>-0.5420035833108395</v>
       </c>
       <c r="C163" t="n">
-        <v>0.7029349140052193</v>
+        <v>1.228624223850436</v>
       </c>
       <c r="D163" t="n">
-        <v>-2.091774092821303</v>
+        <v>-0.4175623726078212</v>
       </c>
       <c r="E163" t="n">
-        <v>-0.7701841598155263</v>
+        <v>0.6633701067091908</v>
       </c>
       <c r="F163" t="n">
-        <v>-1.683317749238918</v>
+        <v>-0.8369646675401176</v>
       </c>
       <c r="G163" t="n">
-        <v>-1.268468191471042</v>
+        <v>-1.269985246330147</v>
       </c>
     </row>
     <row r="164">
@@ -25776,22 +25776,22 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>-0.6361571696696913</v>
+        <v>-0.5369562816676505</v>
       </c>
       <c r="C164" t="n">
-        <v>0.7327779471599034</v>
+        <v>1.228153978391041</v>
       </c>
       <c r="D164" t="n">
-        <v>-1.985719693688672</v>
+        <v>-0.4122063303954011</v>
       </c>
       <c r="E164" t="n">
-        <v>-0.4389292794918578</v>
+        <v>0.6683847450292442</v>
       </c>
       <c r="F164" t="n">
-        <v>-1.701078474312789</v>
+        <v>-0.8374931311580411</v>
       </c>
       <c r="G164" t="n">
-        <v>-1.22473541513154</v>
+        <v>-1.230250575187693</v>
       </c>
     </row>
     <row r="165">
@@ -25801,22 +25801,22 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-0.0666941753802747</v>
+        <v>-0.5321569423004433</v>
       </c>
       <c r="C165" t="n">
-        <v>0.8987404938024228</v>
+        <v>1.227928885844292</v>
       </c>
       <c r="D165" t="n">
-        <v>-2.201313802073231</v>
+        <v>-0.4057790360657121</v>
       </c>
       <c r="E165" t="n">
-        <v>-0.1370451879099519</v>
+        <v>0.6744308911943078</v>
       </c>
       <c r="F165" t="n">
-        <v>-1.784514604171305</v>
+        <v>-0.837736712886212</v>
       </c>
       <c r="G165" t="n">
-        <v>-1.242488949142228</v>
+        <v>-1.252759310127831</v>
       </c>
     </row>
     <row r="166">
@@ -25826,22 +25826,22 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>-0.0156532182917152</v>
+        <v>-0.5310482808610769</v>
       </c>
       <c r="C166" t="n">
-        <v>1.062436411912193</v>
+        <v>1.2278621309799</v>
       </c>
       <c r="D166" t="n">
-        <v>-2.071582173793806</v>
+        <v>-0.4056181600573527</v>
       </c>
       <c r="E166" t="n">
-        <v>-0.2273580834829629</v>
+        <v>0.6747580536455251</v>
       </c>
       <c r="F166" t="n">
-        <v>-1.773714422359306</v>
+        <v>-0.8378184404271463</v>
       </c>
       <c r="G166" t="n">
-        <v>-1.194070004921689</v>
+        <v>-1.233337218960179</v>
       </c>
     </row>
     <row r="167">
@@ -25851,22 +25851,22 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>-0.0156531891188609</v>
+        <v>-0.5310482808610631</v>
       </c>
       <c r="C167" t="n">
-        <v>1.062436422105081</v>
+        <v>1.227862130979898</v>
       </c>
       <c r="D167" t="n">
-        <v>-2.087450502207987</v>
+        <v>-0.4056181580205789</v>
       </c>
       <c r="E167" t="n">
-        <v>-0.2352922633589007</v>
+        <v>0.674758057948174</v>
       </c>
       <c r="F167" t="n">
-        <v>-1.776021244703693</v>
+        <v>-0.8378184404271493</v>
       </c>
       <c r="G167" t="n">
-        <v>-1.229705554378294</v>
+        <v>-1.243429432400429</v>
       </c>
     </row>
   </sheetData>

--- a/excel/Japan_Neutral_Rate_Models.xlsx
+++ b/excel/Japan_Neutral_Rate_Models.xlsx
@@ -3553,28 +3553,28 @@
         <v>0.7712936189418542</v>
       </c>
       <c r="N19" t="n">
-        <v>1.50291714475888</v>
+        <v>0.3029171447588805</v>
       </c>
       <c r="O19" t="n">
-        <v>1.50291714475888</v>
+        <v>0.3029171447588805</v>
       </c>
       <c r="P19" t="n">
-        <v>1.49321754145622</v>
+        <v>1.19321754145622</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.438971952269451</v>
+        <v>1.372305285602784</v>
       </c>
       <c r="R19" t="n">
-        <v>2.830036469018795</v>
+        <v>3.130036469018795</v>
       </c>
       <c r="S19" t="n">
-        <v>4.772784997387244</v>
+        <v>5.072784997387245</v>
       </c>
       <c r="T19" t="n">
-        <v>4.827030586574015</v>
+        <v>4.893697253240681</v>
       </c>
       <c r="U19" t="n">
-        <v>2.990531562687047</v>
+        <v>3.290531562687047</v>
       </c>
       <c r="V19">
         <f>T19-R19</f>
@@ -3676,28 +3676,28 @@
         <v>3.158453542124334</v>
       </c>
       <c r="N20" t="n">
-        <v>1.453181869877104</v>
+        <v>0.253181869877104</v>
       </c>
       <c r="O20" t="n">
-        <v>1.453181869877104</v>
+        <v>0.253181869877104</v>
       </c>
       <c r="P20" t="n">
-        <v>1.506002903940074</v>
+        <v>0.9060029039400743</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.439719842669853</v>
+        <v>1.313404053196169</v>
       </c>
       <c r="R20" t="n">
-        <v>2.615949178410204</v>
+        <v>3.215949178410204</v>
       </c>
       <c r="S20" t="n">
-        <v>4.599687845958956</v>
+        <v>5.199687845958955</v>
       </c>
       <c r="T20" t="n">
-        <v>4.665970907229177</v>
+        <v>4.792286696702861</v>
       </c>
       <c r="U20" t="n">
-        <v>2.841023415299634</v>
+        <v>3.441023415299634</v>
       </c>
       <c r="V20">
         <f>T20-R20</f>
@@ -3799,28 +3799,28 @@
         <v>5.013718719115786</v>
       </c>
       <c r="N21" t="n">
-        <v>1.466458072683654</v>
+        <v>0.2664580726836536</v>
       </c>
       <c r="O21" t="n">
-        <v>1.466458072683654</v>
+        <v>0.2664580726836536</v>
       </c>
       <c r="P21" t="n">
-        <v>1.525761151879036</v>
+        <v>0.6257611518790359</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.441056754170543</v>
+        <v>1.261056754170544</v>
       </c>
       <c r="R21" t="n">
-        <v>2.559372679986082</v>
+        <v>3.459372679986082</v>
       </c>
       <c r="S21" t="n">
-        <v>4.325778757482067</v>
+        <v>5.225778757482066</v>
       </c>
       <c r="T21" t="n">
-        <v>4.410483155190559</v>
+        <v>4.590483155190559</v>
       </c>
       <c r="U21" t="n">
-        <v>2.769853198662895</v>
+        <v>3.669853198662895</v>
       </c>
       <c r="V21">
         <f>T21-R21</f>
@@ -3922,28 +3922,28 @@
         <v>1.466964981910223</v>
       </c>
       <c r="N22" t="n">
-        <v>0.9266227666007671</v>
+        <v>-0.2733772333992328</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9266227666007671</v>
+        <v>-0.2733772333992328</v>
       </c>
       <c r="P22" t="n">
-        <v>1.337294963480101</v>
+        <v>0.1372949634801013</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.429968000389504</v>
+        <v>1.189968000389504</v>
       </c>
       <c r="R22" t="n">
-        <v>2.667678910170685</v>
+        <v>3.867678910170686</v>
       </c>
       <c r="S22" t="n">
-        <v>4.658184931577132</v>
+        <v>5.858184931577132</v>
       </c>
       <c r="T22" t="n">
-        <v>4.56551189466773</v>
+        <v>4.80551189466773</v>
       </c>
       <c r="U22" t="n">
-        <v>2.939156978651208</v>
+        <v>4.139156978651208</v>
       </c>
       <c r="V22">
         <f>T22-R22</f>
@@ -4051,22 +4051,22 @@
         <v>0.8920618159651362</v>
       </c>
       <c r="P23" t="n">
-        <v>1.184581131281665</v>
+        <v>0.2845811312816653</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.412248243949969</v>
+        <v>1.172248243949969</v>
       </c>
       <c r="R23" t="n">
-        <v>2.711113836127282</v>
+        <v>3.611113836127282</v>
       </c>
       <c r="S23" t="n">
-        <v>4.514671483825745</v>
+        <v>5.414671483825744</v>
       </c>
       <c r="T23" t="n">
-        <v>4.28700437115744</v>
+        <v>4.527004371157441</v>
       </c>
       <c r="U23" t="n">
-        <v>2.923719494089031</v>
+        <v>3.823719494089031</v>
       </c>
       <c r="V23">
         <f>T23-R23</f>
@@ -4174,22 +4174,22 @@
         <v>0.6640213188070185</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9872909935141438</v>
+        <v>0.3872909935141439</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.371344602898742</v>
+        <v>1.131344602898742</v>
       </c>
       <c r="R24" t="n">
-        <v>2.85224931257036</v>
+        <v>3.45224931257036</v>
       </c>
       <c r="S24" t="n">
-        <v>4.827618415240468</v>
+        <v>5.427618415240468</v>
       </c>
       <c r="T24" t="n">
-        <v>4.443564805855869</v>
+        <v>4.68356480585587</v>
       </c>
       <c r="U24" t="n">
-        <v>3.063880406808221</v>
+        <v>3.663880406808221</v>
       </c>
       <c r="V24">
         <f>T24-R24</f>
@@ -4297,22 +4297,22 @@
         <v>0.3831971435357721</v>
       </c>
       <c r="P25" t="n">
-        <v>0.7164757612271736</v>
+        <v>0.4164757612271735</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.313785178040981</v>
+        <v>1.07378517804098</v>
       </c>
       <c r="R25" t="n">
-        <v>3.000756500084629</v>
+        <v>3.300756500084629</v>
       </c>
       <c r="S25" t="n">
-        <v>4.791426635119279</v>
+        <v>5.091426635119279</v>
       </c>
       <c r="T25" t="n">
-        <v>4.194117218305473</v>
+        <v>4.434117218305473</v>
       </c>
       <c r="U25" t="n">
-        <v>3.195748662181372</v>
+        <v>3.495748662181372</v>
       </c>
       <c r="V25">
         <f>T25-R25</f>
@@ -4423,7 +4423,7 @@
         <v>0.5995690567971526</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.258241655585404</v>
+        <v>1.018241655585404</v>
       </c>
       <c r="R26" t="n">
         <v>3.433847244108247</v>
@@ -4432,7 +4432,7 @@
         <v>5.246953026712862</v>
       </c>
       <c r="T26" t="n">
-        <v>4.58828042792461</v>
+        <v>4.82828042792461</v>
       </c>
       <c r="U26" t="n">
         <v>3.658350520124271</v>
@@ -4546,7 +4546,7 @@
         <v>0.4788866145619024</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.202072828752279</v>
+        <v>0.962072828752279</v>
       </c>
       <c r="R27" t="n">
         <v>3.361694771326559</v>
@@ -4555,7 +4555,7 @@
         <v>5.198242218590842</v>
       </c>
       <c r="T27" t="n">
-        <v>4.475056004400466</v>
+        <v>4.715056004400465</v>
       </c>
       <c r="U27" t="n">
         <v>3.580447327364004</v>
@@ -4669,7 +4669,7 @@
         <v>0.4283414518028388</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.154073606732986</v>
+        <v>0.9140736067329867</v>
       </c>
       <c r="R28" t="n">
         <v>3.366549318617689</v>
@@ -4678,7 +4678,7 @@
         <v>5.484434686554442</v>
       </c>
       <c r="T28" t="n">
-        <v>4.758702531624294</v>
+        <v>4.998702531624295</v>
       </c>
       <c r="U28" t="n">
         <v>3.604101068874645</v>
@@ -4792,7 +4792,7 @@
         <v>0.4364953460045951</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.110725839693341</v>
+        <v>0.8707258396933415</v>
       </c>
       <c r="R29" t="n">
         <v>3.269951501376605</v>
@@ -4801,7 +4801,7 @@
         <v>5.155080058861085</v>
       </c>
       <c r="T29" t="n">
-        <v>4.480849565172338</v>
+        <v>4.720849565172338</v>
       </c>
       <c r="U29" t="n">
         <v>3.454311813817486</v>
@@ -4915,7 +4915,7 @@
         <v>0.4407997492617576</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.07029390166509</v>
+        <v>0.8302939016650901</v>
       </c>
       <c r="R30" t="n">
         <v>3.010692774755671</v>
@@ -4924,7 +4924,7 @@
         <v>4.739966321760525</v>
       </c>
       <c r="T30" t="n">
-        <v>4.110472169357193</v>
+        <v>4.350472169357192</v>
       </c>
       <c r="U30" t="n">
         <v>3.197630550567353</v>
@@ -5038,7 +5038,7 @@
         <v>0.4473309945327229</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.022852661304303</v>
+        <v>0.7828526613043032</v>
       </c>
       <c r="R31" t="n">
         <v>2.883284222681549</v>
@@ -5047,7 +5047,7 @@
         <v>4.780184009709135</v>
       </c>
       <c r="T31" t="n">
-        <v>4.204662342937555</v>
+        <v>4.444662342937555</v>
       </c>
       <c r="U31" t="n">
         <v>3.06891112755419</v>
@@ -5161,7 +5161,7 @@
         <v>0.4045135192283732</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.9639576205786706</v>
+        <v>0.7239576205786706</v>
       </c>
       <c r="R32" t="n">
         <v>2.912275697587638</v>
@@ -5170,7 +5170,7 @@
         <v>4.676092443879205</v>
       </c>
       <c r="T32" t="n">
-        <v>4.116648342528907</v>
+        <v>4.356648342528907</v>
       </c>
       <c r="U32" t="n">
         <v>3.135999749223009</v>
@@ -5284,7 +5284,7 @@
         <v>0.3660704051489369</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.8967910986456014</v>
+        <v>0.6567910986456014</v>
       </c>
       <c r="R33" t="n">
         <v>2.74936239551631</v>
@@ -5293,7 +5293,7 @@
         <v>4.500387377226189</v>
       </c>
       <c r="T33" t="n">
-        <v>3.969666683729525</v>
+        <v>4.209666683729525</v>
       </c>
       <c r="U33" t="n">
         <v>2.994313628725212</v>
@@ -5407,7 +5407,7 @@
         <v>0.3052722664562841</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.8342491734852215</v>
+        <v>0.5942491734852215</v>
       </c>
       <c r="R34" t="n">
         <v>2.764918803147044</v>
@@ -5416,7 +5416,7 @@
         <v>4.655778939136255</v>
       </c>
       <c r="T34" t="n">
-        <v>4.126802032107317</v>
+        <v>4.366802032107318</v>
       </c>
       <c r="U34" t="n">
         <v>2.951153588352565</v>
@@ -5530,7 +5530,7 @@
         <v>0.2567829604340612</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.7721598484533144</v>
+        <v>0.5321598484533144</v>
       </c>
       <c r="R35" t="n">
         <v>2.59609025397133</v>
@@ -5539,7 +5539,7 @@
         <v>4.399198812748445</v>
       </c>
       <c r="T35" t="n">
-        <v>3.883821924729192</v>
+        <v>4.123821924729191</v>
       </c>
       <c r="U35" t="n">
         <v>2.783347042137537</v>
@@ -5653,7 +5653,7 @@
         <v>0.2794496481439275</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.7211197033258715</v>
+        <v>0.4811197033258716</v>
       </c>
       <c r="R36" t="n">
         <v>2.543302630669609</v>
@@ -5662,7 +5662,7 @@
         <v>4.371160222120789</v>
       </c>
       <c r="T36" t="n">
-        <v>3.929490166938845</v>
+        <v>4.169490166938845</v>
       </c>
       <c r="U36" t="n">
         <v>2.752724947385703</v>
@@ -5776,7 +5776,7 @@
         <v>0.2921675727032838</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.667394047392605</v>
+        <v>0.427394047392605</v>
       </c>
       <c r="R37" t="n">
         <v>2.339406718136988</v>
@@ -5785,7 +5785,7 @@
         <v>4.140805240323518</v>
       </c>
       <c r="T37" t="n">
-        <v>3.765578765634197</v>
+        <v>4.005578765634197</v>
       </c>
       <c r="U37" t="n">
         <v>2.532033873136601</v>
@@ -5899,7 +5899,7 @@
         <v>0.3126561896492119</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.5991184451289014</v>
+        <v>0.3591184451289015</v>
       </c>
       <c r="R38" t="n">
         <v>2.200255251516922</v>
@@ -5908,7 +5908,7 @@
         <v>4.033913564177466</v>
       </c>
       <c r="T38" t="n">
-        <v>3.747451308697777</v>
+        <v>3.987451308697777</v>
       </c>
       <c r="U38" t="n">
         <v>2.42881686111112</v>
@@ -6022,7 +6022,7 @@
         <v>0.3516137639370222</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.5438390929494747</v>
+        <v>0.3638390929494748</v>
       </c>
       <c r="R39" t="n">
         <v>2.101622137146473</v>
@@ -6031,7 +6031,7 @@
         <v>3.944118726890088</v>
       </c>
       <c r="T39" t="n">
-        <v>3.751893397877635</v>
+        <v>3.931893397877635</v>
       </c>
       <c r="U39" t="n">
         <v>2.234068818427902</v>
@@ -6145,7 +6145,7 @@
         <v>0.3229479259615973</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.4845087077301761</v>
+        <v>0.3645087077301762</v>
       </c>
       <c r="R40" t="n">
         <v>1.908963550166195</v>
@@ -6154,7 +6154,7 @@
         <v>3.515266856895653</v>
       </c>
       <c r="T40" t="n">
-        <v>3.353706075127074</v>
+        <v>3.473706075127074</v>
       </c>
       <c r="U40" t="n">
         <v>2.084162398758687</v>
@@ -6268,7 +6268,7 @@
         <v>0.3157938404816628</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.4254005851131303</v>
+        <v>0.3654005851131304</v>
       </c>
       <c r="R41" t="n">
         <v>1.762150054722089</v>
@@ -6277,7 +6277,7 @@
         <v>3.628807321583043</v>
       </c>
       <c r="T41" t="n">
-        <v>3.519200576951576</v>
+        <v>3.579200576951575</v>
       </c>
       <c r="U41" t="n">
         <v>1.938677564703246</v>
@@ -7489,28 +7489,28 @@
         <v>1.643703357446157</v>
       </c>
       <c r="N51" t="n">
-        <v>0.3504814215553214</v>
+        <v>-1.149518578444679</v>
       </c>
       <c r="O51" t="n">
-        <v>0.3504814215553214</v>
+        <v>-1.149518578444679</v>
       </c>
       <c r="P51" t="n">
-        <v>0.5316297823645547</v>
+        <v>0.1566297823645547</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.3766823728625923</v>
+        <v>0.3016823728625923</v>
       </c>
       <c r="R51" t="n">
-        <v>0.3020587443172477</v>
+        <v>0.6770587443172477</v>
       </c>
       <c r="S51" t="n">
-        <v>2.097400017283314</v>
+        <v>2.472400017283314</v>
       </c>
       <c r="T51" t="n">
-        <v>2.252347426785276</v>
+        <v>2.327347426785276</v>
       </c>
       <c r="U51" t="n">
-        <v>0.4727799798338005</v>
+        <v>0.8477799798338005</v>
       </c>
       <c r="V51">
         <f>T51-R51</f>
@@ -7612,28 +7612,28 @@
         <v>3.142388329727964</v>
       </c>
       <c r="N52" t="n">
-        <v>0.4292417610698</v>
+        <v>-1.0707582389302</v>
       </c>
       <c r="O52" t="n">
-        <v>0.4292417610698</v>
+        <v>-1.0707582389302</v>
       </c>
       <c r="P52" t="n">
-        <v>0.4967835137341734</v>
+        <v>-0.2532164862658266</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.383615922588414</v>
+        <v>0.233615922588414</v>
       </c>
       <c r="R52" t="n">
-        <v>0.2655997813212737</v>
+        <v>1.015599781321274</v>
       </c>
       <c r="S52" t="n">
-        <v>2.093486209785998</v>
+        <v>2.843486209785998</v>
       </c>
       <c r="T52" t="n">
-        <v>2.206653800931757</v>
+        <v>2.356653800931757</v>
       </c>
       <c r="U52" t="n">
-        <v>0.4382825348036302</v>
+        <v>1.18828253480363</v>
       </c>
       <c r="V52">
         <f>T52-R52</f>
@@ -7735,28 +7735,28 @@
         <v>4.787303244912437</v>
       </c>
       <c r="N53" t="n">
-        <v>0.2203403212220817</v>
+        <v>-1.279659678777918</v>
       </c>
       <c r="O53" t="n">
-        <v>0.2203403212220817</v>
+        <v>-1.279659678777918</v>
       </c>
       <c r="P53" t="n">
-        <v>0.3909864005810669</v>
+        <v>-0.7340135994189331</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.3815309254482656</v>
+        <v>0.1565309254482655</v>
       </c>
       <c r="R53" t="n">
-        <v>0.2250522681464453</v>
+        <v>1.350052268146445</v>
       </c>
       <c r="S53" t="n">
-        <v>1.924262973184091</v>
+        <v>3.049262973184091</v>
       </c>
       <c r="T53" t="n">
-        <v>1.933718448316893</v>
+        <v>2.158718448316892</v>
       </c>
       <c r="U53" t="n">
-        <v>0.441808736924672</v>
+        <v>1.566808736924672</v>
       </c>
       <c r="V53">
         <f>T53-R53</f>
@@ -7858,28 +7858,28 @@
         <v>-0.9511071227634602</v>
       </c>
       <c r="N54" t="n">
-        <v>0.0938184812127625</v>
+        <v>-1.406181518787238</v>
       </c>
       <c r="O54" t="n">
-        <v>0.0938184812127625</v>
+        <v>-1.406181518787238</v>
       </c>
       <c r="P54" t="n">
-        <v>0.2734704962649914</v>
+        <v>-1.226529503735009</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.3745707991519675</v>
+        <v>0.07457079915196753</v>
       </c>
       <c r="R54" t="n">
-        <v>0.2138606252876079</v>
+        <v>1.713860625287608</v>
       </c>
       <c r="S54" t="n">
-        <v>2.086288893033231</v>
+        <v>3.586288893033231</v>
       </c>
       <c r="T54" t="n">
-        <v>1.985188590146254</v>
+        <v>2.285188590146254</v>
       </c>
       <c r="U54" t="n">
-        <v>0.4072145418156838</v>
+        <v>1.907214541815684</v>
       </c>
       <c r="V54">
         <f>T54-R54</f>
@@ -7987,22 +7987,22 @@
         <v>0.1922989544822906</v>
       </c>
       <c r="P55" t="n">
-        <v>0.2339248794967337</v>
+        <v>-0.8910751205032664</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.3721107566751268</v>
+        <v>0.07211075667512681</v>
       </c>
       <c r="R55" t="n">
-        <v>0.1331158769342633</v>
+        <v>1.258115876934264</v>
       </c>
       <c r="S55" t="n">
-        <v>1.939416113767733</v>
+        <v>3.064416113767733</v>
       </c>
       <c r="T55" t="n">
-        <v>1.80123023658934</v>
+        <v>2.10123023658934</v>
       </c>
       <c r="U55" t="n">
-        <v>0.3525404176555474</v>
+        <v>1.477540417655548</v>
       </c>
       <c r="V55">
         <f>T55-R55</f>
@@ -8110,22 +8110,22 @@
         <v>-0.1981895882109143</v>
       </c>
       <c r="P56" t="n">
-        <v>0.07706704217655512</v>
+        <v>-0.6729329578234449</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.3431394013949395</v>
+        <v>0.04313940139493955</v>
       </c>
       <c r="R56" t="n">
-        <v>0.1831023698544421</v>
+        <v>0.9331023698544421</v>
       </c>
       <c r="S56" t="n">
-        <v>1.793907744523251</v>
+        <v>2.543907744523251</v>
       </c>
       <c r="T56" t="n">
-        <v>1.527835385304866</v>
+        <v>1.827835385304866</v>
       </c>
       <c r="U56" t="n">
-        <v>0.3826929661005832</v>
+        <v>1.132692966100583</v>
       </c>
       <c r="V56">
         <f>T56-R56</f>
@@ -8233,22 +8233,22 @@
         <v>-0.4077356719471128</v>
       </c>
       <c r="P57" t="n">
-        <v>-0.0799519561157435</v>
+        <v>-0.4549519561157435</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.3071070196844601</v>
+        <v>0.007107019684460081</v>
       </c>
       <c r="R57" t="n">
-        <v>0.1545251540185881</v>
+        <v>0.5295251540185881</v>
       </c>
       <c r="S57" t="n">
-        <v>1.758666009978885</v>
+        <v>2.133666009978885</v>
       </c>
       <c r="T57" t="n">
-        <v>1.371607034178681</v>
+        <v>1.671607034178682</v>
       </c>
       <c r="U57" t="n">
-        <v>0.3755750634612751</v>
+        <v>0.7505750634612751</v>
       </c>
       <c r="V57">
         <f>T57-R57</f>
@@ -8359,7 +8359,7 @@
         <v>-0.2373872140581227</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.2645621184105006</v>
+        <v>-0.03543788158949939</v>
       </c>
       <c r="R58" t="n">
         <v>0.3727296961030752</v>
@@ -8368,10 +8368,10 @@
         <v>2.171497766810144</v>
       </c>
       <c r="T58" t="n">
-        <v>1.669548434341521</v>
+        <v>1.969548434341521</v>
       </c>
       <c r="U58" t="n">
-        <v>0.5416773526818559</v>
+        <v>0.541677352681856</v>
       </c>
       <c r="V58">
         <f>T58-R58</f>
@@ -8479,19 +8479,19 @@
         <v>-0.6936990736732007</v>
       </c>
       <c r="P59" t="n">
-        <v>-0.4588867210969956</v>
+        <v>-0.4588867210969955</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.2100106596683233</v>
+        <v>-0.08998934033167673</v>
       </c>
       <c r="R59" t="n">
         <v>0.5920200196162697</v>
       </c>
       <c r="S59" t="n">
-        <v>2.369923287837635</v>
+        <v>2.369923287837634</v>
       </c>
       <c r="T59" t="n">
-        <v>1.701025907072315</v>
+        <v>2.001025907072316</v>
       </c>
       <c r="U59" t="n">
         <v>0.7916574800926217</v>
@@ -8605,7 +8605,7 @@
         <v>-0.5444785397048937</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.1696541082616413</v>
+        <v>-0.1303458917383586</v>
       </c>
       <c r="R60" t="n">
         <v>0.6637304365876987</v>
@@ -8614,7 +8614,7 @@
         <v>2.453388425230235</v>
       </c>
       <c r="T60" t="n">
-        <v>1.739255777263701</v>
+        <v>2.0392557772637</v>
       </c>
       <c r="U60" t="n">
         <v>0.857409736156804</v>
@@ -8728,7 +8728,7 @@
         <v>-0.5443869300615126</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.135070865575825</v>
+        <v>-0.164929134424175</v>
       </c>
       <c r="R61" t="n">
         <v>0.6722136021990757</v>
@@ -8737,7 +8737,7 @@
         <v>2.469415356546054</v>
       </c>
       <c r="T61" t="n">
-        <v>1.789957560908716</v>
+        <v>2.089957560908716</v>
       </c>
       <c r="U61" t="n">
         <v>0.8357368744759518</v>
@@ -8851,7 +8851,7 @@
         <v>-0.4770444985823322</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.1063010112436211</v>
+        <v>-0.1936989887563789</v>
       </c>
       <c r="R62" t="n">
         <v>0.5918653986227651</v>
@@ -8860,7 +8860,7 @@
         <v>2.414421382573783</v>
       </c>
       <c r="T62" t="n">
-        <v>1.83107587274783</v>
+        <v>2.13107587274783</v>
       </c>
       <c r="U62" t="n">
         <v>0.7449610601867046</v>
@@ -8974,7 +8974,7 @@
         <v>-0.3818572412090455</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.07760030977381728</v>
+        <v>-0.2223996902261828</v>
       </c>
       <c r="R63" t="n">
         <v>0.5836109063455988</v>
@@ -8983,7 +8983,7 @@
         <v>2.478375867330429</v>
       </c>
       <c r="T63" t="n">
-        <v>2.018918316347567</v>
+        <v>2.318918316347566</v>
       </c>
       <c r="U63" t="n">
         <v>0.8041833774038387</v>
@@ -9097,7 +9097,7 @@
         <v>-0.3765131623931129</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.03575677957767776</v>
+        <v>-0.2642432204223223</v>
       </c>
       <c r="R64" t="n">
         <v>0.4721584538404874</v>
@@ -9106,7 +9106,7 @@
         <v>2.161047963748731</v>
       </c>
       <c r="T64" t="n">
-        <v>1.748778021777941</v>
+        <v>2.048778021777941</v>
       </c>
       <c r="U64" t="n">
         <v>0.6616298823739479</v>
@@ -9220,7 +9220,7 @@
         <v>-0.4132753832210797</v>
       </c>
       <c r="Q65" t="n">
-        <v>-0.01591566886277312</v>
+        <v>-0.3159156688627731</v>
       </c>
       <c r="R65" t="n">
         <v>0.4979212223043508</v>
@@ -9229,7 +9229,7 @@
         <v>2.180724063014271</v>
       </c>
       <c r="T65" t="n">
-        <v>1.783364348655965</v>
+        <v>2.083364348655965</v>
       </c>
       <c r="U65" t="n">
         <v>0.667252813854931</v>
@@ -9343,7 +9343,7 @@
         <v>-0.4992676477255645</v>
       </c>
       <c r="Q66" t="n">
-        <v>-0.07284763481710735</v>
+        <v>-0.3728476348171074</v>
       </c>
       <c r="R66" t="n">
         <v>0.5615912687076956</v>
@@ -9352,7 +9352,7 @@
         <v>2.252258882918957</v>
       </c>
       <c r="T66" t="n">
-        <v>1.8258388700105</v>
+        <v>2.1258388700105</v>
       </c>
       <c r="U66" t="n">
         <v>0.7587059005999957</v>
@@ -9466,7 +9466,7 @@
         <v>-0.5385577638023759</v>
       </c>
       <c r="Q67" t="n">
-        <v>-0.1227494128494257</v>
+        <v>-0.4227494128494257</v>
       </c>
       <c r="R67" t="n">
         <v>0.586944630273484</v>
@@ -9475,7 +9475,7 @@
         <v>2.415836296990355</v>
       </c>
       <c r="T67" t="n">
-        <v>2.000027946037405</v>
+        <v>2.300027946037404</v>
       </c>
       <c r="U67" t="n">
         <v>0.820785195993963</v>
@@ -9589,7 +9589,7 @@
         <v>-0.4698141841509955</v>
       </c>
       <c r="Q68" t="n">
-        <v>-0.1633910660676547</v>
+        <v>-0.4633910660676547</v>
       </c>
       <c r="R68" t="n">
         <v>0.5075905947709417</v>
@@ -9598,7 +9598,7 @@
         <v>2.432085332635586</v>
       </c>
       <c r="T68" t="n">
-        <v>2.125662214552245</v>
+        <v>2.425662214552246</v>
       </c>
       <c r="U68" t="n">
         <v>0.639168459409784</v>
@@ -9712,7 +9712,7 @@
         <v>-0.3906883150479148</v>
       </c>
       <c r="Q69" t="n">
-        <v>-0.2074632367730367</v>
+        <v>-0.5074632367730367</v>
       </c>
       <c r="R69" t="n">
         <v>0.4462484493863689</v>
@@ -9721,7 +9721,7 @@
         <v>2.203114505562418</v>
       </c>
       <c r="T69" t="n">
-        <v>2.01988942728754</v>
+        <v>2.31988942728754</v>
       </c>
       <c r="U69" t="n">
         <v>0.6013492886892692</v>
@@ -9835,7 +9835,7 @@
         <v>-0.274438208470189</v>
       </c>
       <c r="Q70" t="n">
-        <v>-0.2429334145142434</v>
+        <v>-0.5429334145142434</v>
       </c>
       <c r="R70" t="n">
         <v>0.3709041893875853</v>
@@ -9844,7 +9844,7 @@
         <v>1.92073420497162</v>
       </c>
       <c r="T70" t="n">
-        <v>1.889229411015674</v>
+        <v>2.189229411015674</v>
       </c>
       <c r="U70" t="n">
         <v>0.5432175961307273</v>
@@ -9958,7 +9958,7 @@
         <v>-0.1976067153901603</v>
       </c>
       <c r="Q71" t="n">
-        <v>-0.2685967124003687</v>
+        <v>-0.4935967124003687</v>
       </c>
       <c r="R71" t="n">
         <v>0.314321471815046</v>
@@ -9967,7 +9967,7 @@
         <v>1.943922185554009</v>
       </c>
       <c r="T71" t="n">
-        <v>2.014912182564217</v>
+        <v>2.239912182564217</v>
       </c>
       <c r="U71" t="n">
         <v>0.5581568378166559</v>
@@ -10081,7 +10081,7 @@
         <v>-0.1804742095002639</v>
       </c>
       <c r="Q72" t="n">
-        <v>-0.2988426107145422</v>
+        <v>-0.4488426107145422</v>
       </c>
       <c r="R72" t="n">
         <v>0.283031312427872</v>
@@ -10090,7 +10090,7 @@
         <v>1.999727640148271</v>
       </c>
       <c r="T72" t="n">
-        <v>2.118096041362549</v>
+        <v>2.268096041362549</v>
       </c>
       <c r="U72" t="n">
         <v>0.4915089219154509</v>
@@ -10204,7 +10204,7 @@
         <v>-0.1807192512653087</v>
       </c>
       <c r="Q73" t="n">
-        <v>-0.3218043671423119</v>
+        <v>-0.3968043671423119</v>
       </c>
       <c r="R73" t="n">
         <v>0.242442487393823</v>
@@ -10213,7 +10213,7 @@
         <v>1.986669598644301</v>
       </c>
       <c r="T73" t="n">
-        <v>2.127754714521305</v>
+        <v>2.202754714521305</v>
       </c>
       <c r="U73" t="n">
         <v>0.4654620046076598</v>
@@ -11680,7 +11680,7 @@
         <v>-0.5844752134438926</v>
       </c>
       <c r="Q85" t="n">
-        <v>-0.3405538698439287</v>
+        <v>-0.3405538698439288</v>
       </c>
       <c r="R85" t="n">
         <v>0.6117340891810031</v>
@@ -12049,7 +12049,7 @@
         <v>-0.6597719116184622</v>
       </c>
       <c r="Q88" t="n">
-        <v>-0.3646213178601197</v>
+        <v>-0.3646213178601198</v>
       </c>
       <c r="R88" t="n">
         <v>0.7471460449033138</v>
@@ -12664,7 +12664,7 @@
         <v>-0.1063448546896592</v>
       </c>
       <c r="Q93" t="n">
-        <v>-0.3529104234995888</v>
+        <v>-0.3529104234995887</v>
       </c>
       <c r="R93" t="n">
         <v>0.1527382036183162</v>
@@ -13279,7 +13279,7 @@
         <v>-0.4137672564572768</v>
       </c>
       <c r="Q98" t="n">
-        <v>-0.370920084741046</v>
+        <v>-0.3709200847410461</v>
       </c>
       <c r="R98" t="n">
         <v>0.5255396748727733</v>
@@ -13525,7 +13525,7 @@
         <v>-0.5224662527634057</v>
       </c>
       <c r="Q100" t="n">
-        <v>-0.3921838984891958</v>
+        <v>-0.3921838984891959</v>
       </c>
       <c r="R100" t="n">
         <v>0.5613475371364105</v>
@@ -13771,7 +13771,7 @@
         <v>-0.3596592841075634</v>
       </c>
       <c r="Q102" t="n">
-        <v>-0.3822764813432313</v>
+        <v>-0.3822764813432314</v>
       </c>
       <c r="R102" t="n">
         <v>0.5507242266482189</v>
@@ -14017,7 +14017,7 @@
         <v>-0.2383456199222174</v>
       </c>
       <c r="Q104" t="n">
-        <v>-0.3532303781158585</v>
+        <v>-0.3532303781158584</v>
       </c>
       <c r="R104" t="n">
         <v>0.2742921595799258</v>
@@ -14632,7 +14632,7 @@
         <v>-0.3943057491493276</v>
       </c>
       <c r="Q109" t="n">
-        <v>-0.3059094320205689</v>
+        <v>-0.305909432020569</v>
       </c>
       <c r="R109" t="n">
         <v>0.4055576461672211</v>
@@ -15616,7 +15616,7 @@
         <v>0.6221037443232679</v>
       </c>
       <c r="Q117" t="n">
-        <v>-0.07941467831046629</v>
+        <v>-0.07941467831046631</v>
       </c>
       <c r="R117" t="n">
         <v>-0.4996987761264577</v>
@@ -15739,7 +15739,7 @@
         <v>0.6812384121187774</v>
       </c>
       <c r="Q118" t="n">
-        <v>-0.01390619717346638</v>
+        <v>-0.01390619717346639</v>
       </c>
       <c r="R118" t="n">
         <v>-0.665518277988018</v>
@@ -15853,28 +15853,28 @@
         <v>-2.980631013946095</v>
       </c>
       <c r="N119" t="n">
-        <v>0.5897204656310173</v>
+        <v>-1.410279534368983</v>
       </c>
       <c r="O119" t="n">
-        <v>0.5897204656310173</v>
+        <v>-1.410279534368983</v>
       </c>
       <c r="P119" t="n">
-        <v>0.6802993130511549</v>
+        <v>0.1802993130511549</v>
       </c>
       <c r="Q119" t="n">
-        <v>0.04303390388272887</v>
+        <v>-0.05696609611727114</v>
       </c>
       <c r="R119" t="n">
-        <v>-0.5533975910547424</v>
+        <v>-0.05339759105474237</v>
       </c>
       <c r="S119" t="n">
-        <v>1.237814734703695</v>
+        <v>1.737814734703695</v>
       </c>
       <c r="T119" t="n">
-        <v>1.875080143872122</v>
+        <v>1.975080143872121</v>
       </c>
       <c r="U119" t="n">
-        <v>-0.3128788374261627</v>
+        <v>0.1871211625738373</v>
       </c>
       <c r="V119">
         <f>T119-R119</f>
@@ -15976,28 +15976,28 @@
         <v>6.480648059301984</v>
       </c>
       <c r="N120" t="n">
-        <v>0.6426180078292527</v>
+        <v>-1.357381992170747</v>
       </c>
       <c r="O120" t="n">
-        <v>0.6426180078292527</v>
+        <v>-1.357381992170747</v>
       </c>
       <c r="P120" t="n">
-        <v>0.6735307533340337</v>
+        <v>-0.3264692466659663</v>
       </c>
       <c r="Q120" t="n">
-        <v>0.09737643690542087</v>
+        <v>-0.1026235630945791</v>
       </c>
       <c r="R120" t="n">
-        <v>-0.6252461559177537</v>
+        <v>0.3747538440822463</v>
       </c>
       <c r="S120" t="n">
-        <v>1.268782790570605</v>
+        <v>2.268782790570605</v>
       </c>
       <c r="T120" t="n">
-        <v>1.844937106999218</v>
+        <v>2.044937106999218</v>
       </c>
       <c r="U120" t="n">
-        <v>-0.4248845604996989</v>
+        <v>0.5751154395003011</v>
       </c>
       <c r="V120">
         <f>T120-R120</f>
@@ -16099,28 +16099,28 @@
         <v>-0.8429514910590115</v>
       </c>
       <c r="N121" t="n">
-        <v>0.5187067707573461</v>
+        <v>-1.481293229242654</v>
       </c>
       <c r="O121" t="n">
-        <v>0.5187067707573461</v>
+        <v>-1.481293229242654</v>
       </c>
       <c r="P121" t="n">
-        <v>0.6190449240708124</v>
+        <v>-0.8809550759291876</v>
       </c>
       <c r="Q121" t="n">
-        <v>0.1335185092855263</v>
+        <v>-0.1664814907144737</v>
       </c>
       <c r="R121" t="n">
-        <v>-0.5072811184913992</v>
+        <v>0.9927188815086008</v>
       </c>
       <c r="S121" t="n">
-        <v>1.379315745350317</v>
+        <v>2.879315745350317</v>
       </c>
       <c r="T121" t="n">
-        <v>1.864842160135603</v>
+        <v>2.164842160135603</v>
       </c>
       <c r="U121" t="n">
-        <v>-0.3011972001844658</v>
+        <v>1.198802799815534</v>
       </c>
       <c r="V121">
         <f>T121-R121</f>
@@ -16222,28 +16222,28 @@
         <v>-3.204983066192199</v>
       </c>
       <c r="N122" t="n">
-        <v>0.6280101654154778</v>
+        <v>-1.371989834584522</v>
       </c>
       <c r="O122" t="n">
-        <v>0.6280101654154778</v>
+        <v>-1.371989834584522</v>
       </c>
       <c r="P122" t="n">
-        <v>0.5947638524082735</v>
+        <v>-1.405236147591726</v>
       </c>
       <c r="Q122" t="n">
-        <v>0.176978430129701</v>
+        <v>-0.223021569870299</v>
       </c>
       <c r="R122" t="n">
-        <v>-0.5659505741782266</v>
+        <v>1.434049425821773</v>
       </c>
       <c r="S122" t="n">
-        <v>1.255210399101279</v>
+        <v>3.255210399101278</v>
       </c>
       <c r="T122" t="n">
-        <v>1.672995821379851</v>
+        <v>2.072995821379851</v>
       </c>
       <c r="U122" t="n">
-        <v>-0.3987547152920859</v>
+        <v>1.601245284707914</v>
       </c>
       <c r="V122">
         <f>T122-R122</f>
@@ -16351,22 +16351,22 @@
         <v>0.767527785167593</v>
       </c>
       <c r="P123" t="n">
-        <v>0.6392156822924173</v>
+        <v>-0.8607843177075825</v>
       </c>
       <c r="Q123" t="n">
-        <v>0.2245985663752277</v>
+        <v>-0.1754014336247724</v>
       </c>
       <c r="R123" t="n">
-        <v>-0.5168995749152643</v>
+        <v>0.9831004250847355</v>
       </c>
       <c r="S123" t="n">
-        <v>1.371739821041531</v>
+        <v>2.871739821041531</v>
       </c>
       <c r="T123" t="n">
-        <v>1.786356936958721</v>
+        <v>2.186356936958721</v>
       </c>
       <c r="U123" t="n">
-        <v>-0.3049898357802989</v>
+        <v>1.195010164219701</v>
       </c>
       <c r="V123">
         <f>T123-R123</f>
@@ -16474,22 +16474,22 @@
         <v>0.6776507891594434</v>
       </c>
       <c r="P124" t="n">
-        <v>0.6479738776249651</v>
+        <v>-0.3520261223750348</v>
       </c>
       <c r="Q124" t="n">
-        <v>0.2746403364148574</v>
+        <v>-0.1253596635851427</v>
       </c>
       <c r="R124" t="n">
-        <v>-0.5883038228403338</v>
+        <v>0.4116961771596661</v>
       </c>
       <c r="S124" t="n">
-        <v>1.260772848059048</v>
+        <v>2.260772848059048</v>
       </c>
       <c r="T124" t="n">
-        <v>1.634106389269156</v>
+        <v>2.034106389269156</v>
       </c>
       <c r="U124" t="n">
-        <v>-0.3864922449876012</v>
+        <v>0.6135077550123987</v>
       </c>
       <c r="V124">
         <f>T124-R124</f>
@@ -16597,22 +16597,22 @@
         <v>0.7286705941202097</v>
       </c>
       <c r="P125" t="n">
-        <v>0.700464833465681</v>
+        <v>0.2004648334656811</v>
       </c>
       <c r="Q125" t="n">
-        <v>0.3319058694876608</v>
+        <v>-0.06809413051233919</v>
       </c>
       <c r="R125" t="n">
-        <v>-0.6645965659787071</v>
+        <v>-0.1645965659787072</v>
       </c>
       <c r="S125" t="n">
-        <v>1.255434059847226</v>
+        <v>1.755434059847225</v>
       </c>
       <c r="T125" t="n">
-        <v>1.623993023825246</v>
+        <v>2.023993023825246</v>
       </c>
       <c r="U125" t="n">
-        <v>-0.5036761294837411</v>
+        <v>-0.003676129483741186</v>
       </c>
       <c r="V125">
         <f>T125-R125</f>
@@ -16720,22 +16720,22 @@
         <v>0.7914021027863789</v>
       </c>
       <c r="P126" t="n">
-        <v>0.7413128178084062</v>
+        <v>0.7413128178084063</v>
       </c>
       <c r="Q126" t="n">
-        <v>0.3876163722511878</v>
+        <v>-0.01238362774881223</v>
       </c>
       <c r="R126" t="n">
-        <v>-0.8056218109842862</v>
+        <v>-0.8056218109842863</v>
       </c>
       <c r="S126" t="n">
-        <v>-0.1766858952885751</v>
+        <v>-0.1766858952885753</v>
       </c>
       <c r="T126" t="n">
-        <v>0.1770105502686433</v>
+        <v>0.5770105502686432</v>
       </c>
       <c r="U126" t="n">
-        <v>-0.6071577243387841</v>
+        <v>-0.6071577243387842</v>
       </c>
       <c r="V126">
         <f>T126-R126</f>
@@ -16843,22 +16843,22 @@
         <v>0.9184223589767252</v>
       </c>
       <c r="P127" t="n">
-        <v>0.7790364612606893</v>
+        <v>0.7790364612606894</v>
       </c>
       <c r="Q127" t="n">
-        <v>0.458016887677135</v>
+        <v>0.058016887677135</v>
       </c>
       <c r="R127" t="n">
-        <v>-0.8669542351768517</v>
+        <v>-0.8669542351768518</v>
       </c>
       <c r="S127" t="n">
-        <v>-0.3025240667339552</v>
+        <v>-0.3025240667339553</v>
       </c>
       <c r="T127" t="n">
-        <v>0.01849550684959911</v>
+        <v>0.4184955068495991</v>
       </c>
       <c r="U127" t="n">
-        <v>-0.669346122092556</v>
+        <v>-0.6693461220925561</v>
       </c>
       <c r="V127">
         <f>T127-R127</f>
@@ -16966,22 +16966,22 @@
         <v>0.9334612588769344</v>
       </c>
       <c r="P128" t="n">
-        <v>0.842989078690062</v>
+        <v>0.8429890786900621</v>
       </c>
       <c r="Q128" t="n">
-        <v>0.5217861946078701</v>
+        <v>0.1217861946078701</v>
       </c>
       <c r="R128" t="n">
-        <v>-0.9736879187597068</v>
+        <v>-0.9736879187597069</v>
       </c>
       <c r="S128" t="n">
-        <v>-0.3401037930664045</v>
+        <v>-0.3401037930664046</v>
       </c>
       <c r="T128" t="n">
-        <v>-0.01890090898421259</v>
+        <v>0.3810990910157874</v>
       </c>
       <c r="U128" t="n">
-        <v>-0.7197610837603677</v>
+        <v>-0.7197610837603678</v>
       </c>
       <c r="V128">
         <f>T128-R128</f>
@@ -17089,22 +17089,22 @@
         <v>0.919317361322243</v>
       </c>
       <c r="P129" t="n">
-        <v>0.8906507704905704</v>
+        <v>0.8906507704905705</v>
       </c>
       <c r="Q129" t="n">
-        <v>0.5888971734156405</v>
+        <v>0.1888971734156404</v>
       </c>
       <c r="R129" t="n">
-        <v>-0.9180918280395171</v>
+        <v>-0.9180918280395172</v>
       </c>
       <c r="S129" t="n">
         <v>-0.6111512656247948</v>
       </c>
       <c r="T129" t="n">
-        <v>-0.3093976685498649</v>
+        <v>0.09060233145013522</v>
       </c>
       <c r="U129" t="n">
-        <v>-0.6912654281841148</v>
+        <v>-0.6912654281841151</v>
       </c>
       <c r="V129">
         <f>T129-R129</f>
@@ -17212,22 +17212,22 @@
         <v>0.8537094311227493</v>
       </c>
       <c r="P130" t="n">
-        <v>0.9062276025746629</v>
+        <v>0.9062276025746631</v>
       </c>
       <c r="Q130" t="n">
-        <v>0.6429883066672579</v>
+        <v>0.2429883066672579</v>
       </c>
       <c r="R130" t="n">
         <v>-1.02826022365315</v>
       </c>
       <c r="S130" t="n">
-        <v>-0.3899716500146452</v>
+        <v>-0.3899716500146453</v>
       </c>
       <c r="T130" t="n">
-        <v>-0.1267323541072402</v>
+        <v>0.2732676458927599</v>
       </c>
       <c r="U130" t="n">
-        <v>-0.8279168604804061</v>
+        <v>-0.8279168604804062</v>
       </c>
       <c r="V130">
         <f>T130-R130</f>
@@ -17335,22 +17335,22 @@
         <v>0.6345113139861668</v>
       </c>
       <c r="P131" t="n">
-        <v>0.8352498413270234</v>
+        <v>0.8352498413270235</v>
       </c>
       <c r="Q131" t="n">
-        <v>0.6720152087574542</v>
+        <v>0.2720152087574543</v>
       </c>
       <c r="R131" t="n">
-        <v>-0.9336444576284766</v>
+        <v>-0.9336444576284767</v>
       </c>
       <c r="S131" t="n">
-        <v>-0.6984857401499552</v>
+        <v>-0.6984857401499553</v>
       </c>
       <c r="T131" t="n">
-        <v>-0.5352511075803861</v>
+        <v>-0.1352511075803861</v>
       </c>
       <c r="U131" t="n">
-        <v>-0.7261808383344442</v>
+        <v>-0.7261808383344444</v>
       </c>
       <c r="V131">
         <f>T131-R131</f>
@@ -17458,22 +17458,22 @@
         <v>0.6542880067975776</v>
       </c>
       <c r="P132" t="n">
-        <v>0.7654565283071841</v>
+        <v>0.7654565283071844</v>
       </c>
       <c r="Q132" t="n">
-        <v>0.6967156214941814</v>
+        <v>0.2967156214941814</v>
       </c>
       <c r="R132" t="n">
-        <v>-0.852010855923254</v>
+        <v>-0.8520108559232542</v>
       </c>
       <c r="S132" t="n">
-        <v>-0.424357196663796</v>
+        <v>-0.4243571966637962</v>
       </c>
       <c r="T132" t="n">
-        <v>-0.3556162898507932</v>
+        <v>0.04438371014920678</v>
       </c>
       <c r="U132" t="n">
-        <v>-0.6506844845801283</v>
+        <v>-0.6506844845801285</v>
       </c>
       <c r="V132">
         <f>T132-R132</f>
@@ -17584,7 +17584,7 @@
         <v>0.6957106876521879</v>
       </c>
       <c r="Q133" t="n">
-        <v>0.7055949920005039</v>
+        <v>0.3055949920005039</v>
       </c>
       <c r="R133" t="n">
         <v>-0.8266939843586186</v>
@@ -17593,7 +17593,7 @@
         <v>-0.1815171242645203</v>
       </c>
       <c r="T133" t="n">
-        <v>-0.1914014286128363</v>
+        <v>0.2085985713871638</v>
       </c>
       <c r="U133" t="n">
         <v>-0.6327814039024851</v>
@@ -17704,22 +17704,22 @@
         <v>0.5831591027515952</v>
       </c>
       <c r="P134" t="n">
-        <v>0.6280731055593993</v>
+        <v>0.6280731055593994</v>
       </c>
       <c r="Q134" t="n">
-        <v>0.7103231580939039</v>
+        <v>0.3103231580939039</v>
       </c>
       <c r="R134" t="n">
-        <v>-0.7045162908894028</v>
+        <v>-0.7045162908894029</v>
       </c>
       <c r="S134" t="n">
-        <v>-0.05676335716272329</v>
+        <v>-0.0567633571627234</v>
       </c>
       <c r="T134" t="n">
-        <v>-0.1390134096972279</v>
+        <v>0.2609865903027721</v>
       </c>
       <c r="U134" t="n">
-        <v>-0.5369891068110515</v>
+        <v>-0.5369891068110516</v>
       </c>
       <c r="V134">
         <f>T134-R134</f>
@@ -17830,7 +17830,7 @@
         <v>0.6154655320035929</v>
       </c>
       <c r="Q135" t="n">
-        <v>0.7098533659869755</v>
+        <v>0.3098533659869756</v>
       </c>
       <c r="R135" t="n">
         <v>-0.7421381493618291</v>
@@ -17839,7 +17839,7 @@
         <v>-0.2583810273758222</v>
       </c>
       <c r="T135" t="n">
-        <v>-0.3527688613592048</v>
+        <v>0.04723113864079509</v>
       </c>
       <c r="U135" t="n">
         <v>-0.546669705690037</v>
@@ -17950,22 +17950,22 @@
         <v>0.4398831798183991</v>
       </c>
       <c r="P136" t="n">
-        <v>0.5618643252587981</v>
+        <v>0.5618643252587983</v>
       </c>
       <c r="Q136" t="n">
-        <v>0.6983629126430086</v>
+        <v>0.2983629126430086</v>
       </c>
       <c r="R136" t="n">
-        <v>-0.6824462413696085</v>
+        <v>-0.6824462413696086</v>
       </c>
       <c r="S136" t="n">
-        <v>-0.1536564455575026</v>
+        <v>-0.1536564455575027</v>
       </c>
       <c r="T136" t="n">
-        <v>-0.2901550329417131</v>
+        <v>0.1098449670582869</v>
       </c>
       <c r="U136" t="n">
-        <v>-0.5048291890691841</v>
+        <v>-0.5048291890691842</v>
       </c>
       <c r="V136">
         <f>T136-R136</f>
@@ -18073,22 +18073,22 @@
         <v>0.2863491357155914</v>
       </c>
       <c r="P137" t="n">
-        <v>0.4733681095121316</v>
+        <v>0.4733681095121317</v>
       </c>
       <c r="Q137" t="n">
-        <v>0.6758478650382767</v>
+        <v>0.2758478650382766</v>
       </c>
       <c r="R137" t="n">
-        <v>-0.5052359775219645</v>
+        <v>-0.5052359775219646</v>
       </c>
       <c r="S137" t="n">
-        <v>0.2318181213394486</v>
+        <v>0.2318181213394485</v>
       </c>
       <c r="T137" t="n">
-        <v>0.02933836581330351</v>
+        <v>0.4293383658133035</v>
       </c>
       <c r="U137" t="n">
-        <v>-0.342745443689659</v>
+        <v>-0.3427454436896591</v>
       </c>
       <c r="V137">
         <f>T137-R137</f>
@@ -18196,22 +18196,22 @@
         <v>0.1790022113820543</v>
       </c>
       <c r="P138" t="n">
-        <v>0.3723288866697464</v>
+        <v>0.3723288866697465</v>
       </c>
       <c r="Q138" t="n">
-        <v>0.6485412530040977</v>
+        <v>0.2485412530040977</v>
       </c>
       <c r="R138" t="n">
-        <v>-0.5243581892953679</v>
+        <v>-0.5243581892953681</v>
       </c>
       <c r="S138" t="n">
-        <v>0.0272387975473643</v>
+        <v>0.02723879754736419</v>
       </c>
       <c r="T138" t="n">
-        <v>-0.248973568786987</v>
+        <v>0.151026431213013</v>
       </c>
       <c r="U138" t="n">
-        <v>-0.3090215348589421</v>
+        <v>-0.3090215348589422</v>
       </c>
       <c r="V138">
         <f>T138-R138</f>
@@ -18322,19 +18322,19 @@
         <v>0.2780846880934637</v>
       </c>
       <c r="Q139" t="n">
-        <v>0.6294104409954373</v>
+        <v>0.3294104409954373</v>
       </c>
       <c r="R139" t="n">
-        <v>-0.4987237046399381</v>
+        <v>-0.4987237046399382</v>
       </c>
       <c r="S139" t="n">
-        <v>0.3255683266003603</v>
+        <v>0.3255683266003602</v>
       </c>
       <c r="T139" t="n">
-        <v>-0.02575742630161337</v>
+        <v>0.2742425736983866</v>
       </c>
       <c r="U139" t="n">
-        <v>-0.286985764841941</v>
+        <v>-0.2869857648419411</v>
       </c>
       <c r="V139">
         <f>T139-R139</f>
@@ -18442,22 +18442,22 @@
         <v>0.3043324184573253</v>
       </c>
       <c r="P140" t="n">
-        <v>0.2441969977531952</v>
+        <v>0.2441969977531953</v>
       </c>
       <c r="Q140" t="n">
-        <v>0.6124961615268409</v>
+        <v>0.4124961615268409</v>
       </c>
       <c r="R140" t="n">
         <v>-0.2636501480026004</v>
       </c>
       <c r="S140" t="n">
-        <v>0.3361578666797649</v>
+        <v>0.3361578666797648</v>
       </c>
       <c r="T140" t="n">
-        <v>-0.03214129709388092</v>
+        <v>0.1678587029061191</v>
       </c>
       <c r="U140" t="n">
-        <v>-0.1172513733436428</v>
+        <v>-0.1172513733436429</v>
       </c>
       <c r="V140">
         <f>T140-R140</f>
@@ -18559,28 +18559,28 @@
         <v>4.157000237251395</v>
       </c>
       <c r="N141" t="n">
-        <v>0.605098513338886</v>
+        <v>0.105098513338886</v>
       </c>
       <c r="O141" t="n">
-        <v>0.605098513338886</v>
+        <v>0.105098513338886</v>
       </c>
       <c r="P141" t="n">
-        <v>0.3238843421590188</v>
+        <v>0.1988843421590189</v>
       </c>
       <c r="Q141" t="n">
-        <v>0.6168157486559179</v>
+        <v>0.4918157486559179</v>
       </c>
       <c r="R141" t="n">
-        <v>-0.2964179445286688</v>
+        <v>-0.1714179445286688</v>
       </c>
       <c r="S141" t="n">
-        <v>0.3443856731594579</v>
+        <v>0.4693856731594578</v>
       </c>
       <c r="T141" t="n">
-        <v>0.05145426666255881</v>
+        <v>0.1764542666625588</v>
       </c>
       <c r="U141" t="n">
-        <v>-0.1000984836535226</v>
+        <v>0.02490151634647739</v>
       </c>
       <c r="V141">
         <f>T141-R141</f>
@@ -18682,28 +18682,28 @@
         <v>3.40781991582935</v>
       </c>
       <c r="N142" t="n">
-        <v>0.7718518245561539</v>
+        <v>0.2718518245561539</v>
       </c>
       <c r="O142" t="n">
-        <v>0.7718518245561539</v>
+        <v>0.2718518245561539</v>
       </c>
       <c r="P142" t="n">
-        <v>0.4720967454525438</v>
+        <v>0.2220967454525438</v>
       </c>
       <c r="Q142" t="n">
-        <v>0.6240078316129517</v>
+        <v>0.5740078316129518</v>
       </c>
       <c r="R142" t="n">
-        <v>-0.5923602087250103</v>
+        <v>-0.3423602087250103</v>
       </c>
       <c r="S142" t="n">
-        <v>0.1693272311248504</v>
+        <v>0.4193272311248504</v>
       </c>
       <c r="T142" t="n">
-        <v>0.01741614496444244</v>
+        <v>0.06741614496444237</v>
       </c>
       <c r="U142" t="n">
-        <v>-0.3624891671480127</v>
+        <v>-0.1124891671480127</v>
       </c>
       <c r="V142">
         <f>T142-R142</f>
@@ -18805,28 +18805,28 @@
         <v>-0.4944618658596482</v>
       </c>
       <c r="N143" t="n">
-        <v>0.7340956372009819</v>
+        <v>0.2340956372009819</v>
       </c>
       <c r="O143" t="n">
-        <v>0.7340956372009819</v>
+        <v>0.2340956372009819</v>
       </c>
       <c r="P143" t="n">
-        <v>0.6038445983883367</v>
+        <v>0.2288445983883368</v>
       </c>
       <c r="Q143" t="n">
-        <v>0.6223362242146211</v>
+        <v>0.5473362242146212</v>
       </c>
       <c r="R143" t="n">
-        <v>-0.800686500419346</v>
+        <v>-0.4256865004193461</v>
       </c>
       <c r="S143" t="n">
-        <v>-0.1875837888000041</v>
+        <v>0.1874162111999958</v>
       </c>
       <c r="T143" t="n">
-        <v>-0.2060754146262885</v>
+        <v>-0.1310754146262886</v>
       </c>
       <c r="U143" t="n">
-        <v>-0.5689097882524564</v>
+        <v>-0.1939097882524566</v>
       </c>
       <c r="V143">
         <f>T143-R143</f>
@@ -18928,28 +18928,28 @@
         <v>0.09250505009913468</v>
       </c>
       <c r="N144" t="n">
-        <v>0.7821631401334608</v>
+        <v>0.2821631401334608</v>
       </c>
       <c r="O144" t="n">
-        <v>0.7821631401334608</v>
+        <v>0.2821631401334608</v>
       </c>
       <c r="P144" t="n">
-        <v>0.7233022788073706</v>
+        <v>0.2233022788073707</v>
       </c>
       <c r="Q144" t="n">
-        <v>0.627561841763322</v>
+        <v>0.5275618417633221</v>
       </c>
       <c r="R144" t="n">
-        <v>-0.8388264776171679</v>
+        <v>-0.3388264776171679</v>
       </c>
       <c r="S144" t="n">
-        <v>-0.339060875686248</v>
+        <v>0.1609391243137519</v>
       </c>
       <c r="T144" t="n">
-        <v>-0.2433204386421994</v>
+        <v>-0.1433204386421995</v>
       </c>
       <c r="U144" t="n">
-        <v>-0.6080513723306107</v>
+        <v>-0.1080513723306108</v>
       </c>
       <c r="V144">
         <f>T144-R144</f>
@@ -19057,22 +19057,22 @@
         <v>0.6063399352249725</v>
       </c>
       <c r="P145" t="n">
-        <v>0.7236126342788922</v>
+        <v>0.3486126342788923</v>
       </c>
       <c r="Q145" t="n">
-        <v>0.6214453088185602</v>
+        <v>0.5214453088185602</v>
       </c>
       <c r="R145" t="n">
-        <v>-0.8379237817709256</v>
+        <v>-0.4629237817709257</v>
       </c>
       <c r="S145" t="n">
-        <v>-0.2488965269403547</v>
+        <v>0.1261034730596451</v>
       </c>
       <c r="T145" t="n">
-        <v>-0.1467292014800227</v>
+        <v>-0.04672920148002274</v>
       </c>
       <c r="U145" t="n">
-        <v>-0.6367563855638819</v>
+        <v>-0.261756385563882</v>
       </c>
       <c r="V145">
         <f>T145-R145</f>
@@ -19180,22 +19180,22 @@
         <v>0.5020631446289181</v>
       </c>
       <c r="P146" t="n">
-        <v>0.6561654642970833</v>
+        <v>0.4061654642970834</v>
       </c>
       <c r="Q146" t="n">
-        <v>0.6069783609106871</v>
+        <v>0.5069783609106872</v>
       </c>
       <c r="R146" t="n">
-        <v>-0.7656616563481962</v>
+        <v>-0.5156616563481963</v>
       </c>
       <c r="S146" t="n">
-        <v>-0.1692227299672053</v>
+        <v>0.08077727003279456</v>
       </c>
       <c r="T146" t="n">
-        <v>-0.1200356265808091</v>
+        <v>-0.02003562658080915</v>
       </c>
       <c r="U146" t="n">
-        <v>-0.5910130161872708</v>
+        <v>-0.3410130161872709</v>
       </c>
       <c r="V146">
         <f>T146-R146</f>
@@ -19303,22 +19303,22 @@
         <v>0.5881194020606938</v>
       </c>
       <c r="P147" t="n">
-        <v>0.6196714055120114</v>
+        <v>0.4946714055120114</v>
       </c>
       <c r="Q147" t="n">
-        <v>0.5904632130648856</v>
+        <v>0.4904632130648857</v>
       </c>
       <c r="R147" t="n">
-        <v>-0.7753408076081038</v>
+        <v>-0.6503408076081038</v>
       </c>
       <c r="S147" t="n">
-        <v>-0.3118149728282604</v>
+        <v>-0.1868149728282604</v>
       </c>
       <c r="T147" t="n">
-        <v>-0.2826067803811346</v>
+        <v>-0.1826067803811346</v>
       </c>
       <c r="U147" t="n">
-        <v>-0.6078517724288457</v>
+        <v>-0.4828517724288457</v>
       </c>
       <c r="V147">
         <f>T147-R147</f>
@@ -19426,22 +19426,22 @@
         <v>0.6084791019000265</v>
       </c>
       <c r="P148" t="n">
-        <v>0.5762503959536527</v>
+        <v>0.5762503959536528</v>
       </c>
       <c r="Q148" t="n">
-        <v>0.5742141052160402</v>
+        <v>0.4742141052160401</v>
       </c>
       <c r="R148" t="n">
-        <v>-0.6472723388298288</v>
+        <v>-0.6472723388298289</v>
       </c>
       <c r="S148" t="n">
-        <v>-0.07285554596391119</v>
+        <v>-0.07285554596391131</v>
       </c>
       <c r="T148" t="n">
-        <v>-0.07081925522629873</v>
+        <v>0.02918074477370136</v>
       </c>
       <c r="U148" t="n">
-        <v>-0.4369341916873181</v>
+        <v>-0.4369341916873182</v>
       </c>
       <c r="V148">
         <f>T148-R148</f>
@@ -19549,22 +19549,22 @@
         <v>0.6135655833349997</v>
       </c>
       <c r="P149" t="n">
-        <v>0.5780568079811595</v>
+        <v>0.5780568079811597</v>
       </c>
       <c r="Q149" t="n">
-        <v>0.558926516316678</v>
+        <v>0.458926516316678</v>
       </c>
       <c r="R149" t="n">
-        <v>-0.6518314392168552</v>
+        <v>-0.6518314392168553</v>
       </c>
       <c r="S149" t="n">
-        <v>-0.126050648616599</v>
+        <v>-0.1260506486165991</v>
       </c>
       <c r="T149" t="n">
-        <v>-0.1069203569521175</v>
+        <v>-0.006920356952117457</v>
       </c>
       <c r="U149" t="n">
-        <v>-0.4404530381859003</v>
+        <v>-0.4404530381859004</v>
       </c>
       <c r="V149">
         <f>T149-R149</f>
@@ -19672,22 +19672,22 @@
         <v>1.214681736143084</v>
       </c>
       <c r="P150" t="n">
-        <v>0.7562114558597008</v>
+        <v>0.756211455859701</v>
       </c>
       <c r="Q150" t="n">
-        <v>0.5769751315676948</v>
+        <v>0.4769751315676947</v>
       </c>
       <c r="R150" t="n">
-        <v>-0.9309317368506661</v>
+        <v>-0.9309317368506662</v>
       </c>
       <c r="S150" t="n">
-        <v>-0.2384959611319227</v>
+        <v>-0.2384959611319228</v>
       </c>
       <c r="T150" t="n">
-        <v>-0.05925963683991664</v>
+        <v>0.04074036316008339</v>
       </c>
       <c r="U150" t="n">
-        <v>-0.6923118035025142</v>
+        <v>-0.6923118035025143</v>
       </c>
       <c r="V150">
         <f>T150-R150</f>
@@ -19798,19 +19798,19 @@
         <v>1.01296584171359</v>
       </c>
       <c r="Q151" t="n">
-        <v>0.6260064131421988</v>
+        <v>0.5260064131421989</v>
       </c>
       <c r="R151" t="n">
-        <v>-1.078006005128845</v>
+        <v>-1.078006005128846</v>
       </c>
       <c r="S151" t="n">
-        <v>-0.47454481771032</v>
+        <v>-0.4745448177103202</v>
       </c>
       <c r="T151" t="n">
-        <v>-0.08758538913892899</v>
+        <v>0.01241461086107098</v>
       </c>
       <c r="U151" t="n">
-        <v>-0.8450066156185829</v>
+        <v>-0.8450066156185831</v>
       </c>
       <c r="V151">
         <f>T151-R151</f>
@@ -19921,19 +19921,19 @@
         <v>1.37813970158365</v>
       </c>
       <c r="Q152" t="n">
-        <v>0.6967507398713334</v>
+        <v>0.5967507398713333</v>
       </c>
       <c r="R152" t="n">
         <v>-1.375505452486355</v>
       </c>
       <c r="S152" t="n">
-        <v>-0.803785027401112</v>
+        <v>-0.8037850274011122</v>
       </c>
       <c r="T152" t="n">
-        <v>-0.1223960656887958</v>
+        <v>-0.02239606568879571</v>
       </c>
       <c r="U152" t="n">
-        <v>-1.17947231218229</v>
+        <v>-1.179472312182291</v>
       </c>
       <c r="V152">
         <f>T152-R152</f>
@@ -20044,7 +20044,7 @@
         <v>1.922109420041463</v>
       </c>
       <c r="Q153" t="n">
-        <v>0.8042062627945331</v>
+        <v>0.7042062627945331</v>
       </c>
       <c r="R153" t="n">
         <v>-2.01351140341961</v>
@@ -20053,7 +20053,7 @@
         <v>-1.424129596481868</v>
       </c>
       <c r="T153" t="n">
-        <v>-0.3062264392349378</v>
+        <v>-0.2062264392349378</v>
       </c>
       <c r="U153" t="n">
         <v>-1.850837579785436</v>
@@ -20167,7 +20167,7 @@
         <v>2.300035629232711</v>
       </c>
       <c r="Q154" t="n">
-        <v>0.9113676363023571</v>
+        <v>0.811367636302357</v>
       </c>
       <c r="R154" t="n">
         <v>-2.416901887336136</v>
@@ -20176,7 +20176,7 @@
         <v>-1.794589685495519</v>
       </c>
       <c r="T154" t="n">
-        <v>-0.4059216925651657</v>
+        <v>-0.3059216925651657</v>
       </c>
       <c r="U154" t="n">
         <v>-2.226475085246463</v>
@@ -20287,19 +20287,19 @@
         <v>2.919523027864217</v>
       </c>
       <c r="P155" t="n">
-        <v>2.626132149829702</v>
+        <v>2.626132149829703</v>
       </c>
       <c r="Q155" t="n">
-        <v>1.028139736707421</v>
+        <v>0.9281397367074208</v>
       </c>
       <c r="R155" t="n">
-        <v>-2.733232310550078</v>
+        <v>-2.733232310550079</v>
       </c>
       <c r="S155" t="n">
-        <v>-2.0715508905811</v>
+        <v>-2.071550890581101</v>
       </c>
       <c r="T155" t="n">
-        <v>-0.4735584774588188</v>
+        <v>-0.3735584774588189</v>
       </c>
       <c r="U155" t="n">
         <v>-2.526715374705763</v>
@@ -20413,7 +20413,7 @@
         <v>2.840316417372145</v>
       </c>
       <c r="Q156" t="n">
-        <v>1.152441158294003</v>
+        <v>1.052441158294003</v>
       </c>
       <c r="R156" t="n">
         <v>-2.909553579023717</v>
@@ -20422,10 +20422,10 @@
         <v>-2.409524801890655</v>
       </c>
       <c r="T156" t="n">
-        <v>-0.7216495428125127</v>
+        <v>-0.6216495428125128</v>
       </c>
       <c r="U156" t="n">
-        <v>-2.715616076385399</v>
+        <v>-2.7156160763854</v>
       </c>
       <c r="V156">
         <f>T156-R156</f>
@@ -20533,19 +20533,19 @@
         <v>2.774644364205084</v>
       </c>
       <c r="P157" t="n">
-        <v>2.836616394131852</v>
+        <v>2.836616394131853</v>
       </c>
       <c r="Q157" t="n">
-        <v>1.276855919718477</v>
+        <v>1.176855919718477</v>
       </c>
       <c r="R157" t="n">
-        <v>-3.023149974407213</v>
+        <v>-3.023149974407214</v>
       </c>
       <c r="S157" t="n">
-        <v>-2.52730873766934</v>
+        <v>-2.527308737669341</v>
       </c>
       <c r="T157" t="n">
-        <v>-0.9675482632559654</v>
+        <v>-0.8675482632559656</v>
       </c>
       <c r="U157" t="n">
         <v>-2.840486797649543</v>
@@ -20656,22 +20656,22 @@
         <v>2.753654643928737</v>
       </c>
       <c r="P158" t="n">
-        <v>2.843433411887018</v>
+        <v>2.843433411887019</v>
       </c>
       <c r="Q158" t="n">
-        <v>1.405588541345811</v>
+        <v>1.305588541345811</v>
       </c>
       <c r="R158" t="n">
-        <v>-2.585213876738153</v>
+        <v>-2.585213876738154</v>
       </c>
       <c r="S158" t="n">
         <v>-1.4747459551979</v>
       </c>
       <c r="T158" t="n">
-        <v>-0.03690108465669284</v>
+        <v>0.06309891534330703</v>
       </c>
       <c r="U158" t="n">
-        <v>-2.377627332289056</v>
+        <v>-2.377627332289057</v>
       </c>
       <c r="V158">
         <f>T158-R158</f>
@@ -20782,7 +20782,7 @@
         <v>2.771898401757454</v>
       </c>
       <c r="Q159" t="n">
-        <v>1.526902479440219</v>
+        <v>1.426902479440219</v>
       </c>
       <c r="R159" t="n">
         <v>-2.503921599230595</v>
@@ -20791,7 +20791,7 @@
         <v>-1.545155286451068</v>
       </c>
       <c r="T159" t="n">
-        <v>-0.3001593641338325</v>
+        <v>-0.2001593641338324</v>
       </c>
       <c r="U159" t="n">
         <v>-2.319040331472913</v>
@@ -20905,16 +20905,16 @@
         <v>2.682434947427085</v>
       </c>
       <c r="Q160" t="n">
-        <v>1.640088748228781</v>
+        <v>1.540088748228781</v>
       </c>
       <c r="R160" t="n">
         <v>-2.265043696779283</v>
       </c>
       <c r="S160" t="n">
-        <v>-1.40672790603897</v>
+        <v>-1.406727906038971</v>
       </c>
       <c r="T160" t="n">
-        <v>-0.3643817068406658</v>
+        <v>-0.2643817068406658</v>
       </c>
       <c r="U160" t="n">
         <v>-2.083885679291044</v>
@@ -21028,7 +21028,7 @@
         <v>2.627966884875975</v>
       </c>
       <c r="Q161" t="n">
-        <v>1.737672428261868</v>
+        <v>1.662672428261869</v>
       </c>
       <c r="R161" t="n">
         <v>-2.274175521566223</v>
@@ -21037,7 +21037,7 @@
         <v>-1.229794250627912</v>
       </c>
       <c r="T161" t="n">
-        <v>-0.3394997940138056</v>
+        <v>-0.2644997940138061</v>
       </c>
       <c r="U161" t="n">
         <v>-2.06483193653712</v>
@@ -21151,7 +21151,7 @@
         <v>2.563844614991581</v>
       </c>
       <c r="Q162" t="n">
-        <v>1.823938115253619</v>
+        <v>1.773938115253619</v>
       </c>
       <c r="R162" t="n">
         <v>-2.080450234435605</v>
@@ -21160,7 +21160,7 @@
         <v>-1.034113253832336</v>
       </c>
       <c r="T162" t="n">
-        <v>-0.294206754094374</v>
+        <v>-0.244206754094374</v>
       </c>
       <c r="U162" t="n">
         <v>-1.892510011839481</v>
@@ -21274,7 +21274,7 @@
         <v>2.545465124580588</v>
       </c>
       <c r="Q163" t="n">
-        <v>1.915226584678669</v>
+        <v>1.890226584678669</v>
       </c>
       <c r="R163" t="n">
         <v>-2.163152159469688</v>
@@ -21283,7 +21283,7 @@
         <v>-1.316223685195359</v>
       </c>
       <c r="T163" t="n">
-        <v>-0.6859851452934402</v>
+        <v>-0.6609851452934401</v>
       </c>
       <c r="U163" t="n">
         <v>-1.955829027800338</v>
@@ -21403,13 +21403,13 @@
         <v>-2.074018400380766</v>
       </c>
       <c r="S164" t="n">
-        <v>-1.051070228834405</v>
+        <v>-1.051070228834406</v>
       </c>
       <c r="T164" t="n">
         <v>-0.4837934343249874</v>
       </c>
       <c r="U164" t="n">
-        <v>-1.865822279695202</v>
+        <v>-1.865822279695203</v>
       </c>
       <c r="V164">
         <f>T164-R164</f>
@@ -21523,7 +21523,7 @@
         <v>2.115534566670779</v>
       </c>
       <c r="R165" t="n">
-        <v>-2.084453313133886</v>
+        <v>-2.084453313133887</v>
       </c>
       <c r="S165" t="n">
         <v>-1.010895003891049</v>
@@ -21779,19 +21779,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.189891650120106</v>
+        <v>2.177721952688761</v>
       </c>
       <c r="C4" t="n">
         <v>3.704199271826353</v>
       </c>
       <c r="D4" t="n">
-        <v>1.600929458958214</v>
+        <v>2.209899652680285</v>
       </c>
       <c r="E4" t="n">
-        <v>2.718143682487966</v>
+        <v>3.534603918373683</v>
       </c>
       <c r="F4" t="n">
-        <v>2.669982087306957</v>
+        <v>1.348357550632836</v>
       </c>
     </row>
     <row r="5">
@@ -21801,22 +21801,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.190447218164243</v>
+        <v>2.178316778208431</v>
       </c>
       <c r="C5" t="n">
         <v>3.704047735573145</v>
       </c>
       <c r="D5" t="n">
-        <v>1.601303527555404</v>
+        <v>2.210144668538561</v>
       </c>
       <c r="E5" t="n">
-        <v>2.717990697044214</v>
+        <v>3.534843192677726</v>
       </c>
       <c r="F5" t="n">
-        <v>2.669749703933348</v>
+        <v>1.340015600903558</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1260408596170537</v>
+        <v>2.56475200456449</v>
       </c>
     </row>
     <row r="6">
@@ -21826,22 +21826,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.188500886490559</v>
+        <v>2.176917346886104</v>
       </c>
       <c r="C6" t="n">
         <v>3.703592982563218</v>
       </c>
       <c r="D6" t="n">
-        <v>1.598855270361571</v>
+        <v>2.207900507332232</v>
       </c>
       <c r="E6" t="n">
-        <v>2.715392604877904</v>
+        <v>3.532594357250866</v>
       </c>
       <c r="F6" t="n">
-        <v>2.669098371687085</v>
+        <v>1.301526808515882</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0975428846689432</v>
+        <v>2.530152184667296</v>
       </c>
     </row>
     <row r="7">
@@ -21851,22 +21851,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.183704018445536</v>
+        <v>2.171420156348566</v>
       </c>
       <c r="C7" t="n">
         <v>3.702728773953192</v>
       </c>
       <c r="D7" t="n">
-        <v>1.592861023364508</v>
+        <v>2.201980994102293</v>
       </c>
       <c r="E7" t="n">
-        <v>2.709451361381313</v>
+        <v>3.526670023679725</v>
       </c>
       <c r="F7" t="n">
-        <v>2.667854680422479</v>
+        <v>1.270810094283085</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0965917185550209</v>
+        <v>2.533112716370969</v>
       </c>
     </row>
     <row r="8">
@@ -21876,22 +21876,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.179532408884269</v>
+        <v>2.169754255581379</v>
       </c>
       <c r="C8" t="n">
         <v>3.701362331830191</v>
       </c>
       <c r="D8" t="n">
-        <v>1.590126692019528</v>
+        <v>2.199483727228649</v>
       </c>
       <c r="E8" t="n">
-        <v>2.706370467296889</v>
+        <v>3.524166521781209</v>
       </c>
       <c r="F8" t="n">
-        <v>2.665881006259332</v>
+        <v>1.24568660653752</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0358516745092611</v>
+        <v>2.501652250543098</v>
       </c>
     </row>
     <row r="9">
@@ -21901,22 +21901,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.175344893983689</v>
+        <v>2.169812704178902</v>
       </c>
       <c r="C9" t="n">
         <v>3.699387075888097</v>
       </c>
       <c r="D9" t="n">
-        <v>1.589370518170815</v>
+        <v>2.198284616935769</v>
       </c>
       <c r="E9" t="n">
-        <v>2.705137618200976</v>
+        <v>3.522961112525897</v>
       </c>
       <c r="F9" t="n">
-        <v>2.663031039818183</v>
+        <v>1.240310372230619</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0345884487796335</v>
+        <v>2.534568529651569</v>
       </c>
     </row>
     <row r="10">
@@ -21926,22 +21926,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.168719609259084</v>
+        <v>2.166680050690169</v>
       </c>
       <c r="C10" t="n">
         <v>3.696701321823354</v>
       </c>
       <c r="D10" t="n">
-        <v>1.586382707390485</v>
+        <v>2.194043770983817</v>
       </c>
       <c r="E10" t="n">
-        <v>2.701819704182037</v>
+        <v>3.518714743570131</v>
       </c>
       <c r="F10" t="n">
-        <v>2.659162286155225</v>
+        <v>1.225902398706423</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0179865256749753</v>
+        <v>2.52388065600452</v>
       </c>
     </row>
     <row r="11">
@@ -21951,22 +21951,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.159430616546703</v>
+        <v>2.160637998585528</v>
       </c>
       <c r="C11" t="n">
         <v>3.693211176000598</v>
       </c>
       <c r="D11" t="n">
-        <v>1.582102566891606</v>
+        <v>2.187450846979961</v>
       </c>
       <c r="E11" t="n">
-        <v>2.697181702725392</v>
+        <v>3.512117161127158</v>
       </c>
       <c r="F11" t="n">
-        <v>2.654160620138721</v>
+        <v>1.216439577320639</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0337865290468613</v>
+        <v>2.532823188427562</v>
       </c>
     </row>
     <row r="12">
@@ -21976,22 +21976,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.147634803552198</v>
+        <v>2.151458345899762</v>
       </c>
       <c r="C12" t="n">
         <v>3.688854835180576</v>
       </c>
       <c r="D12" t="n">
-        <v>1.575545001627447</v>
+        <v>2.177741737609594</v>
       </c>
       <c r="E12" t="n">
-        <v>2.690353288005874</v>
+        <v>3.5024039882625</v>
       </c>
       <c r="F12" t="n">
-        <v>2.647933695623552</v>
+        <v>1.213434272773972</v>
       </c>
       <c r="G12" t="n">
-        <v>0.07855713527755979</v>
+        <v>2.578625672371654</v>
       </c>
     </row>
     <row r="13">
@@ -22001,22 +22001,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.13373373873255</v>
+        <v>2.140704567301118</v>
       </c>
       <c r="C13" t="n">
         <v>3.683574737452496</v>
       </c>
       <c r="D13" t="n">
-        <v>1.568240753527408</v>
+        <v>2.166915702905733</v>
       </c>
       <c r="E13" t="n">
-        <v>2.682730092795138</v>
+        <v>3.491575013245078</v>
       </c>
       <c r="F13" t="n">
-        <v>2.640415684573156</v>
+        <v>1.182886211490589</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0757869359993304</v>
+        <v>2.527005570518888</v>
       </c>
     </row>
     <row r="14">
@@ -22026,22 +22026,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.115809293586513</v>
+        <v>2.12383145988612</v>
       </c>
       <c r="C14" t="n">
         <v>3.677310803238674</v>
       </c>
       <c r="D14" t="n">
-        <v>1.556488457230278</v>
+        <v>2.150546875676456</v>
       </c>
       <c r="E14" t="n">
-        <v>2.67098691945715</v>
+        <v>3.475205408009893</v>
       </c>
       <c r="F14" t="n">
-        <v>2.631552807021396</v>
+        <v>1.174458782509249</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0512496486744027</v>
+        <v>2.535659425448616</v>
       </c>
     </row>
     <row r="15">
@@ -22051,22 +22051,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.093854762447159</v>
+        <v>2.101110580770969</v>
       </c>
       <c r="C15" t="n">
         <v>3.67003370590148</v>
       </c>
       <c r="D15" t="n">
-        <v>1.54040105804124</v>
+        <v>2.129074727327276</v>
       </c>
       <c r="E15" t="n">
-        <v>2.655108396317335</v>
+        <v>3.453734160810743</v>
       </c>
       <c r="F15" t="n">
-        <v>2.62132983944717</v>
+        <v>1.15969460417526</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0175076879362832</v>
+        <v>2.520064680399651</v>
       </c>
     </row>
     <row r="16">
@@ -22076,22 +22076,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.068870563326998</v>
+        <v>2.07485995013801</v>
       </c>
       <c r="C16" t="n">
         <v>3.661761584127795</v>
       </c>
       <c r="D16" t="n">
-        <v>1.522107123116938</v>
+        <v>2.104719053581218</v>
       </c>
       <c r="E16" t="n">
-        <v>2.637077435383762</v>
+        <v>3.429381157065109</v>
       </c>
       <c r="F16" t="n">
-        <v>2.609766130551364</v>
+        <v>1.129015202505949</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0180516486011284</v>
+        <v>2.456796477819112</v>
       </c>
     </row>
     <row r="17">
@@ -22101,22 +22101,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.040302164908797</v>
+        <v>2.042924138950046</v>
       </c>
       <c r="C17" t="n">
         <v>3.652548717586725</v>
       </c>
       <c r="D17" t="n">
-        <v>1.499869989740031</v>
+        <v>2.075302720544455</v>
       </c>
       <c r="E17" t="n">
-        <v>2.615349863603518</v>
+        <v>3.399969420299173</v>
       </c>
       <c r="F17" t="n">
-        <v>2.596901076951574</v>
+        <v>1.121564061908328</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0021354430092943</v>
+        <v>2.470750299414413</v>
       </c>
     </row>
     <row r="18">
@@ -22126,22 +22126,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.009702727467696</v>
+        <v>2.00815343705289</v>
       </c>
       <c r="C18" t="n">
         <v>3.642452930951761</v>
       </c>
       <c r="D18" t="n">
-        <v>1.475317005685064</v>
+        <v>2.043270274548694</v>
       </c>
       <c r="E18" t="n">
-        <v>2.591354835406483</v>
+        <v>3.367942107786765</v>
       </c>
       <c r="F18" t="n">
-        <v>2.582807865942649</v>
+        <v>1.11443315358119</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0266936957938512</v>
+        <v>2.478082262090729</v>
       </c>
     </row>
     <row r="19">
@@ -22151,22 +22151,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.979243716935558</v>
+        <v>1.974858358192204</v>
       </c>
       <c r="C19" t="n">
         <v>3.631541510154553</v>
       </c>
       <c r="D19" t="n">
-        <v>1.452064404509695</v>
+        <v>2.012806204862389</v>
       </c>
       <c r="E19" t="n">
-        <v>2.568487001195752</v>
+        <v>3.337483325981761</v>
       </c>
       <c r="F19" t="n">
-        <v>2.567578849634717</v>
+        <v>1.097878235558695</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0066223612034019</v>
+        <v>2.441122700238044</v>
       </c>
     </row>
     <row r="20">
@@ -22176,22 +22176,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.948855202445783</v>
+        <v>1.941444555288562</v>
       </c>
       <c r="C20" t="n">
         <v>3.619881522975725</v>
       </c>
       <c r="D20" t="n">
-        <v>1.427935867313657</v>
+        <v>1.981636722745642</v>
       </c>
       <c r="E20" t="n">
-        <v>2.544854551189405</v>
+        <v>3.306318922476326</v>
       </c>
       <c r="F20" t="n">
-        <v>2.551299803168966</v>
+        <v>1.088178313616716</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0231104152809987</v>
+        <v>2.412505959111927</v>
       </c>
     </row>
     <row r="21">
@@ -22201,22 +22201,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.919636450125448</v>
+        <v>1.911143332745917</v>
       </c>
       <c r="C21" t="n">
         <v>3.607564872832095</v>
       </c>
       <c r="D21" t="n">
-        <v>1.40693347590827</v>
+        <v>1.953642287630632</v>
       </c>
       <c r="E21" t="n">
-        <v>2.524038553873228</v>
+        <v>3.278329350014131</v>
       </c>
       <c r="F21" t="n">
-        <v>2.5340655476405</v>
+        <v>1.092414188838025</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0236941106764547</v>
+        <v>2.449032602254631</v>
       </c>
     </row>
     <row r="22">
@@ -22226,22 +22226,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.890461305144194</v>
+        <v>1.880424265108846</v>
       </c>
       <c r="C22" t="n">
         <v>3.594654977261091</v>
       </c>
       <c r="D22" t="n">
-        <v>1.384889483213314</v>
+        <v>1.924814980483654</v>
       </c>
       <c r="E22" t="n">
-        <v>2.502334289124915</v>
+        <v>3.249506995587554</v>
       </c>
       <c r="F22" t="n">
-        <v>2.515954076164033</v>
+        <v>1.084510705668458</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0568746111186525</v>
+        <v>2.442757824900379</v>
       </c>
     </row>
     <row r="23">
@@ -22251,22 +22251,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.86237390102627</v>
+        <v>1.851775014279605</v>
       </c>
       <c r="C23" t="n">
         <v>3.581210762686716</v>
       </c>
       <c r="D23" t="n">
-        <v>1.364773022570745</v>
+        <v>1.898067432027573</v>
       </c>
       <c r="E23" t="n">
-        <v>2.482345179822625</v>
+        <v>3.22276360910094</v>
       </c>
       <c r="F23" t="n">
-        <v>2.497052257678096</v>
+        <v>1.072365786455583</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0580827465975397</v>
+        <v>2.433873333074002</v>
       </c>
     </row>
     <row r="24">
@@ -22276,22 +22276,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.836687736552514</v>
+        <v>1.827209892733777</v>
       </c>
       <c r="C24" t="n">
         <v>3.567305346170463</v>
       </c>
       <c r="D24" t="n">
-        <v>1.347680158226735</v>
+        <v>1.874518902959199</v>
       </c>
       <c r="E24" t="n">
-        <v>2.465147897612784</v>
+        <v>3.199217735214904</v>
       </c>
       <c r="F24" t="n">
-        <v>2.477436928968711</v>
+        <v>1.075507081809904</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0211301506248714</v>
+        <v>2.483371274358522</v>
       </c>
     </row>
     <row r="25">
@@ -22301,22 +22301,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.813660547016896</v>
+        <v>1.807682507655114</v>
       </c>
       <c r="C25" t="n">
         <v>3.552990702315751</v>
       </c>
       <c r="D25" t="n">
-        <v>1.334895680366637</v>
+        <v>1.855710162838028</v>
       </c>
       <c r="E25" t="n">
-        <v>2.451932427547764</v>
+        <v>3.180410736043769</v>
       </c>
       <c r="F25" t="n">
-        <v>2.457169321990193</v>
+        <v>1.062499917621588</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0005779417961825</v>
+        <v>2.421822200030253</v>
       </c>
     </row>
     <row r="26">
@@ -22326,22 +22326,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.791614166107401</v>
+        <v>1.788793362891245</v>
       </c>
       <c r="C26" t="n">
         <v>3.538315925370654</v>
       </c>
       <c r="D26" t="n">
-        <v>1.322176792759244</v>
+        <v>1.83705983153875</v>
       </c>
       <c r="E26" t="n">
-        <v>2.438860241158926</v>
+        <v>3.161761452259575</v>
       </c>
       <c r="F26" t="n">
-        <v>2.436284189603058</v>
+        <v>1.064484604472635</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0470348945163674</v>
+        <v>2.416785223558922</v>
       </c>
     </row>
     <row r="27">
@@ -22351,22 +22351,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.77198929532921</v>
+        <v>1.774103608735355</v>
       </c>
       <c r="C27" t="n">
         <v>3.523309136752895</v>
       </c>
       <c r="D27" t="n">
-        <v>1.312579411768322</v>
+        <v>1.822298247770023</v>
       </c>
       <c r="E27" t="n">
-        <v>2.428611636987137</v>
+        <v>3.146999097920681</v>
       </c>
       <c r="F27" t="n">
-        <v>2.414818569073918</v>
+        <v>1.058367127053101</v>
       </c>
       <c r="G27" t="n">
-        <v>0.09116281021064809</v>
+        <v>2.36291025802168</v>
       </c>
     </row>
     <row r="28">
@@ -22376,22 +22376,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.755859335529364</v>
+        <v>1.765297463175659</v>
       </c>
       <c r="C28" t="n">
         <v>3.507962215206461</v>
       </c>
       <c r="D28" t="n">
-        <v>1.307079240684258</v>
+        <v>1.812419593671257</v>
       </c>
       <c r="E28" t="n">
-        <v>2.422192121814713</v>
+        <v>3.137117551745373</v>
       </c>
       <c r="F28" t="n">
-        <v>2.392787990538898</v>
+        <v>1.078108748570869</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2003873630464581</v>
+        <v>2.402636329394436</v>
       </c>
     </row>
     <row r="29">
@@ -22401,22 +22401,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.742779689820447</v>
+        <v>1.76162715872454</v>
       </c>
       <c r="C29" t="n">
         <v>3.492242189273123</v>
       </c>
       <c r="D29" t="n">
-        <v>1.304572045508858</v>
+        <v>1.807051292631733</v>
       </c>
       <c r="E29" t="n">
-        <v>2.41862024578726</v>
+        <v>3.131744753225282</v>
       </c>
       <c r="F29" t="n">
-        <v>2.37018138297919</v>
+        <v>1.081446937553356</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1953269074853862</v>
+        <v>2.368897065457323</v>
       </c>
     </row>
     <row r="30">
@@ -22426,22 +22426,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.731381557658903</v>
+        <v>1.760350295261815</v>
       </c>
       <c r="C30" t="n">
         <v>3.476146361211454</v>
       </c>
       <c r="D30" t="n">
-        <v>1.302935876269844</v>
+        <v>1.803589981721623</v>
       </c>
       <c r="E30" t="n">
-        <v>2.415963208807361</v>
+        <v>3.128277839360781</v>
       </c>
       <c r="F30" t="n">
-        <v>2.346962456568255</v>
+        <v>1.090577778751502</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2077266363272396</v>
+        <v>2.383887306950875</v>
       </c>
     </row>
     <row r="31">
@@ -22451,22 +22451,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.721276278468505</v>
+        <v>1.761156504176098</v>
       </c>
       <c r="C31" t="n">
         <v>3.459669325531499</v>
       </c>
       <c r="D31" t="n">
-        <v>1.30191205684301</v>
+        <v>1.80202218739967</v>
       </c>
       <c r="E31" t="n">
-        <v>2.413924454846425</v>
+        <v>3.126703384712389</v>
       </c>
       <c r="F31" t="n">
-        <v>2.323084990136792</v>
+        <v>1.069585669048432</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1953108898499289</v>
+        <v>2.326017725240241</v>
       </c>
     </row>
     <row r="32">
@@ -22476,22 +22476,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.71220401190274</v>
+        <v>1.763758095607506</v>
       </c>
       <c r="C32" t="n">
         <v>3.442760583498273</v>
       </c>
       <c r="D32" t="n">
-        <v>1.301432525062104</v>
+        <v>1.801788285696319</v>
       </c>
       <c r="E32" t="n">
-        <v>2.412451605272233</v>
+        <v>3.126461930179274</v>
       </c>
       <c r="F32" t="n">
-        <v>2.29849177391398</v>
+        <v>1.040743187855164</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1458741166938664</v>
+        <v>2.243141673312959</v>
       </c>
     </row>
     <row r="33">
@@ -22501,22 +22501,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.702934086631234</v>
+        <v>1.76646121614382</v>
       </c>
       <c r="C33" t="n">
         <v>3.425364743487543</v>
       </c>
       <c r="D33" t="n">
-        <v>1.301645236826378</v>
+        <v>1.80202791890846</v>
       </c>
       <c r="E33" t="n">
-        <v>2.4116399174269</v>
+        <v>3.126694418104378</v>
       </c>
       <c r="F33" t="n">
-        <v>2.273117691393022</v>
+        <v>1.032778137057558</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1259518535493879</v>
+        <v>2.22063563104942</v>
       </c>
     </row>
     <row r="34">
@@ -22526,22 +22526,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.691624912639619</v>
+        <v>1.764616634923075</v>
       </c>
       <c r="C34" t="n">
         <v>3.407454792917298</v>
       </c>
       <c r="D34" t="n">
-        <v>1.29760576642053</v>
+        <v>1.797808948682286</v>
       </c>
       <c r="E34" t="n">
-        <v>2.406939335312289</v>
+        <v>3.122468585003647</v>
       </c>
       <c r="F34" t="n">
-        <v>2.246892890873312</v>
+        <v>1.021839664379434</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1431911932610314</v>
+        <v>2.1919079371338</v>
       </c>
     </row>
     <row r="35">
@@ -22551,22 +22551,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.680735566418901</v>
+        <v>1.764167808815742</v>
       </c>
       <c r="C35" t="n">
         <v>3.388980354340865</v>
       </c>
       <c r="D35" t="n">
-        <v>1.294899512155719</v>
+        <v>1.795148865337908</v>
       </c>
       <c r="E35" t="n">
-        <v>2.403345555146186</v>
+        <v>3.119800554241901</v>
       </c>
       <c r="F35" t="n">
-        <v>2.219773899372953</v>
+        <v>1.010382737552253</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1115597947533011</v>
+        <v>2.134776904113722</v>
       </c>
     </row>
     <row r="36">
@@ -22576,22 +22576,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.671169995762055</v>
+        <v>1.766019569783914</v>
       </c>
       <c r="C36" t="n">
         <v>3.369885637216781</v>
       </c>
       <c r="D36" t="n">
-        <v>1.293665163631378</v>
+        <v>1.79400980297066</v>
       </c>
       <c r="E36" t="n">
-        <v>2.40114573791169</v>
+        <v>3.11865235134161</v>
       </c>
       <c r="F36" t="n">
-        <v>2.191705869267007</v>
+        <v>1.00991145345539</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1226919285602181</v>
+        <v>2.127206555506599</v>
       </c>
     </row>
     <row r="37">
@@ -22601,22 +22601,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.662232049702452</v>
+        <v>1.769478028262196</v>
       </c>
       <c r="C37" t="n">
         <v>3.35012973234538</v>
       </c>
       <c r="D37" t="n">
-        <v>1.293825581864107</v>
+        <v>1.794300850040297</v>
       </c>
       <c r="E37" t="n">
-        <v>2.400245556238961</v>
+        <v>3.118933968279706</v>
       </c>
       <c r="F37" t="n">
-        <v>2.162624661503957</v>
+        <v>0.994556847323479</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0916410020377376</v>
+        <v>2.059346208743714</v>
       </c>
     </row>
     <row r="38">
@@ -22626,22 +22626,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.651261759952014</v>
+        <v>1.769435465085519</v>
       </c>
       <c r="C38" t="n">
         <v>3.329647835656707</v>
       </c>
       <c r="D38" t="n">
-        <v>1.291620984220644</v>
+        <v>1.79141029631736</v>
       </c>
       <c r="E38" t="n">
-        <v>2.397206212303082</v>
+        <v>3.116035231002156</v>
       </c>
       <c r="F38" t="n">
-        <v>2.132455764278764</v>
+        <v>0.9871530699995036</v>
       </c>
       <c r="G38" t="n">
-        <v>0.08833780805676</v>
+        <v>2.033405333778984</v>
       </c>
     </row>
     <row r="39">
@@ -22651,22 +22651,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.636961451213276</v>
+        <v>1.763509821072912</v>
       </c>
       <c r="C39" t="n">
         <v>3.308393332950041</v>
       </c>
       <c r="D39" t="n">
-        <v>1.284905785048381</v>
+        <v>1.783287063712164</v>
       </c>
       <c r="E39" t="n">
-        <v>2.389951686405977</v>
+        <v>3.107905026437993</v>
       </c>
       <c r="F39" t="n">
-        <v>2.101141196534736</v>
+        <v>0.9723591791090398</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0493848157362193</v>
+        <v>1.970032990214896</v>
       </c>
     </row>
     <row r="40">
@@ -22676,22 +22676,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.620826701353364</v>
+        <v>1.754896783753763</v>
       </c>
       <c r="C40" t="n">
         <v>3.286335311125574</v>
       </c>
       <c r="D40" t="n">
-        <v>1.276461361897965</v>
+        <v>1.77278863429485</v>
       </c>
       <c r="E40" t="n">
-        <v>2.380994194105223</v>
+        <v>3.097399882424677</v>
       </c>
       <c r="F40" t="n">
-        <v>2.068651237092074</v>
+        <v>0.9608034335403718</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0224505980308911</v>
+        <v>1.924949327579522</v>
       </c>
     </row>
     <row r="41">
@@ -22701,22 +22701,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.604125936759885</v>
+        <v>1.745838282958587</v>
       </c>
       <c r="C41" t="n">
         <v>3.263459249393464</v>
       </c>
       <c r="D41" t="n">
-        <v>1.267804021889693</v>
+        <v>1.761602459057018</v>
       </c>
       <c r="E41" t="n">
-        <v>2.371792402728037</v>
+        <v>3.086206914169794</v>
       </c>
       <c r="F41" t="n">
-        <v>2.034967214223038</v>
+        <v>0.9429838200764372</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0049375456997129</v>
+        <v>1.878808015189329</v>
       </c>
     </row>
     <row r="42">
@@ -22726,22 +22726,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.586249061063955</v>
+        <v>1.73546453839475</v>
       </c>
       <c r="C42" t="n">
         <v>3.239768597625786</v>
       </c>
       <c r="D42" t="n">
-        <v>1.258624774255395</v>
+        <v>1.74923462825967</v>
       </c>
       <c r="E42" t="n">
-        <v>2.36209860048033</v>
+        <v>3.073833223286655</v>
       </c>
       <c r="F42" t="n">
-        <v>2.000072153080987</v>
+        <v>0.9086099935432176</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.0332924668342601</v>
+        <v>1.781105450586521</v>
       </c>
     </row>
     <row r="43">
@@ -22751,22 +22751,22 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.564875240540723</v>
+        <v>1.719164918978425</v>
       </c>
       <c r="C43" t="n">
         <v>3.215247820217695</v>
       </c>
       <c r="D43" t="n">
-        <v>1.245504232967694</v>
+        <v>1.731451883498519</v>
       </c>
       <c r="E43" t="n">
-        <v>2.34876129217836</v>
+        <v>3.056046705154733</v>
       </c>
       <c r="F43" t="n">
-        <v>1.963952841690163</v>
+        <v>0.8946559458174154</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.0597248096983747</v>
+        <v>1.749983924032244</v>
       </c>
     </row>
     <row r="44">
@@ -22776,22 +22776,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.53925969199973</v>
+        <v>1.695959667410861</v>
       </c>
       <c r="C44" t="n">
         <v>3.189910556413487</v>
       </c>
       <c r="D44" t="n">
-        <v>1.227696404284007</v>
+        <v>1.707760592606272</v>
       </c>
       <c r="E44" t="n">
-        <v>2.33099497219901</v>
+        <v>3.032353858569879</v>
       </c>
       <c r="F44" t="n">
-        <v>1.926624898469088</v>
+        <v>0.8689381497552393</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.0772337452879384</v>
+        <v>1.677351652513783</v>
       </c>
     </row>
     <row r="45">
@@ -22801,22 +22801,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.510271192323896</v>
+        <v>1.667201728121246</v>
       </c>
       <c r="C45" t="n">
         <v>3.163755833549857</v>
       </c>
       <c r="D45" t="n">
-        <v>1.205795438748156</v>
+        <v>1.678940923361449</v>
       </c>
       <c r="E45" t="n">
-        <v>2.309356287013024</v>
+        <v>3.003534045183296</v>
       </c>
       <c r="F45" t="n">
-        <v>1.888134635943045</v>
+        <v>0.8513084031218769</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.0835904125550488</v>
+        <v>1.630375885429617</v>
       </c>
     </row>
     <row r="46">
@@ -22826,22 +22826,22 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.479497154582661</v>
+        <v>1.636328690846989</v>
       </c>
       <c r="C46" t="n">
         <v>3.136831240924697</v>
       </c>
       <c r="D46" t="n">
-        <v>1.182884146690522</v>
+        <v>1.648390486115823</v>
       </c>
       <c r="E46" t="n">
-        <v>2.286686020948292</v>
+        <v>2.972984596118025</v>
       </c>
       <c r="F46" t="n">
-        <v>1.84855540522009</v>
+        <v>0.838017106691763</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.1350723706187371</v>
+        <v>1.568996331323955</v>
       </c>
     </row>
     <row r="47">
@@ -22851,22 +22851,22 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.44645799302977</v>
+        <v>1.601617339028524</v>
       </c>
       <c r="C47" t="n">
         <v>3.109181100951862</v>
       </c>
       <c r="D47" t="n">
-        <v>1.157178333086071</v>
+        <v>1.614190071243094</v>
       </c>
       <c r="E47" t="n">
-        <v>2.261436978642108</v>
+        <v>2.938786684210478</v>
       </c>
       <c r="F47" t="n">
-        <v>1.807966808552678</v>
+        <v>0.8261773692521363</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.1448840512872919</v>
+        <v>1.53161455870015</v>
       </c>
     </row>
     <row r="48">
@@ -22876,22 +22876,22 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.411224281417482</v>
+        <v>1.563500787037096</v>
       </c>
       <c r="C48" t="n">
         <v>3.080853158161186</v>
       </c>
       <c r="D48" t="n">
-        <v>1.129073927458675</v>
+        <v>1.576977658657678</v>
       </c>
       <c r="E48" t="n">
-        <v>2.233917923197705</v>
+        <v>2.901578170354161</v>
       </c>
       <c r="F48" t="n">
-        <v>1.766467420533228</v>
+        <v>0.8039420966490248</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.1956822730450083</v>
+        <v>1.450485868513909</v>
       </c>
     </row>
     <row r="49">
@@ -22901,22 +22901,22 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1.373842544566</v>
+        <v>1.522124804521511</v>
       </c>
       <c r="C49" t="n">
         <v>3.051912042595113</v>
       </c>
       <c r="D49" t="n">
-        <v>1.099081155020391</v>
+        <v>1.536961235839429</v>
       </c>
       <c r="E49" t="n">
-        <v>2.204618631202043</v>
+        <v>2.861567343795399</v>
       </c>
       <c r="F49" t="n">
-        <v>1.724170417820752</v>
+        <v>0.7902694089661174</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.2171351479762046</v>
+        <v>1.42118502145311</v>
       </c>
     </row>
     <row r="50">
@@ -22926,22 +22926,22 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1.334083835637386</v>
+        <v>1.476560868809999</v>
       </c>
       <c r="C50" t="n">
         <v>3.022438944393438</v>
       </c>
       <c r="D50" t="n">
-        <v>1.065777258290641</v>
+        <v>1.493083556429213</v>
       </c>
       <c r="E50" t="n">
-        <v>2.172242284467123</v>
+        <v>2.817696805124851</v>
       </c>
       <c r="F50" t="n">
-        <v>1.681202203083539</v>
+        <v>0.7532555772868583</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.2961728818308055</v>
+        <v>1.303000945807292</v>
       </c>
     </row>
     <row r="51">
@@ -22951,22 +22951,22 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1.292901499926925</v>
+        <v>1.428994430808541</v>
       </c>
       <c r="C51" t="n">
         <v>2.992550281553824</v>
       </c>
       <c r="D51" t="n">
-        <v>1.032014330553935</v>
+        <v>1.447645769407027</v>
       </c>
       <c r="E51" t="n">
-        <v>2.139362663140425</v>
+        <v>2.77226737386868</v>
       </c>
       <c r="F51" t="n">
-        <v>1.637709553521216</v>
+        <v>0.7378730992958301</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.3140193235155477</v>
+        <v>1.268679684572692</v>
       </c>
     </row>
     <row r="52">
@@ -22976,22 +22976,22 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.250718483136281</v>
+        <v>1.379479733880631</v>
       </c>
       <c r="C52" t="n">
         <v>2.962333886838155</v>
       </c>
       <c r="D52" t="n">
-        <v>0.9970455166459252</v>
+        <v>1.400305893049107</v>
       </c>
       <c r="E52" t="n">
-        <v>2.105344835660812</v>
+        <v>2.724936733068263</v>
       </c>
       <c r="F52" t="n">
-        <v>1.593845355750153</v>
+        <v>0.7214442438735941</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.3513926912347382</v>
+        <v>1.204208546107898</v>
       </c>
     </row>
     <row r="53">
@@ -23001,22 +23001,22 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1.208642603154051</v>
+        <v>1.330346725062688</v>
       </c>
       <c r="C53" t="n">
         <v>2.931908514334981</v>
       </c>
       <c r="D53" t="n">
-        <v>0.9631268691182342</v>
+        <v>1.353351391109348</v>
       </c>
       <c r="E53" t="n">
-        <v>2.072238420437797</v>
+        <v>2.677991837181656</v>
       </c>
       <c r="F53" t="n">
-        <v>1.5497721168659</v>
+        <v>0.7174654180211695</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.3582366783965688</v>
+        <v>1.209024525060461</v>
       </c>
     </row>
     <row r="54">
@@ -23026,22 +23026,22 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1.166930422607087</v>
+        <v>1.28164211715431</v>
       </c>
       <c r="C54" t="n">
         <v>2.90137973182753</v>
       </c>
       <c r="D54" t="n">
-        <v>0.930172550238712</v>
+        <v>1.306898667730256</v>
       </c>
       <c r="E54" t="n">
-        <v>2.040019553216952</v>
+        <v>2.631549191017646</v>
       </c>
       <c r="F54" t="n">
-        <v>1.505648157081085</v>
+        <v>0.7134807663836307</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.3637589467848117</v>
+        <v>1.213578715159632</v>
       </c>
     </row>
     <row r="55">
@@ -23051,22 +23051,22 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1.126350547510351</v>
+        <v>1.233882970830451</v>
       </c>
       <c r="C55" t="n">
         <v>2.870855211897288</v>
       </c>
       <c r="D55" t="n">
-        <v>0.8977186786024909</v>
+        <v>1.260915740726264</v>
       </c>
       <c r="E55" t="n">
-        <v>2.00826716129285</v>
+        <v>2.585575515861116</v>
       </c>
       <c r="F55" t="n">
-        <v>1.461627489506362</v>
+        <v>0.700565470920656</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.3701233999256625</v>
+        <v>1.193824091686906</v>
       </c>
     </row>
     <row r="56">
@@ -23076,22 +23076,22 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1.089673593450827</v>
+        <v>1.193186673256518</v>
       </c>
       <c r="C56" t="n">
         <v>2.840461486361153</v>
       </c>
       <c r="D56" t="n">
-        <v>0.8716707988549066</v>
+        <v>1.221429020250188</v>
       </c>
       <c r="E56" t="n">
-        <v>1.982373814755576</v>
+        <v>2.546096283865074</v>
       </c>
       <c r="F56" t="n">
-        <v>1.417861962434242</v>
+        <v>0.6969086570936842</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.3729773212536985</v>
+        <v>1.209446074932001</v>
       </c>
     </row>
     <row r="57">
@@ -23101,22 +23101,22 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1.056547884508805</v>
+        <v>1.157638325308193</v>
       </c>
       <c r="C57" t="n">
         <v>2.810286867412405</v>
       </c>
       <c r="D57" t="n">
-        <v>0.8496394825059896</v>
+        <v>1.186103603932676</v>
       </c>
       <c r="E57" t="n">
-        <v>1.960294912737622</v>
+        <v>2.510776905075414</v>
       </c>
       <c r="F57" t="n">
-        <v>1.37446435629943</v>
+        <v>0.6781589017251364</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.3875198690049379</v>
+        <v>1.127328352545669</v>
       </c>
     </row>
     <row r="58">
@@ -23126,22 +23126,22 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1.026982053336656</v>
+        <v>1.127463848598389</v>
       </c>
       <c r="C58" t="n">
         <v>2.780419415696717</v>
       </c>
       <c r="D58" t="n">
-        <v>0.8324717454532609</v>
+        <v>1.155554281134886</v>
       </c>
       <c r="E58" t="n">
-        <v>1.942721927786433</v>
+        <v>2.480231785808426</v>
       </c>
       <c r="F58" t="n">
-        <v>1.331524434145823</v>
+        <v>0.6539831863191046</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.3741620859885333</v>
+        <v>1.045163285400569</v>
       </c>
     </row>
     <row r="59">
@@ -23151,22 +23151,22 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1.001358619657096</v>
+        <v>1.103707586351232</v>
       </c>
       <c r="C59" t="n">
         <v>2.750900355221919</v>
       </c>
       <c r="D59" t="n">
-        <v>0.8210233796537985</v>
+        <v>1.130427565829492</v>
       </c>
       <c r="E59" t="n">
-        <v>1.930443061799677</v>
+        <v>2.455107345255933</v>
       </c>
       <c r="F59" t="n">
-        <v>1.289104716350588</v>
+        <v>0.6425979316721477</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.3782958115464885</v>
+        <v>0.9704716145598083</v>
       </c>
     </row>
     <row r="60">
@@ -23176,22 +23176,22 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.9784678208427482</v>
+        <v>1.084392829494272</v>
       </c>
       <c r="C60" t="n">
         <v>2.721739941614024</v>
       </c>
       <c r="D60" t="n">
-        <v>0.814684070761194</v>
+        <v>1.10957190507716</v>
       </c>
       <c r="E60" t="n">
-        <v>1.922895298295551</v>
+        <v>2.434253263466095</v>
       </c>
       <c r="F60" t="n">
-        <v>1.247236686251959</v>
+        <v>0.6572246227228044</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.3258524459372071</v>
+        <v>0.9678734468256984</v>
       </c>
     </row>
     <row r="61">
@@ -23201,22 +23201,22 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.9566099535859428</v>
+        <v>1.065354330466997</v>
       </c>
       <c r="C61" t="n">
         <v>2.692941323099362</v>
       </c>
       <c r="D61" t="n">
-        <v>0.8083031048902694</v>
+        <v>1.08838947258527</v>
       </c>
       <c r="E61" t="n">
-        <v>1.915345392617331</v>
+        <v>2.413071432243743</v>
       </c>
       <c r="F61" t="n">
-        <v>1.205926405075722</v>
+        <v>0.6657934605891227</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.2713705695385653</v>
+        <v>0.9701951173580941</v>
       </c>
     </row>
     <row r="62">
@@ -23226,22 +23226,22 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.9374300707292478</v>
+        <v>1.05150899430827</v>
       </c>
       <c r="C62" t="n">
         <v>2.664513710534574</v>
       </c>
       <c r="D62" t="n">
-        <v>0.8072052630720981</v>
+        <v>1.072579095062118</v>
       </c>
       <c r="E62" t="n">
-        <v>1.912570683675112</v>
+        <v>2.397260396266689</v>
       </c>
       <c r="F62" t="n">
-        <v>1.165183749374532</v>
+        <v>0.6727934116604161</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.2556424308061253</v>
+        <v>0.9572675560365012</v>
       </c>
     </row>
     <row r="63">
@@ -23251,22 +23251,22 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.9202325266898734</v>
+        <v>1.039421418461711</v>
       </c>
       <c r="C63" t="n">
         <v>2.636441586700357</v>
       </c>
       <c r="D63" t="n">
-        <v>0.8065913799941864</v>
+        <v>1.057505829892928</v>
       </c>
       <c r="E63" t="n">
-        <v>1.910345897014345</v>
+        <v>2.382184796739592</v>
       </c>
       <c r="F63" t="n">
-        <v>1.124985312195941</v>
+        <v>0.6799212090692611</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.2494178940019917</v>
+        <v>0.9461167831712648</v>
       </c>
     </row>
     <row r="64">
@@ -23276,22 +23276,22 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.907080884943714</v>
+        <v>1.034789836333053</v>
       </c>
       <c r="C64" t="n">
         <v>2.608689783711277</v>
       </c>
       <c r="D64" t="n">
-        <v>0.8125805921439584</v>
+        <v>1.049470269917963</v>
       </c>
       <c r="E64" t="n">
-        <v>1.914130325166544</v>
+        <v>2.37414447447555</v>
       </c>
       <c r="F64" t="n">
-        <v>1.085306162734366</v>
+        <v>0.686996847324062</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.2689864925010032</v>
+        <v>0.922210232726174</v>
       </c>
     </row>
     <row r="65">
@@ -23301,22 +23301,22 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8966002315488959</v>
+        <v>1.03415868625511</v>
       </c>
       <c r="C65" t="n">
         <v>2.581213185517281</v>
       </c>
       <c r="D65" t="n">
-        <v>0.8217088588778019</v>
+        <v>1.044536513261732</v>
       </c>
       <c r="E65" t="n">
-        <v>1.920921686143497</v>
+        <v>2.36920474472134</v>
       </c>
       <c r="F65" t="n">
-        <v>1.046079396525905</v>
+        <v>0.6953529169451965</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.2675313666292633</v>
+        <v>0.9254935690556084</v>
       </c>
     </row>
     <row r="66">
@@ -23326,22 +23326,22 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.8868008881002045</v>
+        <v>1.034338326789552</v>
       </c>
       <c r="C66" t="n">
         <v>2.553956837203716</v>
       </c>
       <c r="D66" t="n">
-        <v>0.8319581607620474</v>
+        <v>1.040460406846067</v>
       </c>
       <c r="E66" t="n">
-        <v>1.928752545041133</v>
+        <v>2.365122298516973</v>
       </c>
       <c r="F66" t="n">
-        <v>1.007221195730782</v>
+        <v>0.6838816846029517</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.2904353174160475</v>
+        <v>0.8698672798045639</v>
       </c>
     </row>
     <row r="67">
@@ -23351,22 +23351,22 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8763491755236954</v>
+        <v>1.033275551337519</v>
       </c>
       <c r="C67" t="n">
         <v>2.526898003565909</v>
       </c>
       <c r="D67" t="n">
-        <v>0.8420851181386251</v>
+        <v>1.035312627264049</v>
       </c>
       <c r="E67" t="n">
-        <v>1.936436502874558</v>
+        <v>2.359968466331831</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9686425092683384</v>
+        <v>0.6841331187723285</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.2824532805714517</v>
+        <v>0.8594583536945029</v>
       </c>
     </row>
     <row r="68">
@@ -23376,22 +23376,22 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8643055212543014</v>
+        <v>1.02947050877117</v>
       </c>
       <c r="C68" t="n">
         <v>2.500005459659412</v>
       </c>
       <c r="D68" t="n">
-        <v>0.8510057630068424</v>
+        <v>1.027956082584978</v>
       </c>
       <c r="E68" t="n">
-        <v>1.942930542880182</v>
+        <v>2.352606649478911</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9302598265626104</v>
+        <v>0.6909936662212928</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.2662606757140052</v>
+        <v>0.8534838174020789</v>
       </c>
     </row>
     <row r="69">
@@ -23401,22 +23401,22 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.850451699906472</v>
+        <v>1.022261570789371</v>
       </c>
       <c r="C69" t="n">
         <v>2.473216573426881</v>
       </c>
       <c r="D69" t="n">
-        <v>0.8576876664704223</v>
+        <v>1.017582758360488</v>
       </c>
       <c r="E69" t="n">
-        <v>1.947275983606285</v>
+        <v>2.342228549382804</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8920012560136737</v>
+        <v>0.7053053432333247</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.2590423461379746</v>
+        <v>0.8591910604821138</v>
       </c>
     </row>
     <row r="70">
@@ -23426,22 +23426,22 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8359565992952596</v>
+        <v>1.01433371349379</v>
       </c>
       <c r="C70" t="n">
         <v>2.446487231356413</v>
       </c>
       <c r="D70" t="n">
-        <v>0.8641088383378319</v>
+        <v>1.006604265903123</v>
       </c>
       <c r="E70" t="n">
-        <v>1.951275455913402</v>
+        <v>2.331245262813725</v>
       </c>
       <c r="F70" t="n">
-        <v>0.8538119083071054</v>
+        <v>0.7146942630626218</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.2772976681194595</v>
+        <v>0.8497999965904092</v>
       </c>
     </row>
     <row r="71">
@@ -23451,22 +23451,22 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8204113626356415</v>
+        <v>1.005106671572109</v>
       </c>
       <c r="C71" t="n">
         <v>2.419760328161972</v>
       </c>
       <c r="D71" t="n">
-        <v>0.8700326103419664</v>
+        <v>0.99464737469181</v>
       </c>
       <c r="E71" t="n">
-        <v>1.954782533335675</v>
+        <v>2.319284538732965</v>
       </c>
       <c r="F71" t="n">
-        <v>0.8156392443923485</v>
+        <v>0.7092943379631145</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.2904872767671687</v>
+        <v>0.8179587099997447</v>
       </c>
     </row>
     <row r="72">
@@ -23476,22 +23476,22 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8019444471629189</v>
+        <v>0.9903334727794216</v>
       </c>
       <c r="C72" t="n">
         <v>2.392993463266256</v>
       </c>
       <c r="D72" t="n">
-        <v>0.8717908877991851</v>
+        <v>0.9777114765421228</v>
       </c>
       <c r="E72" t="n">
-        <v>1.954425301960221</v>
+        <v>2.302346292416353</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7774348330462768</v>
+        <v>0.7006044775977298</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.3052203889401756</v>
+        <v>0.7841894316074765</v>
       </c>
     </row>
     <row r="73">
@@ -23501,22 +23501,22 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7816150955146752</v>
+        <v>0.9724885797310612</v>
       </c>
       <c r="C73" t="n">
         <v>2.366179348595636</v>
       </c>
       <c r="D73" t="n">
-        <v>0.8716116207919473</v>
+        <v>0.9581563388268126</v>
       </c>
       <c r="E73" t="n">
-        <v>1.9521397526215</v>
+        <v>2.282789242570263</v>
       </c>
       <c r="F73" t="n">
-        <v>0.7391789704995623</v>
+        <v>0.7005617902591147</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.3187898088611359</v>
+        <v>0.7694889719668728</v>
       </c>
     </row>
     <row r="74">
@@ -23526,22 +23526,22 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7611325705320695</v>
+        <v>0.9547927210134062</v>
       </c>
       <c r="C74" t="n">
         <v>2.339330146890782</v>
       </c>
       <c r="D74" t="n">
-        <v>0.8718453578560919</v>
+        <v>0.938704996287739</v>
       </c>
       <c r="E74" t="n">
-        <v>1.950145906969451</v>
+        <v>2.263335914455478</v>
       </c>
       <c r="F74" t="n">
-        <v>0.7008662610876976</v>
+        <v>0.7011296237576303</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.3268274649798284</v>
+        <v>0.754803380436369</v>
       </c>
     </row>
     <row r="75">
@@ -23551,22 +23551,22 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7405066622429768</v>
+        <v>0.9369457910951456</v>
       </c>
       <c r="C75" t="n">
         <v>2.312435141077637</v>
       </c>
       <c r="D75" t="n">
-        <v>0.8719415570445133</v>
+        <v>0.9188691258398411</v>
       </c>
       <c r="E75" t="n">
-        <v>1.948003641583313</v>
+        <v>2.243498222586787</v>
       </c>
       <c r="F75" t="n">
-        <v>0.6624899826471714</v>
+        <v>0.6985898728436559</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.3354349178206539</v>
+        <v>0.7309691532547924</v>
       </c>
     </row>
     <row r="76">
@@ -23576,22 +23576,22 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7186864491172442</v>
+        <v>0.9174641948188156</v>
       </c>
       <c r="C76" t="n">
         <v>2.285479870861552</v>
       </c>
       <c r="D76" t="n">
-        <v>0.871312767709072</v>
+        <v>0.8977676095216935</v>
       </c>
       <c r="E76" t="n">
-        <v>1.945155791077877</v>
+        <v>2.222396088121587</v>
       </c>
       <c r="F76" t="n">
-        <v>0.6240456619897914</v>
+        <v>0.701008307052389</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.3068135125488442</v>
+        <v>0.7331323490219523</v>
       </c>
     </row>
     <row r="77">
@@ -23601,22 +23601,22 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6937758384032779</v>
+        <v>0.8924588590874585</v>
       </c>
       <c r="C77" t="n">
         <v>2.258433751952458</v>
       </c>
       <c r="D77" t="n">
-        <v>0.8660955574506124</v>
+        <v>0.8716366844719317</v>
       </c>
       <c r="E77" t="n">
-        <v>1.938058578325617</v>
+        <v>2.196266483824598</v>
       </c>
       <c r="F77" t="n">
-        <v>0.5855350492085163</v>
+        <v>0.7041995342569014</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.2983466549540088</v>
+        <v>0.7311265516533064</v>
       </c>
     </row>
     <row r="78">
@@ -23626,22 +23626,22 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6655836815535841</v>
+        <v>0.8622966484554615</v>
       </c>
       <c r="C78" t="n">
         <v>2.231318787090734</v>
       </c>
       <c r="D78" t="n">
-        <v>0.8570114819359853</v>
+        <v>0.8413724530464832</v>
       </c>
       <c r="E78" t="n">
-        <v>1.927297693149794</v>
+        <v>2.166005680433747</v>
       </c>
       <c r="F78" t="n">
-        <v>0.5469888528133874</v>
+        <v>0.7018415688907377</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.3027193704212164</v>
+        <v>0.7084952609332353</v>
       </c>
     </row>
     <row r="79">
@@ -23651,22 +23651,22 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.634238346580986</v>
+        <v>0.8265324286378588</v>
       </c>
       <c r="C79" t="n">
         <v>2.204159680354117</v>
       </c>
       <c r="D79" t="n">
-        <v>0.8429401863558841</v>
+        <v>0.806028407025825</v>
       </c>
       <c r="E79" t="n">
-        <v>1.91189216042763</v>
+        <v>2.130666788012964</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5084599403578192</v>
+        <v>0.703828479224524</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.3064717766559194</v>
+        <v>0.706551009029556</v>
       </c>
     </row>
     <row r="80">
@@ -23676,22 +23676,22 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6011938479921186</v>
+        <v>0.7884874719010044</v>
       </c>
       <c r="C80" t="n">
         <v>2.177010573679491</v>
       </c>
       <c r="D80" t="n">
-        <v>0.8267806939424194</v>
+        <v>0.7689383006549702</v>
       </c>
       <c r="E80" t="n">
-        <v>1.894473229638544</v>
+        <v>2.093583086282584</v>
       </c>
       <c r="F80" t="n">
-        <v>0.4700304861089646</v>
+        <v>0.6956202292308674</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.3002953909297009</v>
+        <v>0.6818378888713416</v>
       </c>
     </row>
     <row r="81">
@@ -23701,22 +23701,22 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5662790351154308</v>
+        <v>0.7472776915167474</v>
       </c>
       <c r="C81" t="n">
         <v>2.149927934141529</v>
       </c>
       <c r="D81" t="n">
-        <v>0.8076176151591206</v>
+        <v>0.729144681783461</v>
       </c>
       <c r="E81" t="n">
-        <v>1.874297254552424</v>
+        <v>2.053797598135581</v>
       </c>
       <c r="F81" t="n">
-        <v>0.4317914143236225</v>
+        <v>0.6893208418319151</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.3080781381970434</v>
+        <v>0.6610674287752492</v>
       </c>
     </row>
     <row r="82">
@@ -23726,22 +23726,22 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5294255131530083</v>
+        <v>0.7023908356769515</v>
       </c>
       <c r="C82" t="n">
         <v>2.122988288030277</v>
       </c>
       <c r="D82" t="n">
-        <v>0.7847303026582537</v>
+        <v>0.6860605507244104</v>
       </c>
       <c r="E82" t="n">
-        <v>1.850673229167168</v>
+        <v>2.010722888299822</v>
       </c>
       <c r="F82" t="n">
-        <v>0.3938489640622893</v>
+        <v>0.6878259782668213</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.3253575800122201</v>
+        <v>0.6479715340891852</v>
       </c>
     </row>
     <row r="83">
@@ -23751,22 +23751,22 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4919392486905438</v>
+        <v>0.6567934597553444</v>
       </c>
       <c r="C83" t="n">
         <v>2.096260446297067</v>
       </c>
       <c r="D83" t="n">
-        <v>0.7609215030860428</v>
+        <v>0.6427401687088157</v>
       </c>
       <c r="E83" t="n">
-        <v>1.826156542946931</v>
+        <v>1.96741287900031</v>
       </c>
       <c r="F83" t="n">
-        <v>0.3563288927277394</v>
+        <v>0.6830409721829971</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.3141954534216449</v>
+        <v>0.6247054828877507</v>
       </c>
     </row>
     <row r="84">
@@ -23776,22 +23776,22 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4541244467628531</v>
+        <v>0.6099369545174045</v>
       </c>
       <c r="C84" t="n">
         <v>2.069814594904052</v>
       </c>
       <c r="D84" t="n">
-        <v>0.7349399443823348</v>
+        <v>0.5980982533979948</v>
       </c>
       <c r="E84" t="n">
-        <v>1.799684339363429</v>
+        <v>1.922781822971031</v>
       </c>
       <c r="F84" t="n">
-        <v>0.3193576077007216</v>
+        <v>0.692904943357579</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.2992270930642089</v>
+        <v>0.6433968363624428</v>
       </c>
     </row>
     <row r="85">
@@ -23801,22 +23801,22 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4176288686809861</v>
+        <v>0.5653920495638887</v>
       </c>
       <c r="C85" t="n">
         <v>2.043789449957827</v>
       </c>
       <c r="D85" t="n">
-        <v>0.7097523348154091</v>
+        <v>0.5557401398604775</v>
       </c>
       <c r="E85" t="n">
-        <v>1.773941201732855</v>
+        <v>1.880434252112059</v>
       </c>
       <c r="F85" t="n">
-        <v>0.2830707755575239</v>
+        <v>0.6932805724241482</v>
       </c>
       <c r="G85" t="n">
-        <v>-0.3010930812770216</v>
+        <v>0.6226910018568337</v>
       </c>
     </row>
     <row r="86">
@@ -23826,22 +23826,22 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.3829992750310373</v>
+        <v>0.5234827845817798</v>
       </c>
       <c r="C86" t="n">
         <v>2.018258228766336</v>
       </c>
       <c r="D86" t="n">
-        <v>0.6853719589446214</v>
+        <v>0.5156907466797302</v>
       </c>
       <c r="E86" t="n">
-        <v>1.749040714524311</v>
+        <v>1.840394941576656</v>
       </c>
       <c r="F86" t="n">
-        <v>0.247591312455409</v>
+        <v>0.6974290235201682</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.274064819502308</v>
+        <v>0.6258066831076214</v>
       </c>
     </row>
     <row r="87">
@@ -23851,22 +23851,22 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.3509532185293962</v>
+        <v>0.4852584530925115</v>
       </c>
       <c r="C87" t="n">
         <v>1.993290977239602</v>
       </c>
       <c r="D87" t="n">
-        <v>0.6622016817500258</v>
+        <v>0.4787081633266599</v>
       </c>
       <c r="E87" t="n">
-        <v>1.725341341681466</v>
+        <v>1.803421168585722</v>
       </c>
       <c r="F87" t="n">
-        <v>0.2130305490662887</v>
+        <v>0.7046802910708568</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.2596112291123124</v>
+        <v>0.6319748563461984</v>
       </c>
     </row>
     <row r="88">
@@ -23876,22 +23876,22 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.3223437388327481</v>
+        <v>0.4529833435612529</v>
       </c>
       <c r="C88" t="n">
         <v>1.968989740303734</v>
       </c>
       <c r="D88" t="n">
-        <v>0.6426513469683091</v>
+        <v>0.4473220867836802</v>
       </c>
       <c r="E88" t="n">
-        <v>1.705070943949424</v>
+        <v>1.772042841250198</v>
       </c>
       <c r="F88" t="n">
-        <v>0.1794845305633412</v>
+        <v>0.706083914759652</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.2124503375428581</v>
+        <v>0.6298259462883342</v>
       </c>
     </row>
     <row r="89">
@@ -23901,22 +23901,22 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.2958496088273648</v>
+        <v>0.423000885447228</v>
       </c>
       <c r="C89" t="n">
         <v>1.945448009515209</v>
       </c>
       <c r="D89" t="n">
-        <v>0.6228858430468041</v>
+        <v>0.417655702095524</v>
       </c>
       <c r="E89" t="n">
-        <v>1.68478833730026</v>
+        <v>1.742383396607756</v>
       </c>
       <c r="F89" t="n">
-        <v>0.1470178232631284</v>
+        <v>0.7155696905600237</v>
       </c>
       <c r="G89" t="n">
-        <v>-0.2080537494155159</v>
+        <v>0.6511562456828577</v>
       </c>
     </row>
     <row r="90">
@@ -23926,22 +23926,22 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.2721655383630528</v>
+        <v>0.3975884258232818</v>
       </c>
       <c r="C90" t="n">
         <v>1.922692720667797</v>
       </c>
       <c r="D90" t="n">
-        <v>0.6052171229966739</v>
+        <v>0.3923484615482646</v>
       </c>
       <c r="E90" t="n">
-        <v>1.666513196369384</v>
+        <v>1.717081827960441</v>
       </c>
       <c r="F90" t="n">
-        <v>0.1156884242310992</v>
+        <v>0.6999820228837006</v>
       </c>
       <c r="G90" t="n">
-        <v>-0.2341678542856203</v>
+        <v>0.5979619853638907</v>
       </c>
     </row>
     <row r="91">
@@ -23951,22 +23951,22 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.2509984620624716</v>
+        <v>0.3759238980934694</v>
       </c>
       <c r="C91" t="n">
         <v>1.900746230776112</v>
       </c>
       <c r="D91" t="n">
-        <v>0.5892372860921888</v>
+        <v>0.3703624851422857</v>
       </c>
       <c r="E91" t="n">
-        <v>1.649945374614345</v>
+        <v>1.6951006905945</v>
       </c>
       <c r="F91" t="n">
-        <v>0.08553044185154959</v>
+        <v>0.6897399772325423</v>
       </c>
       <c r="G91" t="n">
-        <v>-0.259115140048714</v>
+        <v>0.5700466595278482</v>
       </c>
     </row>
     <row r="92">
@@ -23976,22 +23976,22 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.2315180956132945</v>
+        <v>0.3564469396863927</v>
       </c>
       <c r="C92" t="n">
         <v>1.879631691819442</v>
       </c>
       <c r="D92" t="n">
-        <v>0.5740429646536356</v>
+        <v>0.3504293466294772</v>
       </c>
       <c r="E92" t="n">
-        <v>1.634204408314548</v>
+        <v>1.675171805053443</v>
       </c>
       <c r="F92" t="n">
-        <v>0.0565608511364819</v>
+        <v>0.6853789637038931</v>
       </c>
       <c r="G92" t="n">
-        <v>-0.3243133775369717</v>
+        <v>0.5348945183060351</v>
       </c>
     </row>
     <row r="93">
@@ -24001,22 +24001,22 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.2134223622445272</v>
+        <v>0.3389054044768587</v>
       </c>
       <c r="C93" t="n">
         <v>1.859385017716077</v>
       </c>
       <c r="D93" t="n">
-        <v>0.5599692141646031</v>
+        <v>0.3324713599926165</v>
       </c>
       <c r="E93" t="n">
-        <v>1.61955654364807</v>
+        <v>1.657217644455148</v>
       </c>
       <c r="F93" t="n">
-        <v>0.0287867835903835</v>
+        <v>0.682803007039974</v>
       </c>
       <c r="G93" t="n">
-        <v>-0.3384069915783122</v>
+        <v>0.5126416172928892</v>
       </c>
     </row>
     <row r="94">
@@ -24026,22 +24026,22 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.1965746565665989</v>
+        <v>0.3227168613501585</v>
       </c>
       <c r="C94" t="n">
         <v>1.839994470754758</v>
       </c>
       <c r="D94" t="n">
-        <v>0.5464091595196567</v>
+        <v>0.3157896175174308</v>
       </c>
       <c r="E94" t="n">
-        <v>1.605437647162368</v>
+        <v>1.640539070896013</v>
       </c>
       <c r="F94" t="n">
-        <v>0.0022054262001563</v>
+        <v>0.6881043717144369</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.3523101001541839</v>
+        <v>0.5045550721757497</v>
       </c>
     </row>
     <row r="95">
@@ -24051,22 +24051,22 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.1818629089557981</v>
+        <v>0.309810014530985</v>
       </c>
       <c r="C95" t="n">
         <v>1.821454670751212</v>
       </c>
       <c r="D95" t="n">
-        <v>0.5349625835933169</v>
+        <v>0.3021296108769968</v>
       </c>
       <c r="E95" t="n">
-        <v>1.593290044320621</v>
+        <v>1.626881006465264</v>
       </c>
       <c r="F95" t="n">
-        <v>-0.023191212954922</v>
+        <v>0.695531381558526</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.3800513086431158</v>
+        <v>0.4901061674613959</v>
       </c>
     </row>
     <row r="96">
@@ -24076,22 +24076,22 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.1695484361087764</v>
+        <v>0.3006110407146527</v>
       </c>
       <c r="C96" t="n">
         <v>1.803762257471688</v>
       </c>
       <c r="D96" t="n">
-        <v>0.5262218253999107</v>
+        <v>0.291958529950743</v>
       </c>
       <c r="E96" t="n">
-        <v>1.583697693938003</v>
+        <v>1.616710780959437</v>
       </c>
       <c r="F96" t="n">
-        <v>-0.0474267905214573</v>
+        <v>0.7028206322400038</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.3664326152904439</v>
+        <v>0.4943455548988327</v>
       </c>
     </row>
     <row r="97">
@@ -24101,22 +24101,22 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.1595201872605036</v>
+        <v>0.2941982276413093</v>
       </c>
       <c r="C97" t="n">
         <v>1.786892152522548</v>
       </c>
       <c r="D97" t="n">
-        <v>0.5187452064313431</v>
+        <v>0.2840441381016847</v>
       </c>
       <c r="E97" t="n">
-        <v>1.575348459328334</v>
+        <v>1.608795576298226</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.07054334242264999</v>
+        <v>0.7027368797651751</v>
       </c>
       <c r="G97" t="n">
-        <v>-0.3461018888878877</v>
+        <v>0.4850182699448058</v>
       </c>
     </row>
     <row r="98">
@@ -24126,22 +24126,22 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.1533525037156193</v>
+        <v>0.2942787970599112</v>
       </c>
       <c r="C98" t="n">
         <v>1.770795541730098</v>
       </c>
       <c r="D98" t="n">
-        <v>0.5160534429764354</v>
+        <v>0.2820315840988638</v>
       </c>
       <c r="E98" t="n">
-        <v>1.571430455640488</v>
+        <v>1.606779823791115</v>
       </c>
       <c r="F98" t="n">
-        <v>-0.09259259876109729</v>
+        <v>0.7044427964306641</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.3753896526303667</v>
+        <v>0.4625492890412964</v>
       </c>
     </row>
     <row r="99">
@@ -24151,22 +24151,22 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.1508279978323625</v>
+        <v>0.2999700099325773</v>
       </c>
       <c r="C99" t="n">
         <v>1.755411573461783</v>
       </c>
       <c r="D99" t="n">
-        <v>0.5173658162644648</v>
+        <v>0.2847715524204293</v>
       </c>
       <c r="E99" t="n">
-        <v>1.57131398342894</v>
+        <v>1.609514549433507</v>
       </c>
       <c r="F99" t="n">
-        <v>-0.1136585682760964</v>
+        <v>0.709522058144282</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.3457688865216968</v>
+        <v>0.467623895442982</v>
       </c>
     </row>
     <row r="100">
@@ -24176,22 +24176,22 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.1509987415674969</v>
+        <v>0.3098624204492477</v>
       </c>
       <c r="C100" t="n">
         <v>1.740636533913782</v>
       </c>
       <c r="D100" t="n">
-        <v>0.5216868677838118</v>
+        <v>0.2911242543220951</v>
       </c>
       <c r="E100" t="n">
-        <v>1.57404003391587</v>
+        <v>1.615860423400203</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.1338498170700892</v>
+        <v>0.7161392793288205</v>
       </c>
       <c r="G100" t="n">
-        <v>-0.3078913637560609</v>
+        <v>0.4812510461943476</v>
       </c>
     </row>
     <row r="101">
@@ -24201,22 +24201,22 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.1522095749569363</v>
+        <v>0.3214838092034746</v>
       </c>
       <c r="C101" t="n">
         <v>1.726373903121119</v>
       </c>
       <c r="D101" t="n">
-        <v>0.5274154041660255</v>
+        <v>0.2992656884120608</v>
       </c>
       <c r="E101" t="n">
-        <v>1.578125946352758</v>
+        <v>1.623994749237296</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.1532934837136462</v>
+        <v>0.7153859543589454</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.2779236805304492</v>
+        <v>0.480045725039361</v>
       </c>
     </row>
     <row r="102">
@@ -24226,22 +24226,22 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.1523825674004397</v>
+        <v>0.3303851585046002</v>
       </c>
       <c r="C102" t="n">
         <v>1.712520663437433</v>
       </c>
       <c r="D102" t="n">
-        <v>0.5303444052935475</v>
+        <v>0.3048444275138726</v>
       </c>
       <c r="E102" t="n">
-        <v>1.579692220085271</v>
+        <v>1.629566495350331</v>
       </c>
       <c r="F102" t="n">
-        <v>-0.172126035152736</v>
+        <v>0.7076463744118615</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.3026816781965653</v>
+        <v>0.4540432718897766</v>
       </c>
     </row>
     <row r="103">
@@ -24251,22 +24251,22 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.1521627219501355</v>
+        <v>0.3391234867798947</v>
       </c>
       <c r="C103" t="n">
         <v>1.698992984167706</v>
       </c>
       <c r="D103" t="n">
-        <v>0.5332814940181736</v>
+        <v>0.3105130534716658</v>
       </c>
       <c r="E103" t="n">
-        <v>1.581203398428159</v>
+        <v>1.63522799534308</v>
       </c>
       <c r="F103" t="n">
-        <v>-0.1904667739543817</v>
+        <v>0.6930174447167597</v>
       </c>
       <c r="G103" t="n">
-        <v>-0.3080328163863087</v>
+        <v>0.4109793178953516</v>
       </c>
     </row>
     <row r="104">
@@ -24276,22 +24276,22 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.1502243332951041</v>
+        <v>0.3452829616609125</v>
       </c>
       <c r="C104" t="n">
         <v>1.685694822920873</v>
       </c>
       <c r="D104" t="n">
-        <v>0.5348236821959702</v>
+        <v>0.3142173565183792</v>
       </c>
       <c r="E104" t="n">
-        <v>1.581445220706621</v>
+        <v>1.638926615343798</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.2084355424202973</v>
+        <v>0.6965011731191452</v>
       </c>
       <c r="G104" t="n">
-        <v>-0.3123872508182084</v>
+        <v>0.4213619107765419</v>
       </c>
     </row>
     <row r="105">
@@ -24301,22 +24301,22 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.144304612941166</v>
+        <v>0.3439312342473979</v>
       </c>
       <c r="C105" t="n">
         <v>1.672554553719479</v>
       </c>
       <c r="D105" t="n">
-        <v>0.5299806493929085</v>
+        <v>0.3110988714661069</v>
       </c>
       <c r="E105" t="n">
-        <v>1.575798562999583</v>
+        <v>1.635804246273531</v>
       </c>
       <c r="F105" t="n">
-        <v>-0.226141095467032</v>
+        <v>0.6852980498528116</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.3736806490680794</v>
+        <v>0.359989460444977</v>
       </c>
     </row>
     <row r="106">
@@ -24326,22 +24326,22 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.1353303871076614</v>
+        <v>0.3382984084008418</v>
       </c>
       <c r="C106" t="n">
         <v>1.659540521309415</v>
       </c>
       <c r="D106" t="n">
-        <v>0.522905150344986</v>
+        <v>0.3049334729129127</v>
       </c>
       <c r="E106" t="n">
-        <v>1.567950279835559</v>
+        <v>1.629636650401268</v>
       </c>
       <c r="F106" t="n">
-        <v>-0.2436513454707227</v>
+        <v>0.6869056661851274</v>
       </c>
       <c r="G106" t="n">
-        <v>-0.3820014168852363</v>
+        <v>0.3531986433679672</v>
       </c>
     </row>
     <row r="107">
@@ -24351,22 +24351,22 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.1230407900591443</v>
+        <v>0.3265365763685739</v>
       </c>
       <c r="C107" t="n">
         <v>1.646621291735614</v>
       </c>
       <c r="D107" t="n">
-        <v>0.5105155274312994</v>
+        <v>0.2930012797347252</v>
       </c>
       <c r="E107" t="n">
-        <v>1.555188299614155</v>
+        <v>1.617703747999346</v>
       </c>
       <c r="F107" t="n">
-        <v>-0.26101839406668</v>
+        <v>0.6863803702268545</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.3624750248847863</v>
+        <v>0.3417178298816584</v>
       </c>
     </row>
     <row r="108">
@@ -24376,22 +24376,22 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.108943337845383</v>
+        <v>0.3124379851784524</v>
       </c>
       <c r="C108" t="n">
         <v>1.633794478184509</v>
       </c>
       <c r="D108" t="n">
-        <v>0.4966451248557284</v>
+        <v>0.2795164308530709</v>
       </c>
       <c r="E108" t="n">
-        <v>1.540950431892552</v>
+        <v>1.604219163933708</v>
       </c>
       <c r="F108" t="n">
-        <v>-0.2782596267447834</v>
+        <v>0.6908668704546491</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.364583215048661</v>
+        <v>0.3267716074325899</v>
       </c>
     </row>
     <row r="109">
@@ -24401,22 +24401,22 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.0931059809507683</v>
+        <v>0.2950945702186542</v>
       </c>
       <c r="C109" t="n">
         <v>1.621053493938226</v>
       </c>
       <c r="D109" t="n">
-        <v>0.4795012731717012</v>
+        <v>0.2629040837603835</v>
       </c>
       <c r="E109" t="n">
-        <v>1.523723002796951</v>
+        <v>1.587608021953651</v>
       </c>
       <c r="F109" t="n">
-        <v>-0.2953844839204713</v>
+        <v>0.7029310572099011</v>
       </c>
       <c r="G109" t="n">
-        <v>-0.3352873485333456</v>
+        <v>0.3519422598677466</v>
       </c>
     </row>
     <row r="110">
@@ -24426,22 +24426,22 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.0761749109325509</v>
+        <v>0.2763720452033269</v>
       </c>
       <c r="C110" t="n">
         <v>1.608407330539844</v>
       </c>
       <c r="D110" t="n">
-        <v>0.4605030903948943</v>
+        <v>0.2452134950652809</v>
       </c>
       <c r="E110" t="n">
-        <v>1.504768291997662</v>
+        <v>1.569919412165646</v>
       </c>
       <c r="F110" t="n">
-        <v>-0.3123830381089751</v>
+        <v>0.6925252703424277</v>
       </c>
       <c r="G110" t="n">
-        <v>-0.3458125841009503</v>
+        <v>0.3052981588398746</v>
       </c>
     </row>
     <row r="111">
@@ -24451,22 +24451,22 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.0572988346669132</v>
+        <v>0.2545005341183444</v>
       </c>
       <c r="C111" t="n">
         <v>1.595858616822451</v>
       </c>
       <c r="D111" t="n">
-        <v>0.4386810632273672</v>
+        <v>0.2250552267050334</v>
       </c>
       <c r="E111" t="n">
-        <v>1.483269763373663</v>
+        <v>1.549764913040768</v>
       </c>
       <c r="F111" t="n">
-        <v>-0.3292392583197378</v>
+        <v>0.68751844163946</v>
       </c>
       <c r="G111" t="n">
-        <v>-0.3719606210236063</v>
+        <v>0.2755476327879543</v>
       </c>
     </row>
     <row r="112">
@@ -24476,22 +24476,22 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.0359847875665992</v>
+        <v>0.2275152960714661</v>
       </c>
       <c r="C112" t="n">
         <v>1.58343551956489</v>
       </c>
       <c r="D112" t="n">
-        <v>0.4113887717105182</v>
+        <v>0.1999680779561197</v>
       </c>
       <c r="E112" t="n">
-        <v>1.456764462825989</v>
+        <v>1.524682405146927</v>
       </c>
       <c r="F112" t="n">
-        <v>-0.3459229752222283</v>
+        <v>0.688452535445864</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.3548089926891826</v>
+        <v>0.2712385792738185</v>
       </c>
     </row>
     <row r="113">
@@ -24501,22 +24501,22 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.0149236387861892</v>
+        <v>0.2022603894985892</v>
       </c>
       <c r="C113" t="n">
         <v>1.571180361120048</v>
       </c>
       <c r="D113" t="n">
-        <v>0.3851507507563267</v>
+        <v>0.1770323310093169</v>
       </c>
       <c r="E113" t="n">
-        <v>1.431172228785673</v>
+        <v>1.501751639778083</v>
       </c>
       <c r="F113" t="n">
-        <v>-0.3623732624056648</v>
+        <v>0.6878464022669748</v>
       </c>
       <c r="G113" t="n">
-        <v>-0.4059971002398472</v>
+        <v>0.2292907208599379</v>
       </c>
     </row>
     <row r="114">
@@ -24526,22 +24526,22 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-0.0073362507312411</v>
+        <v>0.1743118717223344</v>
       </c>
       <c r="C114" t="n">
         <v>1.55916151755453</v>
       </c>
       <c r="D114" t="n">
-        <v>0.3554559387221738</v>
+        <v>0.1513864549959225</v>
       </c>
       <c r="E114" t="n">
-        <v>1.402558181075743</v>
+        <v>1.476112055830333</v>
       </c>
       <c r="F114" t="n">
-        <v>-0.3785432330427212</v>
+        <v>0.6904985821029773</v>
       </c>
       <c r="G114" t="n">
-        <v>-0.416313547193515</v>
+        <v>0.2164882052841154</v>
       </c>
     </row>
     <row r="115">
@@ -24551,22 +24551,22 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-0.0306533174780774</v>
+        <v>0.1441542614180511</v>
       </c>
       <c r="C115" t="n">
         <v>1.547453922129047</v>
       </c>
       <c r="D115" t="n">
-        <v>0.3230133012497411</v>
+        <v>0.1240774547664722</v>
       </c>
       <c r="E115" t="n">
-        <v>1.371431060676987</v>
+        <v>1.448809870700203</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.3943684487019854</v>
+        <v>0.6877010000327474</v>
       </c>
       <c r="G115" t="n">
-        <v>-0.4937575076396659</v>
+        <v>0.1608090689808535</v>
       </c>
     </row>
     <row r="116">
@@ -24576,22 +24576,22 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-0.0527728621050995</v>
+        <v>0.1159181338097834</v>
       </c>
       <c r="C116" t="n">
         <v>1.536116744767253</v>
       </c>
       <c r="D116" t="n">
-        <v>0.2908492925889625</v>
+        <v>0.0982473152787697</v>
       </c>
       <c r="E116" t="n">
-        <v>1.340604572520175</v>
+        <v>1.422985687827328</v>
       </c>
       <c r="F116" t="n">
-        <v>-0.4097739368045959</v>
+        <v>0.6887418338124126</v>
       </c>
       <c r="G116" t="n">
-        <v>-0.5411943126202933</v>
+        <v>0.127996352162355</v>
       </c>
     </row>
     <row r="117">
@@ -24601,22 +24601,22 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-0.07226076540107</v>
+        <v>0.0924787205201926</v>
       </c>
       <c r="C117" t="n">
         <v>1.525184720345438</v>
       </c>
       <c r="D117" t="n">
-        <v>0.2618866574740863</v>
+        <v>0.07683284180811339</v>
       </c>
       <c r="E117" t="n">
-        <v>1.31281280520297</v>
+        <v>1.401576305647654</v>
       </c>
       <c r="F117" t="n">
-        <v>-0.4246916796184321</v>
+        <v>0.6880743770356631</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.5650866666719585</v>
+        <v>0.1057969304546138</v>
       </c>
     </row>
     <row r="118">
@@ -24626,22 +24626,22 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-0.0901670874895141</v>
+        <v>0.07084006471816991</v>
       </c>
       <c r="C118" t="n">
         <v>1.51467119214928</v>
       </c>
       <c r="D118" t="n">
-        <v>0.2329692332552912</v>
+        <v>0.0566033072785767</v>
       </c>
       <c r="E118" t="n">
-        <v>1.285232787152362</v>
+        <v>1.38135124810111</v>
       </c>
       <c r="F118" t="n">
-        <v>-0.4390784307247073</v>
+        <v>0.674605266459288</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.5950851329794613</v>
+        <v>0.0569086755459748</v>
       </c>
     </row>
     <row r="119">
@@ -24651,22 +24651,22 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-0.1061450592019197</v>
+        <v>0.052461078471226</v>
       </c>
       <c r="C119" t="n">
         <v>1.504622234354639</v>
       </c>
       <c r="D119" t="n">
-        <v>0.2063217339608396</v>
+        <v>0.0395234529671608</v>
       </c>
       <c r="E119" t="n">
-        <v>1.259805619506975</v>
+        <v>1.36427507701792</v>
       </c>
       <c r="F119" t="n">
-        <v>-0.4528948835074083</v>
+        <v>0.6614673558397195</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.6205667343291499</v>
+        <v>0.0211116989938598</v>
       </c>
     </row>
     <row r="120">
@@ -24676,22 +24676,22 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>-0.1204470849887862</v>
+        <v>0.036456871211556</v>
       </c>
       <c r="C120" t="n">
         <v>1.49505561026837</v>
       </c>
       <c r="D120" t="n">
-        <v>0.1806690429580699</v>
+        <v>0.0242056905036449</v>
       </c>
       <c r="E120" t="n">
-        <v>1.235417037875319</v>
+        <v>1.348960261850535</v>
       </c>
       <c r="F120" t="n">
-        <v>-0.4661189776070095</v>
+        <v>0.64250311974708</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.6625576724146596</v>
+        <v>-0.0520602931087701</v>
       </c>
     </row>
     <row r="121">
@@ -24701,22 +24701,22 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-0.1334759770002389</v>
+        <v>0.0227828170558888</v>
       </c>
       <c r="C121" t="n">
         <v>1.485986859490123</v>
       </c>
       <c r="D121" t="n">
-        <v>0.1574054700933942</v>
+        <v>0.0113559635059237</v>
       </c>
       <c r="E121" t="n">
-        <v>1.213285656752463</v>
+        <v>1.336113402994905</v>
       </c>
       <c r="F121" t="n">
-        <v>-0.4787366229105553</v>
+        <v>0.6532623210519628</v>
       </c>
       <c r="G121" t="n">
-        <v>-0.6429004458290986</v>
+        <v>0.0043489214649952</v>
       </c>
     </row>
     <row r="122">
@@ -24726,22 +24726,22 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-0.1463770588422701</v>
+        <v>0.0080574634229895</v>
       </c>
       <c r="C122" t="n">
         <v>1.477386764752884</v>
       </c>
       <c r="D122" t="n">
-        <v>0.1324669323743705</v>
+        <v>-0.002691116290018</v>
       </c>
       <c r="E122" t="n">
-        <v>1.189715879520908</v>
+        <v>1.322068898260579</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.4907476806800502</v>
+        <v>0.6631901624342172</v>
       </c>
       <c r="G122" t="n">
-        <v>-0.6622831314349884</v>
+        <v>0.0265606222483954</v>
       </c>
     </row>
     <row r="123">
@@ -24751,22 +24751,22 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-0.1566734489849262</v>
+        <v>-0.0023362408263549</v>
       </c>
       <c r="C123" t="n">
         <v>1.469276055402131</v>
       </c>
       <c r="D123" t="n">
-        <v>0.1105623574126664</v>
+        <v>-0.0128217099956127</v>
       </c>
       <c r="E123" t="n">
-        <v>1.168933054114914</v>
+        <v>1.31193884027021</v>
       </c>
       <c r="F123" t="n">
-        <v>-0.5021422120121798</v>
+        <v>0.6718173694083465</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.6431430050076827</v>
+        <v>0.0648692107394699</v>
       </c>
     </row>
     <row r="124">
@@ -24776,22 +24776,22 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>-0.1628839217917039</v>
+        <v>-0.0056696624130143</v>
       </c>
       <c r="C124" t="n">
         <v>1.461652257400579</v>
       </c>
       <c r="D124" t="n">
-        <v>0.0937416219998468</v>
+        <v>-0.0167515064746808</v>
       </c>
       <c r="E124" t="n">
-        <v>1.152949862848874</v>
+        <v>1.308007575749647</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.5129315797242443</v>
+        <v>0.6690820665021289</v>
       </c>
       <c r="G124" t="n">
-        <v>-0.6624533795396419</v>
+        <v>0.0650215470154442</v>
       </c>
     </row>
     <row r="125">
@@ -24801,22 +24801,22 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-0.166484164751941</v>
+        <v>-0.0053302023067844</v>
       </c>
       <c r="C125" t="n">
         <v>1.454466154119277</v>
       </c>
       <c r="D125" t="n">
-        <v>0.0793417244652365</v>
+        <v>-0.0177231775316513</v>
       </c>
       <c r="E125" t="n">
-        <v>1.139365642697076</v>
+        <v>1.307033146375313</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.5231616200207898</v>
+        <v>0.6668840198718226</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.6551198262273258</v>
+        <v>0.0141122551244026</v>
       </c>
     </row>
     <row r="126">
@@ -24826,22 +24826,22 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>-0.1686945447884287</v>
+        <v>-0.0026629447270145</v>
       </c>
       <c r="C126" t="n">
         <v>1.447663596566767</v>
       </c>
       <c r="D126" t="n">
-        <v>0.0668232599259504</v>
+        <v>-0.016380382360748</v>
       </c>
       <c r="E126" t="n">
-        <v>1.127597922158111</v>
+        <v>1.308372699118284</v>
       </c>
       <c r="F126" t="n">
-        <v>-0.5328927636416779</v>
+        <v>0.6445496830467499</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.6764286240618185</v>
+        <v>-0.07889840150247519</v>
       </c>
     </row>
     <row r="127">
@@ -24851,22 +24851,22 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>-0.1711709006759127</v>
+        <v>-0.001118267748817</v>
       </c>
       <c r="C127" t="n">
         <v>1.441197526937789</v>
       </c>
       <c r="D127" t="n">
-        <v>0.0532514232809218</v>
+        <v>-0.016087564750074</v>
       </c>
       <c r="E127" t="n">
-        <v>1.114960687363052</v>
+        <v>1.308662365270559</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.5421982713591466</v>
+        <v>0.6024861412244344</v>
       </c>
       <c r="G127" t="n">
-        <v>-0.6976540536562563</v>
+        <v>-0.1572101071334867</v>
       </c>
     </row>
     <row r="128">
@@ -24876,22 +24876,22 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>-0.1737467318620402</v>
+        <v>0.0002233069437016</v>
       </c>
       <c r="C128" t="n">
         <v>1.435021609362427</v>
       </c>
       <c r="D128" t="n">
-        <v>0.0394483908373279</v>
+        <v>-0.0159593189601632</v>
       </c>
       <c r="E128" t="n">
-        <v>1.102121261625358</v>
+        <v>1.308787151770806</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.5511439088070802</v>
+        <v>0.4963887445076538</v>
       </c>
       <c r="G128" t="n">
-        <v>-0.7355301490576749</v>
+        <v>-0.4003028493845856</v>
       </c>
     </row>
     <row r="129">
@@ -24901,22 +24901,22 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-0.1764332482203012</v>
+        <v>0.0017171710407084</v>
       </c>
       <c r="C129" t="n">
         <v>1.429079962589927</v>
       </c>
       <c r="D129" t="n">
-        <v>0.0278513971216698</v>
+        <v>-0.0153406253110954</v>
       </c>
       <c r="E129" t="n">
-        <v>1.091301003121791</v>
+        <v>1.309402698256975</v>
       </c>
       <c r="F129" t="n">
-        <v>-0.5597939923697799</v>
+        <v>0.4451135010369384</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.7553460098289526</v>
+        <v>-0.4541056245887104</v>
       </c>
     </row>
     <row r="130">
@@ -24926,22 +24926,22 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>-0.1799698791647463</v>
+        <v>0.000681383684653</v>
       </c>
       <c r="C130" t="n">
         <v>1.42331828243418</v>
       </c>
       <c r="D130" t="n">
-        <v>0.0152059591127313</v>
+        <v>-0.0174390513958999</v>
       </c>
       <c r="E130" t="n">
-        <v>1.079491491364381</v>
+        <v>1.307300820755188</v>
       </c>
       <c r="F130" t="n">
-        <v>-0.5682161406744687</v>
+        <v>0.4182593367631521</v>
       </c>
       <c r="G130" t="n">
-        <v>-0.7832346723393453</v>
+        <v>-0.4952873870308217</v>
       </c>
     </row>
     <row r="131">
@@ -24951,22 +24951,22 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>-0.1817919127987803</v>
+        <v>0.0033014319841302</v>
       </c>
       <c r="C131" t="n">
         <v>1.417691621680092</v>
       </c>
       <c r="D131" t="n">
-        <v>0.0074980482679727</v>
+        <v>-0.0159698532211571</v>
       </c>
       <c r="E131" t="n">
-        <v>1.072082477908853</v>
+        <v>1.308765177314708</v>
       </c>
       <c r="F131" t="n">
-        <v>-0.576459853192744</v>
+        <v>0.3925327453967541</v>
       </c>
       <c r="G131" t="n">
-        <v>-0.7791116102632488</v>
+        <v>-0.5539461392809542</v>
       </c>
     </row>
     <row r="132">
@@ -24976,22 +24976,22 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>-0.181938763317337</v>
+        <v>0.0085055153520556</v>
       </c>
       <c r="C132" t="n">
         <v>1.412149915278012</v>
       </c>
       <c r="D132" t="n">
-        <v>0.0031471742649085</v>
+        <v>-0.0127476201463925</v>
       </c>
       <c r="E132" t="n">
-        <v>1.067784712562389</v>
+        <v>1.311981502844401</v>
       </c>
       <c r="F132" t="n">
-        <v>-0.5845958420859245</v>
+        <v>0.3869477110106105</v>
       </c>
       <c r="G132" t="n">
-        <v>-0.808266709584776</v>
+        <v>-0.5699124556181154</v>
       </c>
     </row>
     <row r="133">
@@ -25001,22 +25001,22 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-0.1810818812714323</v>
+        <v>0.015437117007621</v>
       </c>
       <c r="C133" t="n">
         <v>1.406659983210084</v>
       </c>
       <c r="D133" t="n">
-        <v>0.002078219282728</v>
+        <v>-0.0078759499184859</v>
       </c>
       <c r="E133" t="n">
-        <v>1.066457089692669</v>
+        <v>1.316846614974793</v>
       </c>
       <c r="F133" t="n">
-        <v>-0.5927032151880248</v>
+        <v>0.3657871372057313</v>
       </c>
       <c r="G133" t="n">
-        <v>-0.7921369109086718</v>
+        <v>-0.6333236325231676</v>
       </c>
     </row>
     <row r="134">
@@ -25026,22 +25026,22 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-0.1798929138632656</v>
+        <v>0.0225769335664494</v>
       </c>
       <c r="C134" t="n">
         <v>1.401114972316795</v>
       </c>
       <c r="D134" t="n">
-        <v>0.0026622030305363</v>
+        <v>-0.0033246701185527</v>
       </c>
       <c r="E134" t="n">
-        <v>1.066607951086467</v>
+        <v>1.321390648232084</v>
       </c>
       <c r="F134" t="n">
-        <v>-0.6008702353517623</v>
+        <v>0.3722285384270513</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.7777895274433365</v>
+        <v>-0.6315022200051994</v>
       </c>
     </row>
     <row r="135">
@@ -25051,22 +25051,22 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>-0.1785260309515572</v>
+        <v>0.0309087220461536</v>
       </c>
       <c r="C135" t="n">
         <v>1.395446808832448</v>
       </c>
       <c r="D135" t="n">
-        <v>0.006428886067642</v>
+        <v>0.0025892694898088</v>
       </c>
       <c r="E135" t="n">
-        <v>1.069582663116758</v>
+        <v>1.327297487220055</v>
       </c>
       <c r="F135" t="n">
-        <v>-0.6091818526825652</v>
+        <v>0.3841949302401621</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.7780574818781019</v>
+        <v>-0.6367547976544345</v>
       </c>
     </row>
     <row r="136">
@@ -25076,22 +25076,22 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-0.1795095575252847</v>
+        <v>0.0346040836820438</v>
       </c>
       <c r="C136" t="n">
         <v>1.389587111347781</v>
       </c>
       <c r="D136" t="n">
-        <v>0.0076349636323787</v>
+        <v>0.004083702825179</v>
       </c>
       <c r="E136" t="n">
-        <v>1.070192805210844</v>
+        <v>1.328785986346104</v>
       </c>
       <c r="F136" t="n">
-        <v>-0.6177322825015913</v>
+        <v>0.3881810364707075</v>
       </c>
       <c r="G136" t="n">
-        <v>-0.7529092066513182</v>
+        <v>-0.6422438077046977</v>
       </c>
     </row>
     <row r="137">
@@ -25101,22 +25101,22 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>-0.1822904136677743</v>
+        <v>0.0352642782730585</v>
       </c>
       <c r="C137" t="n">
         <v>1.383486284559478</v>
       </c>
       <c r="D137" t="n">
-        <v>0.0075269702760323</v>
+        <v>0.002928517540913</v>
       </c>
       <c r="E137" t="n">
-        <v>1.06944449016637</v>
+        <v>1.327625006848462</v>
       </c>
       <c r="F137" t="n">
-        <v>-0.62658930412424</v>
+        <v>0.3800772613630653</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.7674639332314797</v>
+        <v>-0.6928547729568129</v>
       </c>
     </row>
     <row r="138">
@@ -25126,22 +25126,22 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-0.1850798136873026</v>
+        <v>0.0366301423207353</v>
       </c>
       <c r="C138" t="n">
         <v>1.377098547005987</v>
       </c>
       <c r="D138" t="n">
-        <v>0.0091927974012193</v>
+        <v>0.0022335333604575</v>
       </c>
       <c r="E138" t="n">
-        <v>1.070226458247349</v>
+        <v>1.326923912930884</v>
       </c>
       <c r="F138" t="n">
-        <v>-0.6358057135213003</v>
+        <v>0.3857739464092432</v>
       </c>
       <c r="G138" t="n">
-        <v>-0.7605393854836451</v>
+        <v>-0.7051092433391372</v>
       </c>
     </row>
     <row r="139">
@@ -25151,22 +25151,22 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>-0.188726603636796</v>
+        <v>0.036987342290961</v>
       </c>
       <c r="C139" t="n">
         <v>1.370351548694358</v>
       </c>
       <c r="D139" t="n">
-        <v>0.0112119680641669</v>
+        <v>0.0005283851440558</v>
       </c>
       <c r="E139" t="n">
-        <v>1.07130489188285</v>
+        <v>1.325213459621359</v>
       </c>
       <c r="F139" t="n">
-        <v>-0.6454377747835347</v>
+        <v>0.4013919815154684</v>
       </c>
       <c r="G139" t="n">
-        <v>-0.7250296367629383</v>
+        <v>-0.6772943869312873</v>
       </c>
     </row>
     <row r="140">
@@ -25176,22 +25176,22 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>-0.1955917904937563</v>
+        <v>0.0319743608659519</v>
       </c>
       <c r="C140" t="n">
         <v>1.363213077379434</v>
       </c>
       <c r="D140" t="n">
-        <v>0.0094999963360349</v>
+        <v>-0.0060098021018737</v>
       </c>
       <c r="E140" t="n">
-        <v>1.068919566280451</v>
+        <v>1.318672026001913</v>
       </c>
       <c r="F140" t="n">
-        <v>-0.6555367114716207</v>
+        <v>0.392191716232175</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.7329627557428011</v>
+        <v>-0.7299370419300919</v>
       </c>
     </row>
     <row r="141">
@@ -25201,22 +25201,22 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>-0.2073736785433209</v>
+        <v>0.0193355453795678</v>
       </c>
       <c r="C141" t="n">
         <v>1.355689651435779</v>
       </c>
       <c r="D141" t="n">
-        <v>0.0028549186709438</v>
+        <v>-0.0190768707297936</v>
       </c>
       <c r="E141" t="n">
-        <v>1.061896077423853</v>
+        <v>1.305604926897948</v>
       </c>
       <c r="F141" t="n">
-        <v>-0.6661267629394099</v>
+        <v>0.3933492248850926</v>
       </c>
       <c r="G141" t="n">
-        <v>-0.7318484465083908</v>
+        <v>-0.7360163033623059</v>
       </c>
     </row>
     <row r="142">
@@ -25226,22 +25226,22 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>-0.2262065032734632</v>
+        <v>-0.0047803381401969</v>
       </c>
       <c r="C142" t="n">
         <v>1.347762445330285</v>
       </c>
       <c r="D142" t="n">
-        <v>-0.0120686143454857</v>
+        <v>-0.0418195814842172</v>
       </c>
       <c r="E142" t="n">
-        <v>1.047155979104883</v>
+        <v>1.282866862341851</v>
       </c>
       <c r="F142" t="n">
-        <v>-0.67719708237554</v>
+        <v>0.3861823701093279</v>
       </c>
       <c r="G142" t="n">
-        <v>-0.6827864751556115</v>
+        <v>-0.7491574355640216</v>
       </c>
     </row>
     <row r="143">
@@ -25251,22 +25251,22 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>-0.2526146350487821</v>
+        <v>-0.0421841817640218</v>
       </c>
       <c r="C143" t="n">
         <v>1.339491595016226</v>
       </c>
       <c r="D143" t="n">
-        <v>-0.0380334853813995</v>
+        <v>-0.0762050530562845</v>
       </c>
       <c r="E143" t="n">
-        <v>1.022135831731539</v>
+        <v>1.248489956709555</v>
       </c>
       <c r="F143" t="n">
-        <v>-0.6886840954977781</v>
+        <v>0.3801341011090964</v>
       </c>
       <c r="G143" t="n">
-        <v>-0.6950651971931048</v>
+        <v>-0.7621717834508339</v>
       </c>
     </row>
     <row r="144">
@@ -25276,22 +25276,22 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-0.2824979252690935</v>
+        <v>-0.08494728365232281</v>
       </c>
       <c r="C144" t="n">
         <v>1.330965328825113</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.06890420846477061</v>
+        <v>-0.1149156673393316</v>
       </c>
       <c r="E144" t="n">
-        <v>0.9924390055595708</v>
+        <v>1.209789386792187</v>
       </c>
       <c r="F144" t="n">
-        <v>-0.7004584962460175</v>
+        <v>0.3672303480515427</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.7716703899888221</v>
+        <v>-0.8141165855082768</v>
       </c>
     </row>
     <row r="145">
@@ -25301,22 +25301,22 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>-0.3118388662426248</v>
+        <v>-0.1265722925041137</v>
       </c>
       <c r="C145" t="n">
         <v>1.322292558371933</v>
       </c>
       <c r="D145" t="n">
-        <v>-0.100364374662055</v>
+        <v>-0.153077506425892</v>
       </c>
       <c r="E145" t="n">
-        <v>0.9622083646259654</v>
+        <v>1.171637169796298</v>
       </c>
       <c r="F145" t="n">
-        <v>-0.7123683830160349</v>
+        <v>0.3511362494683082</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.8272412846939561</v>
+        <v>-0.8675113464213988</v>
       </c>
     </row>
     <row r="146">
@@ -25326,22 +25326,22 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-0.3390549900211277</v>
+        <v>-0.163822320316717</v>
       </c>
       <c r="C146" t="n">
         <v>1.313563940999623</v>
       </c>
       <c r="D146" t="n">
-        <v>-0.1285116467903364</v>
+        <v>-0.1871101870716509</v>
       </c>
       <c r="E146" t="n">
-        <v>0.9350923016204692</v>
+        <v>1.137614073725006</v>
       </c>
       <c r="F146" t="n">
-        <v>-0.7242651474746564</v>
+        <v>0.3465313335384454</v>
       </c>
       <c r="G146" t="n">
-        <v>-0.8437835359236823</v>
+        <v>-0.8861246989988056</v>
       </c>
     </row>
     <row r="147">
@@ -25351,22 +25351,22 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-0.3661625897573659</v>
+        <v>-0.2020587098478725</v>
       </c>
       <c r="C147" t="n">
         <v>1.304857836175983</v>
       </c>
       <c r="D147" t="n">
-        <v>-0.1587027681793706</v>
+        <v>-0.222546261631777</v>
       </c>
       <c r="E147" t="n">
-        <v>0.9062590596379434</v>
+        <v>1.102188120301292</v>
       </c>
       <c r="F147" t="n">
-        <v>-0.7360255474194657</v>
+        <v>0.3504118527242225</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.8468687926517301</v>
+        <v>-0.906140085349724</v>
       </c>
     </row>
     <row r="148">
@@ -25376,22 +25376,22 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-0.3923003319255329</v>
+        <v>-0.2385548763041498</v>
       </c>
       <c r="C148" t="n">
         <v>1.296290312645529</v>
       </c>
       <c r="D148" t="n">
-        <v>-0.1880440054934107</v>
+        <v>-0.2561149883029754</v>
       </c>
       <c r="E148" t="n">
-        <v>0.8782142598533418</v>
+        <v>1.068629383289395</v>
       </c>
       <c r="F148" t="n">
-        <v>-0.7475165381094604</v>
+        <v>0.351439415447379</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.8381276970728344</v>
+        <v>-0.932017322448341</v>
       </c>
     </row>
     <row r="149">
@@ -25401,22 +25401,22 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-0.4169055921764748</v>
+        <v>-0.2728902621228517</v>
       </c>
       <c r="C149" t="n">
         <v>1.287957492288714</v>
       </c>
       <c r="D149" t="n">
-        <v>-0.2170336572807425</v>
+        <v>-0.2880007034455145</v>
       </c>
       <c r="E149" t="n">
-        <v>0.850612852923148</v>
+        <v>1.036753314495423</v>
       </c>
       <c r="F149" t="n">
-        <v>-0.7586167899267078</v>
+        <v>0.3464843913310446</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.8459667896407741</v>
+        <v>-0.9836233644820088</v>
       </c>
     </row>
     <row r="150">
@@ -25426,22 +25426,22 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>-0.4395570316381032</v>
+        <v>-0.304082931930546</v>
       </c>
       <c r="C150" t="n">
         <v>1.279971366246844</v>
       </c>
       <c r="D150" t="n">
-        <v>-0.2444888808200991</v>
+        <v>-0.317098849915882</v>
       </c>
       <c r="E150" t="n">
-        <v>0.8245215981009508</v>
+        <v>1.007664318677629</v>
       </c>
       <c r="F150" t="n">
-        <v>-0.7692141956069931</v>
+        <v>0.3566082241225611</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.8235043376107761</v>
+        <v>-0.983586939156795</v>
       </c>
     </row>
     <row r="151">
@@ -25451,22 +25451,22 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>-0.4608974966580665</v>
+        <v>-0.3332243318256416</v>
       </c>
       <c r="C151" t="n">
         <v>1.272420006044874</v>
       </c>
       <c r="D151" t="n">
-        <v>-0.2714643479113618</v>
+        <v>-0.3442007595007932</v>
       </c>
       <c r="E151" t="n">
-        <v>0.7990121985991476</v>
+        <v>0.9805718325529272</v>
       </c>
       <c r="F151" t="n">
-        <v>-0.779212881709815</v>
+        <v>0.358578141928229</v>
       </c>
       <c r="G151" t="n">
-        <v>-0.8304818065221273</v>
+        <v>-1.010501559096833</v>
       </c>
     </row>
     <row r="152">
@@ -25476,22 +25476,22 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-0.4820741053774213</v>
+        <v>-0.3630719117509957</v>
       </c>
       <c r="C152" t="n">
         <v>1.265369058892201</v>
       </c>
       <c r="D152" t="n">
-        <v>-0.3005802240494684</v>
+        <v>-0.3719693294470344</v>
       </c>
       <c r="E152" t="n">
-        <v>0.7716795937248735</v>
+        <v>0.952813010014142</v>
       </c>
       <c r="F152" t="n">
-        <v>-0.7885290737730505</v>
+        <v>0.3604772475888462</v>
       </c>
       <c r="G152" t="n">
-        <v>-0.8988838669452313</v>
+        <v>-1.050255889949877</v>
       </c>
     </row>
     <row r="153">
@@ -25501,22 +25501,22 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>-0.5018385984696243</v>
+        <v>-0.3908208604063601</v>
       </c>
       <c r="C153" t="n">
         <v>1.258909167797001</v>
       </c>
       <c r="D153" t="n">
-        <v>-0.3291128966938994</v>
+        <v>-0.3975981670974445</v>
       </c>
       <c r="E153" t="n">
-        <v>0.744952226754334</v>
+        <v>0.9271933433853736</v>
       </c>
       <c r="F153" t="n">
-        <v>-0.7970745860906199</v>
+        <v>0.3567554129663065</v>
       </c>
       <c r="G153" t="n">
-        <v>-0.94034486319138</v>
+        <v>-1.089857828733293</v>
       </c>
     </row>
     <row r="154">
@@ -25526,22 +25526,22 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>-0.5187341907858917</v>
+        <v>-0.414433937860486</v>
       </c>
       <c r="C154" t="n">
         <v>1.253095449458147</v>
       </c>
       <c r="D154" t="n">
-        <v>-0.3557833500930334</v>
+        <v>-0.4196456981761443</v>
       </c>
       <c r="E154" t="n">
-        <v>0.7200726831738886</v>
+        <v>0.90515348307774</v>
       </c>
       <c r="F154" t="n">
-        <v>-0.8047741317308184</v>
+        <v>0.3480115794633615</v>
       </c>
       <c r="G154" t="n">
-        <v>-1.015385850597196</v>
+        <v>-1.141862593014435</v>
       </c>
     </row>
     <row r="155">
@@ -25551,22 +25551,22 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>-0.5309534521048839</v>
+        <v>-0.4307160862854782</v>
       </c>
       <c r="C155" t="n">
         <v>1.247978082126054</v>
       </c>
       <c r="D155" t="n">
-        <v>-0.3778177580761168</v>
+        <v>-0.4353881773515407</v>
       </c>
       <c r="E155" t="n">
-        <v>0.6995917033331578</v>
+        <v>0.8894160222383584</v>
       </c>
       <c r="F155" t="n">
-        <v>-0.8115723537501177</v>
+        <v>0.3304156601712834</v>
       </c>
       <c r="G155" t="n">
-        <v>-1.168235581516655</v>
+        <v>-1.238525164399782</v>
       </c>
     </row>
     <row r="156">
@@ -25576,22 +25576,22 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>-0.5376622045287548</v>
+        <v>-0.4378692409773845</v>
       </c>
       <c r="C156" t="n">
         <v>1.243559482555015</v>
       </c>
       <c r="D156" t="n">
-        <v>-0.3924866192573493</v>
+        <v>-0.4430668048673214</v>
       </c>
       <c r="E156" t="n">
-        <v>0.686036257901657</v>
+        <v>0.8817398707285707</v>
       </c>
       <c r="F156" t="n">
-        <v>-0.8174492607693298</v>
+        <v>0.3146924669111348</v>
       </c>
       <c r="G156" t="n">
-        <v>-1.267616121746084</v>
+        <v>-1.305382172033119</v>
       </c>
     </row>
     <row r="157">
@@ -25601,22 +25601,22 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-0.5404972009164799</v>
+        <v>-0.4392132829247024</v>
       </c>
       <c r="C157" t="n">
         <v>1.239816560644606</v>
       </c>
       <c r="D157" t="n">
-        <v>-0.4021519022456319</v>
+        <v>-0.4459537321169948</v>
       </c>
       <c r="E157" t="n">
-        <v>0.6772374965162866</v>
+        <v>0.8788537835162458</v>
       </c>
       <c r="F157" t="n">
-        <v>-0.8224310392210358</v>
+        <v>0.2999071619296389</v>
       </c>
       <c r="G157" t="n">
-        <v>-1.344359668525745</v>
+        <v>-1.358027959331071</v>
       </c>
     </row>
     <row r="158">
@@ -25626,22 +25626,22 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-0.541548592264119</v>
+        <v>-0.4377006393368092</v>
       </c>
       <c r="C158" t="n">
         <v>1.23669431102082</v>
       </c>
       <c r="D158" t="n">
-        <v>-0.4077231537390764</v>
+        <v>-0.4458568955512153</v>
       </c>
       <c r="E158" t="n">
-        <v>0.6722498479859524</v>
+        <v>0.8789513032342425</v>
       </c>
       <c r="F158" t="n">
-        <v>-0.826570409801534</v>
+        <v>0.2809251408257394</v>
       </c>
       <c r="G158" t="n">
-        <v>-1.389847473650611</v>
+        <v>-1.418039439483866</v>
       </c>
     </row>
     <row r="159">
@@ -25651,22 +25651,22 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>-0.5431082873345553</v>
+        <v>-0.4382974521388392</v>
       </c>
       <c r="C159" t="n">
         <v>1.234151275210423</v>
       </c>
       <c r="D159" t="n">
-        <v>-0.4137153861625244</v>
+        <v>-0.4478926912116618</v>
       </c>
       <c r="E159" t="n">
-        <v>0.6668906607366649</v>
+        <v>0.8769163900167997</v>
       </c>
       <c r="F159" t="n">
-        <v>-0.8299385040114782</v>
+        <v>0.2772856210484112</v>
       </c>
       <c r="G159" t="n">
-        <v>-1.41840639106983</v>
+        <v>-1.468765563298319</v>
       </c>
     </row>
     <row r="160">
@@ -25676,22 +25676,22 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>-0.5443217145359471</v>
+        <v>-0.4379581071946716</v>
       </c>
       <c r="C160" t="n">
         <v>1.23212053723311</v>
       </c>
       <c r="D160" t="n">
-        <v>-0.4162995495179142</v>
+        <v>-0.4484387863313811</v>
       </c>
       <c r="E160" t="n">
-        <v>0.6645192092713335</v>
+        <v>0.8763711270890764</v>
       </c>
       <c r="F160" t="n">
-        <v>-0.8325934617247044</v>
+        <v>0.3249742536322439</v>
       </c>
       <c r="G160" t="n">
-        <v>-1.326094348775481</v>
+        <v>-1.347461234380237</v>
       </c>
     </row>
     <row r="161">
@@ -25701,22 +25701,22 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-0.5454825181224905</v>
+        <v>-0.4384826220490434</v>
       </c>
       <c r="C161" t="n">
         <v>1.23055403928415</v>
       </c>
       <c r="D161" t="n">
-        <v>-0.4196171172934071</v>
+        <v>-0.4499479350283977</v>
       </c>
       <c r="E161" t="n">
-        <v>0.6614855334199121</v>
+        <v>0.8748626262760318</v>
       </c>
       <c r="F161" t="n">
-        <v>-0.8346045787981893</v>
+        <v>0.3250667982999968</v>
       </c>
       <c r="G161" t="n">
-        <v>-1.310742627972998</v>
+        <v>-1.381882610188986</v>
       </c>
     </row>
     <row r="162">
@@ -25726,22 +25726,22 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>-0.5450515350937317</v>
+        <v>-0.436520915390524</v>
       </c>
       <c r="C162" t="n">
         <v>1.229401938021343</v>
       </c>
       <c r="D162" t="n">
-        <v>-0.4203901393116673</v>
+        <v>-0.4490590545706704</v>
       </c>
       <c r="E162" t="n">
-        <v>0.6607514490595072</v>
+        <v>0.8757508727014139</v>
       </c>
       <c r="F162" t="n">
-        <v>-0.8360354605569174</v>
+        <v>0.3204136797383246</v>
       </c>
       <c r="G162" t="n">
-        <v>-1.26296210467933</v>
+        <v>-1.383495212886893</v>
       </c>
     </row>
     <row r="163">
@@ -25751,22 +25751,22 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>-0.5420035833108395</v>
+        <v>-0.4303255645063262</v>
       </c>
       <c r="C163" t="n">
         <v>1.228624223850436</v>
       </c>
       <c r="D163" t="n">
-        <v>-0.4175623726078212</v>
+        <v>-0.4444325181087147</v>
       </c>
       <c r="E163" t="n">
-        <v>0.6633701067091908</v>
+        <v>0.8803753550315103</v>
       </c>
       <c r="F163" t="n">
-        <v>-0.8369646675401176</v>
+        <v>0.3163077641297293</v>
       </c>
       <c r="G163" t="n">
-        <v>-1.269985246330147</v>
+        <v>-1.396642889631886</v>
       </c>
     </row>
     <row r="164">
@@ -25776,22 +25776,22 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>-0.5369562816676505</v>
+        <v>-0.4210314445062355</v>
       </c>
       <c r="C164" t="n">
         <v>1.228153978391041</v>
       </c>
       <c r="D164" t="n">
-        <v>-0.4122063303954011</v>
+        <v>-0.4373248215457078</v>
       </c>
       <c r="E164" t="n">
-        <v>0.6683847450292442</v>
+        <v>0.8874800358780341</v>
       </c>
       <c r="F164" t="n">
-        <v>-0.8374931311580411</v>
+        <v>0.3082746165075589</v>
       </c>
       <c r="G164" t="n">
-        <v>-1.230250575187693</v>
+        <v>-1.389019353984273</v>
       </c>
     </row>
     <row r="165">
@@ -25801,22 +25801,22 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-0.5321569423004433</v>
+        <v>-0.4117655638329616</v>
       </c>
       <c r="C165" t="n">
         <v>1.227928885844292</v>
       </c>
       <c r="D165" t="n">
-        <v>-0.4057790360657121</v>
+        <v>-0.4295494323876526</v>
       </c>
       <c r="E165" t="n">
-        <v>0.6744308911943078</v>
+        <v>0.8952536539431931</v>
       </c>
       <c r="F165" t="n">
-        <v>-0.837736712886212</v>
+        <v>0.2841797229015925</v>
       </c>
       <c r="G165" t="n">
-        <v>-1.252759310127831</v>
+        <v>-1.45109271183292</v>
       </c>
     </row>
     <row r="166">
@@ -25826,22 +25826,22 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>-0.5310482808610769</v>
+        <v>-0.4105149436714326</v>
       </c>
       <c r="C166" t="n">
         <v>1.2278621309799</v>
       </c>
       <c r="D166" t="n">
-        <v>-0.4056181600573527</v>
+        <v>-0.4291733875309065</v>
       </c>
       <c r="E166" t="n">
-        <v>0.6747580536455251</v>
+        <v>0.8956296165547589</v>
       </c>
       <c r="F166" t="n">
-        <v>-0.8378184404271463</v>
+        <v>0.2853110543568272</v>
       </c>
       <c r="G166" t="n">
-        <v>-1.233337218960179</v>
+        <v>-1.430180345119398</v>
       </c>
     </row>
     <row r="167">
@@ -25851,22 +25851,22 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>-0.5310482808610631</v>
+        <v>-0.4105149433771298</v>
       </c>
       <c r="C167" t="n">
         <v>1.227862130979898</v>
       </c>
       <c r="D167" t="n">
-        <v>-0.4056181580205789</v>
+        <v>-0.4291733875102024</v>
       </c>
       <c r="E167" t="n">
-        <v>0.674758057948174</v>
+        <v>0.895629616575463</v>
       </c>
       <c r="F167" t="n">
-        <v>-0.8378184404271493</v>
+        <v>0.2841173676899249</v>
       </c>
       <c r="G167" t="n">
-        <v>-1.243429432400429</v>
+        <v>-1.445816596773652</v>
       </c>
     </row>
   </sheetData>
